--- a/backend/assets/data/fujitsu_capacities_calculated.xlsx
+++ b/backend/assets/data/fujitsu_capacities_calculated.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29609"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -16,7 +16,7 @@
     <sheet name="indoor_combinations" sheetId="2" r:id="rId1"/>
     <sheet name="capacity_70_0" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,28 +39,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="21">
   <si>
-    <t>Indoor Capacity (kBtu/h)</t>
-  </si>
-  <si>
-    <t>Outdoor Temp (°F)</t>
-  </si>
-  <si>
-    <t>Capacity at 70F (Btu/h)</t>
-  </si>
-  <si>
-    <t>AOUH24KWAH3</t>
-  </si>
-  <si>
-    <t>AOUH18KWAH2</t>
-  </si>
-  <si>
     <t>Model</t>
   </si>
   <si>
-    <t>AOUH36KWAH4</t>
-  </si>
-  <si>
-    <t>Capacity at 70°F Indoor / 0°F Outdoor</t>
+    <t>Type</t>
   </si>
   <si>
     <t>Indoor Capacity</t>
@@ -72,13 +54,28 @@
     <t>Unit 2</t>
   </si>
   <si>
+    <t>Unit 3</t>
+  </si>
+  <si>
+    <t>Unit 4</t>
+  </si>
+  <si>
     <t>Max Capacity Unit 1</t>
   </si>
   <si>
     <t>Max Capacity Unit 2</t>
   </si>
   <si>
+    <t>Max Capacity Unit 3</t>
+  </si>
+  <si>
+    <t>Max Capacity Unit 4</t>
+  </si>
+  <si>
     <t>Total Capacity</t>
+  </si>
+  <si>
+    <t>AOUH18KWAH2</t>
   </si>
   <si>
     <t>Non-ducted</t>
@@ -87,26 +84,29 @@
     <t>Ducted</t>
   </si>
   <si>
-    <t>Unit 3</t>
+    <t>AOUH24KWAH3</t>
   </si>
   <si>
-    <t>Max Capacity Unit 3</t>
+    <t>AOUH36KWAH4</t>
   </si>
   <si>
-    <t>Unit 4</t>
+    <t>Capacity at 70°F Indoor / 0°F Outdoor</t>
   </si>
   <si>
-    <t>Max Capacity Unit 4</t>
+    <t>Indoor Capacity (kBtu/h)</t>
   </si>
   <si>
-    <t>Type</t>
+    <t>Outdoor Temp (°F)</t>
+  </si>
+  <si>
+    <t>Capacity at 70F (Btu/h)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -428,62 +428,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4304B4-14C5-40DF-85A6-AED3FDED911B}">
   <dimension ref="A1:N177"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="5.7265625" customWidth="1"/>
-    <col min="8" max="9" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="17.453125" customWidth="1"/>
-    <col min="12" max="12" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.7109375" customWidth="1"/>
+    <col min="8" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="17.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>14</v>
@@ -504,12 +504,12 @@
         <v>16335</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>16</v>
@@ -530,12 +530,12 @@
         <v>17750</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4">
         <v>19</v>
@@ -556,12 +556,12 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>22</v>
@@ -582,12 +582,12 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>18</v>
@@ -608,12 +608,12 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>21</v>
@@ -634,12 +634,12 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8">
         <v>24</v>
@@ -660,12 +660,12 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9">
         <v>24</v>
@@ -686,12 +686,12 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10">
         <v>14</v>
@@ -712,12 +712,12 @@
         <v>16335</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11">
         <v>16</v>
@@ -738,12 +738,12 @@
         <v>17750</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>19</v>
@@ -764,12 +764,12 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>18</v>
@@ -790,12 +790,12 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14">
         <v>21</v>
@@ -816,12 +816,12 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15">
         <v>24</v>
@@ -842,12 +842,12 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16">
         <v>14</v>
@@ -872,12 +872,12 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -902,12 +902,12 @@
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18">
         <v>19</v>
@@ -932,12 +932,12 @@
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C19">
         <v>22</v>
@@ -962,12 +962,12 @@
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C20">
         <v>25</v>
@@ -992,12 +992,12 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C21">
         <v>18</v>
@@ -1022,12 +1022,12 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1052,12 +1052,12 @@
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C23">
         <v>24</v>
@@ -1082,12 +1082,12 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24">
         <v>27</v>
@@ -1112,12 +1112,12 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1142,12 +1142,12 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26">
         <v>27</v>
@@ -1172,12 +1172,12 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C27">
         <v>30</v>
@@ -1202,12 +1202,12 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C28">
         <v>30</v>
@@ -1232,12 +1232,12 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29">
         <v>21</v>
@@ -1267,12 +1267,12 @@
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C30">
         <v>23</v>
@@ -1302,12 +1302,12 @@
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C31">
         <v>26</v>
@@ -1337,12 +1337,12 @@
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C32">
         <v>29</v>
@@ -1372,12 +1372,12 @@
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C33">
         <v>25</v>
@@ -1407,12 +1407,12 @@
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C34">
         <v>28</v>
@@ -1442,12 +1442,12 @@
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C35">
         <v>31</v>
@@ -1477,12 +1477,12 @@
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C36">
         <v>31</v>
@@ -1512,12 +1512,12 @@
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C37">
         <v>27</v>
@@ -1547,12 +1547,12 @@
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C38">
         <v>30</v>
@@ -1582,12 +1582,12 @@
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C39">
         <v>14</v>
@@ -1610,12 +1610,12 @@
         <v>16115</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C40">
         <v>16</v>
@@ -1638,12 +1638,12 @@
         <v>17785</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C41">
         <v>19</v>
@@ -1666,12 +1666,12 @@
         <v>19165</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C42">
         <v>25</v>
@@ -1694,12 +1694,12 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C43">
         <v>18</v>
@@ -1722,12 +1722,12 @@
         <v>18440</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C44">
         <v>21</v>
@@ -1750,12 +1750,12 @@
         <v>20690</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C45">
         <v>27</v>
@@ -1778,12 +1778,12 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C46">
         <v>24</v>
@@ -1806,12 +1806,12 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C47">
         <v>30</v>
@@ -1834,12 +1834,12 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C48">
         <v>21</v>
@@ -1868,12 +1868,12 @@
         <v>20690</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C49">
         <v>23</v>
@@ -1902,12 +1902,12 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C50">
         <v>26</v>
@@ -1936,12 +1936,12 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C51">
         <v>25</v>
@@ -1970,12 +1970,12 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C52">
         <v>28</v>
@@ -2004,12 +2004,12 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C53">
         <v>31</v>
@@ -2038,12 +2038,12 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C54">
         <v>27</v>
@@ -2072,12 +2072,12 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C55">
         <v>30</v>
@@ -2106,12 +2106,12 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C56">
         <v>31</v>
@@ -2132,12 +2132,12 @@
         <v>27260</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C57">
         <v>33</v>
@@ -2158,12 +2158,12 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C58">
         <v>30</v>
@@ -2184,12 +2184,12 @@
         <v>26610</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C59">
         <v>36</v>
@@ -2210,12 +2210,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C60">
         <v>33</v>
@@ -2236,12 +2236,12 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C61">
         <v>39</v>
@@ -2262,12 +2262,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B62" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C62">
         <v>36</v>
@@ -2288,12 +2288,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C63">
         <v>42</v>
@@ -2314,12 +2314,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C64">
         <v>26</v>
@@ -2346,12 +2346,12 @@
         <v>24010</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C65">
         <v>29</v>
@@ -2378,12 +2378,12 @@
         <v>25960</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B66" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C66">
         <v>32</v>
@@ -2410,12 +2410,12 @@
         <v>27910</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C67">
         <v>38</v>
@@ -2442,12 +2442,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B68" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C68">
         <v>25</v>
@@ -2474,12 +2474,12 @@
         <v>23360</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C69">
         <v>28</v>
@@ -2506,12 +2506,12 @@
         <v>25310</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C70">
         <v>31</v>
@@ -2538,12 +2538,12 @@
         <v>27260</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C71">
         <v>34</v>
@@ -2570,12 +2570,12 @@
         <v>29260</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B72" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C72">
         <v>40</v>
@@ -2602,12 +2602,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C73">
         <v>31</v>
@@ -2634,12 +2634,12 @@
         <v>27260</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C74">
         <v>34</v>
@@ -2666,12 +2666,12 @@
         <v>29260</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B75" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C75">
         <v>37</v>
@@ -2698,12 +2698,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C76">
         <v>43</v>
@@ -2730,12 +2730,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B77" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C77">
         <v>37</v>
@@ -2762,12 +2762,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B78" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C78">
         <v>40</v>
@@ -2794,12 +2794,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B79" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C79">
         <v>46</v>
@@ -2826,12 +2826,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C80">
         <v>43</v>
@@ -2858,12 +2858,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C81">
         <v>27</v>
@@ -2890,12 +2890,12 @@
         <v>24660</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B82" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C82">
         <v>30</v>
@@ -2922,12 +2922,12 @@
         <v>26610</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B83" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C83">
         <v>33</v>
@@ -2954,12 +2954,12 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B84" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C84">
         <v>36</v>
@@ -2986,12 +2986,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B85" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C85">
         <v>42</v>
@@ -3018,12 +3018,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B86" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C86">
         <v>33</v>
@@ -3050,12 +3050,12 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B87" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C87">
         <v>36</v>
@@ -3082,12 +3082,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B88" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C88">
         <v>39</v>
@@ -3114,12 +3114,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B89" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C89">
         <v>45</v>
@@ -3146,12 +3146,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B90" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C90">
         <v>39</v>
@@ -3178,12 +3178,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B91" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C91">
         <v>42</v>
@@ -3210,12 +3210,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B92" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C92">
         <v>45</v>
@@ -3242,12 +3242,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B93" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C93">
         <v>36</v>
@@ -3274,12 +3274,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B94" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C94">
         <v>39</v>
@@ -3306,12 +3306,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B95" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C95">
         <v>42</v>
@@ -3338,12 +3338,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B96" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C96">
         <v>42</v>
@@ -3370,12 +3370,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B97" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C97">
         <v>45</v>
@@ -3402,12 +3402,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B98" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C98">
         <v>45</v>
@@ -3434,12 +3434,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B99" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C99">
         <v>28</v>
@@ -3472,12 +3472,12 @@
         <v>25310</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B100" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C100">
         <v>30</v>
@@ -3510,12 +3510,12 @@
         <v>26610</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B101" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C101">
         <v>33</v>
@@ -3548,12 +3548,12 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B102" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C102">
         <v>36</v>
@@ -3586,12 +3586,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B103" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C103">
         <v>39</v>
@@ -3624,12 +3624,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B104" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C104">
         <v>45</v>
@@ -3662,12 +3662,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B105" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C105">
         <v>32</v>
@@ -3700,12 +3700,12 @@
         <v>27910</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B106" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C106">
         <v>35</v>
@@ -3738,12 +3738,12 @@
         <v>29880</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B107" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C107">
         <v>38</v>
@@ -3776,12 +3776,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B108" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C108">
         <v>41</v>
@@ -3814,12 +3814,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B109" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C109">
         <v>38</v>
@@ -3852,12 +3852,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B110" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C110">
         <v>41</v>
@@ -3890,12 +3890,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B111" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C111">
         <v>44</v>
@@ -3928,12 +3928,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B112" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C112">
         <v>44</v>
@@ -3966,12 +3966,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B113" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C113">
         <v>34</v>
@@ -4004,12 +4004,12 @@
         <v>29260</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B114" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C114">
         <v>37</v>
@@ -4042,12 +4042,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B115" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C115">
         <v>40</v>
@@ -4080,12 +4080,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B116" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C116">
         <v>43</v>
@@ -4118,12 +4118,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B117" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C117">
         <v>40</v>
@@ -4156,12 +4156,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B118" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C118">
         <v>43</v>
@@ -4194,12 +4194,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B119" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C119">
         <v>46</v>
@@ -4232,12 +4232,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B120" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C120">
         <v>46</v>
@@ -4270,12 +4270,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B121" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C121">
         <v>43</v>
@@ -4308,12 +4308,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B122" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C122">
         <v>46</v>
@@ -4346,12 +4346,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B123" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C123">
         <v>36</v>
@@ -4384,12 +4384,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B124" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C124">
         <v>39</v>
@@ -4422,12 +4422,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:12">
       <c r="A125" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B125" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C125">
         <v>42</v>
@@ -4460,12 +4460,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C126">
         <v>45</v>
@@ -4498,12 +4498,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C127">
         <v>42</v>
@@ -4536,12 +4536,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B128" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C128">
         <v>45</v>
@@ -4574,12 +4574,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:12">
       <c r="A129" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C129">
         <v>45</v>
@@ -4612,12 +4612,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B130" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C130">
         <v>31</v>
@@ -4638,12 +4638,12 @@
         <v>27260</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:12">
       <c r="A131" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B131" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C131">
         <v>33</v>
@@ -4664,12 +4664,12 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:12">
       <c r="A132" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B132" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C132">
         <v>30</v>
@@ -4690,12 +4690,12 @@
         <v>26610</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:12">
       <c r="A133" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -4716,12 +4716,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:12">
       <c r="A134" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B134" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C134">
         <v>36</v>
@@ -4742,12 +4742,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:12">
       <c r="A135" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B135" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C135">
         <v>42</v>
@@ -4768,12 +4768,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:12">
       <c r="A136" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B136" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C136">
         <v>26</v>
@@ -4800,12 +4800,12 @@
         <v>24010</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:12">
       <c r="A137" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B137" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C137">
         <v>32</v>
@@ -4832,12 +4832,12 @@
         <v>27910</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:12">
       <c r="A138" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B138" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C138">
         <v>38</v>
@@ -4864,12 +4864,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:12">
       <c r="A139" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B139" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C139">
         <v>25</v>
@@ -4896,12 +4896,12 @@
         <v>23360</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:12">
       <c r="A140" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B140" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C140">
         <v>28</v>
@@ -4928,12 +4928,12 @@
         <v>25310</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:12">
       <c r="A141" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B141" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C141">
         <v>34</v>
@@ -4960,12 +4960,12 @@
         <v>29260</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:12">
       <c r="A142" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B142" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C142">
         <v>40</v>
@@ -4992,12 +4992,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B143" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C143">
         <v>31</v>
@@ -5024,12 +5024,12 @@
         <v>27260</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:12">
       <c r="A144" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B144" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C144">
         <v>37</v>
@@ -5056,12 +5056,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:12">
       <c r="A145" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B145" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C145">
         <v>43</v>
@@ -5088,12 +5088,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:12">
       <c r="A146" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B146" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C146">
         <v>43</v>
@@ -5120,12 +5120,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:12">
       <c r="A147" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B147" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C147">
         <v>27</v>
@@ -5152,12 +5152,12 @@
         <v>24660</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:12">
       <c r="A148" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C148">
         <v>30</v>
@@ -5184,12 +5184,12 @@
         <v>26610</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:12">
       <c r="A149" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B149" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C149">
         <v>36</v>
@@ -5216,12 +5216,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:12">
       <c r="A150" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B150" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C150">
         <v>42</v>
@@ -5248,12 +5248,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:12">
       <c r="A151" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C151">
         <v>33</v>
@@ -5280,12 +5280,12 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:12">
       <c r="A152" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B152" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C152">
         <v>39</v>
@@ -5312,12 +5312,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:12">
       <c r="A153" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B153" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C153">
         <v>45</v>
@@ -5344,12 +5344,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:12">
       <c r="A154" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B154" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C154">
         <v>45</v>
@@ -5376,12 +5376,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:12">
       <c r="A155" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B155" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C155">
         <v>36</v>
@@ -5408,12 +5408,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:12">
       <c r="A156" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C156">
         <v>42</v>
@@ -5440,12 +5440,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:12">
       <c r="A157" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C157">
         <v>28</v>
@@ -5478,12 +5478,12 @@
         <v>25310</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:12">
       <c r="A158" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C158">
         <v>30</v>
@@ -5516,12 +5516,12 @@
         <v>26610</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:12">
       <c r="A159" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C159">
         <v>33</v>
@@ -5554,12 +5554,12 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:12">
       <c r="A160" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C160">
         <v>39</v>
@@ -5592,12 +5592,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:12">
       <c r="A161" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C161">
         <v>45</v>
@@ -5630,12 +5630,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:12">
       <c r="A162" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C162">
         <v>32</v>
@@ -5668,12 +5668,12 @@
         <v>27910</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:12">
       <c r="A163" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C163">
         <v>35</v>
@@ -5706,12 +5706,12 @@
         <v>29880</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:12">
       <c r="A164" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C164">
         <v>41</v>
@@ -5744,12 +5744,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:12">
       <c r="A165" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C165">
         <v>38</v>
@@ -5782,12 +5782,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:12">
       <c r="A166" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C166">
         <v>44</v>
@@ -5820,12 +5820,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:12">
       <c r="A167" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C167">
         <v>34</v>
@@ -5858,12 +5858,12 @@
         <v>29260</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:12">
       <c r="A168" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C168">
         <v>37</v>
@@ -5896,12 +5896,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:12">
       <c r="A169" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C169">
         <v>43</v>
@@ -5934,12 +5934,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:12">
       <c r="A170" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C170">
         <v>40</v>
@@ -5972,12 +5972,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:12">
       <c r="A171" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B171" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C171">
         <v>46</v>
@@ -6010,12 +6010,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:12">
       <c r="A172" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B172" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C172">
         <v>43</v>
@@ -6048,12 +6048,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:12">
       <c r="A173" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B173" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C173">
         <v>36</v>
@@ -6086,12 +6086,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:12">
       <c r="A174" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B174" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C174">
         <v>39</v>
@@ -6124,12 +6124,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:12">
       <c r="A175" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B175" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C175">
         <v>45</v>
@@ -6162,12 +6162,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:12">
       <c r="A176" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B176" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C176">
         <v>42</v>
@@ -6200,12 +6200,12 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:12">
       <c r="A177" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B177" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C177">
         <v>45</v>
@@ -6247,39 +6247,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D46"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>46</v>
@@ -6291,9 +6291,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>45</v>
@@ -6305,9 +6305,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B5">
         <v>44</v>
@@ -6319,9 +6319,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>43</v>
@@ -6333,9 +6333,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>42</v>
@@ -6347,9 +6347,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>41</v>
@@ -6361,9 +6361,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>40</v>
@@ -6375,9 +6375,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>39</v>
@@ -6389,9 +6389,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>38</v>
@@ -6403,9 +6403,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>37</v>
@@ -6417,9 +6417,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>36</v>
@@ -6431,9 +6431,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>35</v>
@@ -6445,9 +6445,9 @@
         <v>29880</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B15">
         <v>34</v>
@@ -6459,9 +6459,9 @@
         <v>29260</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>33</v>
@@ -6473,9 +6473,9 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>32</v>
@@ -6487,9 +6487,9 @@
         <v>27910</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B18">
         <v>31</v>
@@ -6501,9 +6501,9 @@
         <v>27260</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B19">
         <v>30</v>
@@ -6515,9 +6515,9 @@
         <v>26610</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B20">
         <v>29</v>
@@ -6529,9 +6529,9 @@
         <v>25960</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>28</v>
@@ -6543,9 +6543,9 @@
         <v>25310</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B22">
         <v>27</v>
@@ -6557,9 +6557,9 @@
         <v>24660</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B23">
         <v>26</v>
@@ -6571,9 +6571,9 @@
         <v>24010</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B24">
         <v>25</v>
@@ -6585,9 +6585,9 @@
         <v>23360</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B25">
         <v>31</v>
@@ -6599,9 +6599,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B26">
         <v>30</v>
@@ -6613,9 +6613,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B27">
         <v>29</v>
@@ -6627,9 +6627,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B28">
         <v>28</v>
@@ -6641,9 +6641,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B29">
         <v>27</v>
@@ -6655,9 +6655,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B30">
         <v>26</v>
@@ -6669,9 +6669,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B31">
         <v>25</v>
@@ -6683,9 +6683,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B32">
         <v>24</v>
@@ -6697,9 +6697,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B33">
         <v>23</v>
@@ -6711,9 +6711,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B34">
         <v>22</v>
@@ -6725,9 +6725,9 @@
         <v>21630</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B35">
         <v>21</v>
@@ -6739,9 +6739,9 @@
         <v>20690</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B36">
         <v>19</v>
@@ -6753,9 +6753,9 @@
         <v>19165</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B37">
         <v>18</v>
@@ -6767,9 +6767,9 @@
         <v>18440</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B38">
         <v>16</v>
@@ -6781,9 +6781,9 @@
         <v>17785</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B39">
         <v>14</v>
@@ -6795,9 +6795,9 @@
         <v>16115</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B40">
         <v>24</v>
@@ -6809,9 +6809,9 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B41">
         <v>22</v>
@@ -6823,9 +6823,9 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B42">
         <v>21</v>
@@ -6837,9 +6837,9 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B43">
         <v>19</v>
@@ -6851,9 +6851,9 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B44">
         <v>18</v>
@@ -6865,9 +6865,9 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B45">
         <v>16</v>
@@ -6879,9 +6879,9 @@
         <v>17750</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B46">
         <v>14</v>

--- a/backend/assets/data/fujitsu_capacities_calculated.xlsx
+++ b/backend/assets/data/fujitsu_capacities_calculated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexWest\OneDrive - Paradigm Energy Services\data_operations\ashp_calculator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pardigmpartners-my.sharepoint.com/personal/alex_paradigm-esco_com/Documents/data_operations/ashp_calculator/backend/assets/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D420F103-AC1D-4B35-A441-D57FBF080E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{D420F103-AC1D-4B35-A441-D57FBF080E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7573420A-3779-4C44-8361-9FBDA80001B9}"/>
   <bookViews>
-    <workbookView xWindow="4940" yWindow="1440" windowWidth="30890" windowHeight="17110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6110" yWindow="820" windowWidth="30890" windowHeight="17460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="indoor_combinations" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="27">
   <si>
     <t>Model</t>
   </si>
@@ -101,12 +101,30 @@
   <si>
     <t>Capacity at 70F (Btu/h)</t>
   </si>
+  <si>
+    <t>AOUH12KUAS1</t>
+  </si>
+  <si>
+    <t>AOUH18KUAS1</t>
+  </si>
+  <si>
+    <t>AOUH24KUAS1</t>
+  </si>
+  <si>
+    <t>AOUH30KUAS1</t>
+  </si>
+  <si>
+    <t>AOUH36KUAS1</t>
+  </si>
+  <si>
+    <t>AOUH48KUAS1</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,11 +159,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,20 +451,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4304B4-14C5-40DF-85A6-AED3FDED911B}">
-  <dimension ref="A1:N177"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:N183"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="5.7109375" customWidth="1"/>
-    <col min="8" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="17.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.7265625" customWidth="1"/>
+    <col min="8" max="9" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="17.453125" customWidth="1"/>
+    <col min="12" max="12" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -478,7 +502,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -504,7 +528,7 @@
         <v>16335</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -530,7 +554,7 @@
         <v>17750</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -556,7 +580,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -582,7 +606,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -608,7 +632,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -634,7 +658,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -660,7 +684,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -686,7 +710,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -712,7 +736,7 @@
         <v>16335</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -738,7 +762,7 @@
         <v>17750</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -764,7 +788,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -790,7 +814,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -816,7 +840,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -842,7 +866,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -872,7 +896,7 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -902,7 +926,7 @@
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -932,7 +956,7 @@
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -962,7 +986,7 @@
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -992,7 +1016,7 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -1022,7 +1046,7 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -1052,7 +1076,7 @@
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -1082,7 +1106,7 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1112,7 +1136,7 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -1142,7 +1166,7 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -1172,7 +1196,7 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -1202,7 +1226,7 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -1232,7 +1256,7 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -1267,7 +1291,7 @@
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>15</v>
       </c>
@@ -1302,7 +1326,7 @@
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -1337,7 +1361,7 @@
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -1372,7 +1396,7 @@
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -1407,7 +1431,7 @@
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -1442,7 +1466,7 @@
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -1477,7 +1501,7 @@
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -1512,7 +1536,7 @@
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -1547,7 +1571,7 @@
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -1582,7 +1606,7 @@
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -1610,7 +1634,7 @@
         <v>16115</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -1638,7 +1662,7 @@
         <v>17785</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -1666,7 +1690,7 @@
         <v>19165</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>15</v>
       </c>
@@ -1694,7 +1718,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>15</v>
       </c>
@@ -1722,7 +1746,7 @@
         <v>18440</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -1750,7 +1774,7 @@
         <v>20690</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -1778,7 +1802,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -1806,7 +1830,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -1834,7 +1858,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -1868,7 +1892,7 @@
         <v>20690</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -1902,7 +1926,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>15</v>
       </c>
@@ -1936,7 +1960,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -1970,7 +1994,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -2004,7 +2028,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -2038,7 +2062,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>15</v>
       </c>
@@ -2072,7 +2096,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>15</v>
       </c>
@@ -2106,7 +2130,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>16</v>
       </c>
@@ -2132,7 +2156,7 @@
         <v>27260</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>16</v>
       </c>
@@ -2158,7 +2182,7 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>16</v>
       </c>
@@ -2184,7 +2208,7 @@
         <v>26610</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>16</v>
       </c>
@@ -2210,7 +2234,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>16</v>
       </c>
@@ -2236,7 +2260,7 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>16</v>
       </c>
@@ -2262,7 +2286,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>16</v>
       </c>
@@ -2288,7 +2312,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>16</v>
       </c>
@@ -2314,7 +2338,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>16</v>
       </c>
@@ -2346,7 +2370,7 @@
         <v>24010</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>16</v>
       </c>
@@ -2378,7 +2402,7 @@
         <v>25960</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>16</v>
       </c>
@@ -2410,7 +2434,7 @@
         <v>27910</v>
       </c>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>16</v>
       </c>
@@ -2442,7 +2466,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>16</v>
       </c>
@@ -2474,7 +2498,7 @@
         <v>23360</v>
       </c>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>16</v>
       </c>
@@ -2506,7 +2530,7 @@
         <v>25310</v>
       </c>
     </row>
-    <row r="70" spans="1:12">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>16</v>
       </c>
@@ -2538,7 +2562,7 @@
         <v>27260</v>
       </c>
     </row>
-    <row r="71" spans="1:12">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>16</v>
       </c>
@@ -2570,7 +2594,7 @@
         <v>29260</v>
       </c>
     </row>
-    <row r="72" spans="1:12">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>16</v>
       </c>
@@ -2602,7 +2626,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>16</v>
       </c>
@@ -2634,7 +2658,7 @@
         <v>27260</v>
       </c>
     </row>
-    <row r="74" spans="1:12">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>16</v>
       </c>
@@ -2666,7 +2690,7 @@
         <v>29260</v>
       </c>
     </row>
-    <row r="75" spans="1:12">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>16</v>
       </c>
@@ -2698,7 +2722,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="76" spans="1:12">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>16</v>
       </c>
@@ -2730,7 +2754,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>16</v>
       </c>
@@ -2762,7 +2786,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>16</v>
       </c>
@@ -2794,7 +2818,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="79" spans="1:12">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>16</v>
       </c>
@@ -2826,7 +2850,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="80" spans="1:12">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>16</v>
       </c>
@@ -2858,7 +2882,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="81" spans="1:12">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>16</v>
       </c>
@@ -2890,7 +2914,7 @@
         <v>24660</v>
       </c>
     </row>
-    <row r="82" spans="1:12">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>16</v>
       </c>
@@ -2922,7 +2946,7 @@
         <v>26610</v>
       </c>
     </row>
-    <row r="83" spans="1:12">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>16</v>
       </c>
@@ -2954,7 +2978,7 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="84" spans="1:12">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>16</v>
       </c>
@@ -2986,7 +3010,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="85" spans="1:12">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>16</v>
       </c>
@@ -3018,7 +3042,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="86" spans="1:12">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>16</v>
       </c>
@@ -3050,7 +3074,7 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="87" spans="1:12">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>16</v>
       </c>
@@ -3082,7 +3106,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="88" spans="1:12">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>16</v>
       </c>
@@ -3114,7 +3138,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="89" spans="1:12">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>16</v>
       </c>
@@ -3146,7 +3170,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>16</v>
       </c>
@@ -3178,7 +3202,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>16</v>
       </c>
@@ -3210,7 +3234,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>16</v>
       </c>
@@ -3242,7 +3266,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>16</v>
       </c>
@@ -3274,7 +3298,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>16</v>
       </c>
@@ -3306,7 +3330,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>16</v>
       </c>
@@ -3338,7 +3362,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="96" spans="1:12">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>16</v>
       </c>
@@ -3370,7 +3394,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="97" spans="1:12">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>16</v>
       </c>
@@ -3402,7 +3426,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="98" spans="1:12">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>16</v>
       </c>
@@ -3434,7 +3458,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="99" spans="1:12">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>16</v>
       </c>
@@ -3472,7 +3496,7 @@
         <v>25310</v>
       </c>
     </row>
-    <row r="100" spans="1:12">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>16</v>
       </c>
@@ -3510,7 +3534,7 @@
         <v>26610</v>
       </c>
     </row>
-    <row r="101" spans="1:12">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>16</v>
       </c>
@@ -3548,7 +3572,7 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="102" spans="1:12">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -3586,7 +3610,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="103" spans="1:12">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -3624,7 +3648,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="104" spans="1:12">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -3662,7 +3686,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="105" spans="1:12">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>16</v>
       </c>
@@ -3700,7 +3724,7 @@
         <v>27910</v>
       </c>
     </row>
-    <row r="106" spans="1:12">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>16</v>
       </c>
@@ -3738,7 +3762,7 @@
         <v>29880</v>
       </c>
     </row>
-    <row r="107" spans="1:12">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>16</v>
       </c>
@@ -3776,7 +3800,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="108" spans="1:12">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>16</v>
       </c>
@@ -3814,7 +3838,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="109" spans="1:12">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>16</v>
       </c>
@@ -3852,7 +3876,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="110" spans="1:12">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>16</v>
       </c>
@@ -3890,7 +3914,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="111" spans="1:12">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>16</v>
       </c>
@@ -3928,7 +3952,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="112" spans="1:12">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>16</v>
       </c>
@@ -3966,7 +3990,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="113" spans="1:12">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>16</v>
       </c>
@@ -4004,7 +4028,7 @@
         <v>29260</v>
       </c>
     </row>
-    <row r="114" spans="1:12">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>16</v>
       </c>
@@ -4042,7 +4066,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="115" spans="1:12">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>16</v>
       </c>
@@ -4080,7 +4104,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="116" spans="1:12">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>16</v>
       </c>
@@ -4118,7 +4142,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="117" spans="1:12">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>16</v>
       </c>
@@ -4156,7 +4180,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="118" spans="1:12">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>16</v>
       </c>
@@ -4194,7 +4218,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="119" spans="1:12">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>16</v>
       </c>
@@ -4232,7 +4256,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="120" spans="1:12">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>16</v>
       </c>
@@ -4270,7 +4294,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="121" spans="1:12">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>16</v>
       </c>
@@ -4308,7 +4332,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="122" spans="1:12">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>16</v>
       </c>
@@ -4346,7 +4370,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="123" spans="1:12">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>16</v>
       </c>
@@ -4384,7 +4408,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="124" spans="1:12">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>16</v>
       </c>
@@ -4422,7 +4446,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="125" spans="1:12">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>16</v>
       </c>
@@ -4460,7 +4484,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="126" spans="1:12">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>16</v>
       </c>
@@ -4498,7 +4522,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="127" spans="1:12">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>16</v>
       </c>
@@ -4536,7 +4560,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="128" spans="1:12">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>16</v>
       </c>
@@ -4574,7 +4598,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="129" spans="1:12">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>16</v>
       </c>
@@ -4612,7 +4636,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="130" spans="1:12">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>16</v>
       </c>
@@ -4638,7 +4662,7 @@
         <v>27260</v>
       </c>
     </row>
-    <row r="131" spans="1:12">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>16</v>
       </c>
@@ -4664,7 +4688,7 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="132" spans="1:12">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>16</v>
       </c>
@@ -4690,7 +4714,7 @@
         <v>26610</v>
       </c>
     </row>
-    <row r="133" spans="1:12">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>16</v>
       </c>
@@ -4716,7 +4740,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="134" spans="1:12">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>16</v>
       </c>
@@ -4742,7 +4766,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="135" spans="1:12">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>16</v>
       </c>
@@ -4768,7 +4792,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="136" spans="1:12">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>16</v>
       </c>
@@ -4800,7 +4824,7 @@
         <v>24010</v>
       </c>
     </row>
-    <row r="137" spans="1:12">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>16</v>
       </c>
@@ -4832,7 +4856,7 @@
         <v>27910</v>
       </c>
     </row>
-    <row r="138" spans="1:12">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>16</v>
       </c>
@@ -4864,7 +4888,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="139" spans="1:12">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>16</v>
       </c>
@@ -4896,7 +4920,7 @@
         <v>23360</v>
       </c>
     </row>
-    <row r="140" spans="1:12">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>16</v>
       </c>
@@ -4928,7 +4952,7 @@
         <v>25310</v>
       </c>
     </row>
-    <row r="141" spans="1:12">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>16</v>
       </c>
@@ -4960,7 +4984,7 @@
         <v>29260</v>
       </c>
     </row>
-    <row r="142" spans="1:12">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>16</v>
       </c>
@@ -4992,7 +5016,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="143" spans="1:12">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>16</v>
       </c>
@@ -5024,7 +5048,7 @@
         <v>27260</v>
       </c>
     </row>
-    <row r="144" spans="1:12">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>16</v>
       </c>
@@ -5056,7 +5080,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="145" spans="1:12">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>16</v>
       </c>
@@ -5088,7 +5112,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="146" spans="1:12">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>16</v>
       </c>
@@ -5120,7 +5144,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="147" spans="1:12">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>16</v>
       </c>
@@ -5152,7 +5176,7 @@
         <v>24660</v>
       </c>
     </row>
-    <row r="148" spans="1:12">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>16</v>
       </c>
@@ -5184,7 +5208,7 @@
         <v>26610</v>
       </c>
     </row>
-    <row r="149" spans="1:12">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>16</v>
       </c>
@@ -5216,7 +5240,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="150" spans="1:12">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>16</v>
       </c>
@@ -5248,7 +5272,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="151" spans="1:12">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>16</v>
       </c>
@@ -5280,7 +5304,7 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="152" spans="1:12">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>16</v>
       </c>
@@ -5312,7 +5336,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="153" spans="1:12">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>16</v>
       </c>
@@ -5344,7 +5368,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="154" spans="1:12">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>16</v>
       </c>
@@ -5376,7 +5400,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="155" spans="1:12">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>16</v>
       </c>
@@ -5408,7 +5432,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="156" spans="1:12">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>16</v>
       </c>
@@ -5440,7 +5464,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="157" spans="1:12">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>16</v>
       </c>
@@ -5478,7 +5502,7 @@
         <v>25310</v>
       </c>
     </row>
-    <row r="158" spans="1:12">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>16</v>
       </c>
@@ -5516,7 +5540,7 @@
         <v>26610</v>
       </c>
     </row>
-    <row r="159" spans="1:12">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>16</v>
       </c>
@@ -5554,7 +5578,7 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="160" spans="1:12">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>16</v>
       </c>
@@ -5592,7 +5616,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="161" spans="1:12">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>16</v>
       </c>
@@ -5630,7 +5654,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="162" spans="1:12">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>16</v>
       </c>
@@ -5668,7 +5692,7 @@
         <v>27910</v>
       </c>
     </row>
-    <row r="163" spans="1:12">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>16</v>
       </c>
@@ -5706,7 +5730,7 @@
         <v>29880</v>
       </c>
     </row>
-    <row r="164" spans="1:12">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>16</v>
       </c>
@@ -5744,7 +5768,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="165" spans="1:12">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>16</v>
       </c>
@@ -5782,7 +5806,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="166" spans="1:12">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>16</v>
       </c>
@@ -5820,7 +5844,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="167" spans="1:12">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>16</v>
       </c>
@@ -5858,7 +5882,7 @@
         <v>29260</v>
       </c>
     </row>
-    <row r="168" spans="1:12">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>16</v>
       </c>
@@ -5896,7 +5920,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="169" spans="1:12">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>16</v>
       </c>
@@ -5934,7 +5958,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="170" spans="1:12">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>16</v>
       </c>
@@ -5972,7 +5996,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="171" spans="1:12">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>16</v>
       </c>
@@ -6010,7 +6034,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="172" spans="1:12">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>16</v>
       </c>
@@ -6048,7 +6072,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="173" spans="1:12">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>16</v>
       </c>
@@ -6086,7 +6110,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="174" spans="1:12">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>16</v>
       </c>
@@ -6124,7 +6148,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="175" spans="1:12">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>16</v>
       </c>
@@ -6162,7 +6186,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="176" spans="1:12">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>16</v>
       </c>
@@ -6200,7 +6224,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="177" spans="1:12">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>16</v>
       </c>
@@ -6236,6 +6260,156 @@
       </c>
       <c r="L177" s="1">
         <v>30760</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A178" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B178" t="s">
+        <v>14</v>
+      </c>
+      <c r="C178" s="3">
+        <v>12</v>
+      </c>
+      <c r="D178" s="3">
+        <v>12</v>
+      </c>
+      <c r="E178" s="4"/>
+      <c r="F178" s="3"/>
+      <c r="G178" s="3"/>
+      <c r="H178" s="4">
+        <v>15310</v>
+      </c>
+      <c r="I178" s="3"/>
+      <c r="J178" s="3"/>
+      <c r="L178" s="4">
+        <v>15310</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A179" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B179" t="s">
+        <v>14</v>
+      </c>
+      <c r="C179" s="3">
+        <v>18</v>
+      </c>
+      <c r="D179" s="3">
+        <v>18</v>
+      </c>
+      <c r="E179" s="4"/>
+      <c r="F179" s="3"/>
+      <c r="G179" s="3"/>
+      <c r="H179" s="4">
+        <v>15935</v>
+      </c>
+      <c r="I179" s="3"/>
+      <c r="J179" s="3"/>
+      <c r="L179" s="4">
+        <v>15935</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A180" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B180" t="s">
+        <v>14</v>
+      </c>
+      <c r="C180" s="3">
+        <v>24</v>
+      </c>
+      <c r="D180" s="3">
+        <v>24</v>
+      </c>
+      <c r="E180" s="4"/>
+      <c r="F180" s="3"/>
+      <c r="G180" s="3"/>
+      <c r="H180" s="4">
+        <v>23230</v>
+      </c>
+      <c r="I180" s="3"/>
+      <c r="J180" s="3"/>
+      <c r="L180" s="4">
+        <v>23230</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A181" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B181" t="s">
+        <v>14</v>
+      </c>
+      <c r="C181" s="3">
+        <v>30</v>
+      </c>
+      <c r="D181" s="3">
+        <v>30</v>
+      </c>
+      <c r="E181" s="4"/>
+      <c r="F181" s="3"/>
+      <c r="G181" s="3"/>
+      <c r="H181" s="4">
+        <v>27295</v>
+      </c>
+      <c r="I181" s="3"/>
+      <c r="J181" s="3"/>
+      <c r="L181" s="4">
+        <v>27295</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A182" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B182" t="s">
+        <v>14</v>
+      </c>
+      <c r="C182" s="3">
+        <v>36</v>
+      </c>
+      <c r="D182" s="3">
+        <v>36</v>
+      </c>
+      <c r="E182" s="4"/>
+      <c r="F182" s="3"/>
+      <c r="G182" s="3"/>
+      <c r="H182" s="4">
+        <v>29925</v>
+      </c>
+      <c r="I182" s="3"/>
+      <c r="J182" s="3"/>
+      <c r="L182" s="4">
+        <v>29925</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A183" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B183" t="s">
+        <v>14</v>
+      </c>
+      <c r="C183" s="3">
+        <v>48</v>
+      </c>
+      <c r="D183" s="3">
+        <v>48</v>
+      </c>
+      <c r="E183" s="4"/>
+      <c r="F183" s="3"/>
+      <c r="G183" s="3"/>
+      <c r="H183" s="4">
+        <v>39480</v>
+      </c>
+      <c r="I183" s="3"/>
+      <c r="J183" s="3"/>
+      <c r="L183" s="4">
+        <v>39480</v>
       </c>
     </row>
   </sheetData>
@@ -6247,15 +6421,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D46"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>17</v>
       </c>
@@ -6263,7 +6437,7 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6277,7 +6451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -6291,7 +6465,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -6305,7 +6479,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -6319,7 +6493,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -6333,7 +6507,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -6347,7 +6521,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -6361,7 +6535,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -6375,7 +6549,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -6389,7 +6563,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6403,7 +6577,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -6417,7 +6591,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -6431,7 +6605,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -6445,7 +6619,7 @@
         <v>29880</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -6459,7 +6633,7 @@
         <v>29260</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -6473,7 +6647,7 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -6487,7 +6661,7 @@
         <v>27910</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -6501,7 +6675,7 @@
         <v>27260</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -6515,7 +6689,7 @@
         <v>26610</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -6529,7 +6703,7 @@
         <v>25960</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -6543,7 +6717,7 @@
         <v>25310</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -6557,7 +6731,7 @@
         <v>24660</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -6571,7 +6745,7 @@
         <v>24010</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -6585,7 +6759,7 @@
         <v>23360</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -6599,7 +6773,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -6613,7 +6787,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -6627,7 +6801,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -6641,7 +6815,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -6655,7 +6829,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>15</v>
       </c>
@@ -6669,7 +6843,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -6683,7 +6857,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -6697,7 +6871,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -6711,7 +6885,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -6725,7 +6899,7 @@
         <v>21630</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -6739,7 +6913,7 @@
         <v>20690</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -6753,7 +6927,7 @@
         <v>19165</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -6767,7 +6941,7 @@
         <v>18440</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -6781,7 +6955,7 @@
         <v>17785</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -6795,7 +6969,7 @@
         <v>16115</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>12</v>
       </c>
@@ -6809,7 +6983,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>12</v>
       </c>
@@ -6823,7 +6997,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -6837,7 +7011,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>12</v>
       </c>
@@ -6851,7 +7025,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>12</v>
       </c>
@@ -6865,7 +7039,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>12</v>
       </c>
@@ -6879,7 +7053,7 @@
         <v>17750</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>12</v>
       </c>

--- a/backend/assets/data/fujitsu_capacities_calculated.xlsx
+++ b/backend/assets/data/fujitsu_capacities_calculated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pardigmpartners-my.sharepoint.com/personal/alex_paradigm-esco_com/Documents/data_operations/ashp_calculator/backend/assets/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{D420F103-AC1D-4B35-A441-D57FBF080E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7573420A-3779-4C44-8361-9FBDA80001B9}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{D420F103-AC1D-4B35-A441-D57FBF080E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C634B1E9-07E3-4BC0-A3B4-EFD420E9B3DF}"/>
   <bookViews>
-    <workbookView xWindow="6110" yWindow="820" windowWidth="30890" windowHeight="17460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5690" yWindow="2620" windowWidth="30890" windowHeight="17110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="indoor_combinations" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="35">
   <si>
     <t>Model</t>
   </si>
@@ -119,6 +119,30 @@
   <si>
     <t>AOUH48KUAS1</t>
   </si>
+  <si>
+    <t>Op. Watts/Htg</t>
+  </si>
+  <si>
+    <t>Breaker Req.</t>
+  </si>
+  <si>
+    <t>BTU @ 5*F</t>
+  </si>
+  <si>
+    <t>BTU @ 0*F</t>
+  </si>
+  <si>
+    <t>Tonnage</t>
+  </si>
+  <si>
+    <t>SEER2</t>
+  </si>
+  <si>
+    <t>EER2</t>
+  </si>
+  <si>
+    <t>HSPF2</t>
+  </si>
 </sst>
 </file>
 
@@ -163,13 +187,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -186,6 +210,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -451,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4304B4-14C5-40DF-85A6-AED3FDED911B}">
-  <dimension ref="A1:N183"/>
+  <dimension ref="A1:U183"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -462,9 +490,16 @@
     <col min="8" max="9" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="17.453125" customWidth="1"/>
     <col min="12" max="12" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.90625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -501,8 +536,32 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>30</v>
+      </c>
+      <c r="R1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -528,7 +587,7 @@
         <v>16335</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -554,7 +613,7 @@
         <v>17750</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -580,7 +639,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -606,7 +665,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -632,7 +691,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -658,7 +717,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -684,7 +743,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -710,7 +769,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -736,7 +795,7 @@
         <v>16335</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -762,7 +821,7 @@
         <v>17750</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -788,7 +847,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -814,7 +873,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -840,7 +899,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -866,7 +925,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -6224,7 +6283,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>16</v>
       </c>
@@ -6262,154 +6321,298 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A178" s="3" t="s">
+    <row r="178" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A178" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B178" t="s">
         <v>14</v>
       </c>
-      <c r="C178" s="3">
-        <v>12</v>
-      </c>
-      <c r="D178" s="3">
-        <v>12</v>
-      </c>
-      <c r="E178" s="4"/>
-      <c r="F178" s="3"/>
-      <c r="G178" s="3"/>
-      <c r="H178" s="4">
+      <c r="C178" s="2">
+        <v>12</v>
+      </c>
+      <c r="D178" s="2">
+        <v>12</v>
+      </c>
+      <c r="E178" s="3"/>
+      <c r="F178" s="2"/>
+      <c r="G178" s="2"/>
+      <c r="H178" s="3">
         <v>15310</v>
       </c>
-      <c r="I178" s="3"/>
-      <c r="J178" s="3"/>
-      <c r="L178" s="4">
+      <c r="I178" s="2"/>
+      <c r="J178" s="2"/>
+      <c r="L178" s="3">
         <v>15310</v>
       </c>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A179" s="3" t="s">
+      <c r="N178" s="3">
+        <v>3408</v>
+      </c>
+      <c r="O178" s="2">
+        <v>15</v>
+      </c>
+      <c r="P178" s="3">
+        <v>16100</v>
+      </c>
+      <c r="Q178" s="3">
+        <v>15310</v>
+      </c>
+      <c r="R178" s="2">
+        <v>1</v>
+      </c>
+      <c r="S178" s="2">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="T178" s="2">
+        <v>13</v>
+      </c>
+      <c r="U178" s="2">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A179" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B179" t="s">
         <v>14</v>
       </c>
-      <c r="C179" s="3">
+      <c r="C179" s="2">
         <v>18</v>
       </c>
-      <c r="D179" s="3">
+      <c r="D179" s="2">
         <v>18</v>
       </c>
-      <c r="E179" s="4"/>
-      <c r="F179" s="3"/>
-      <c r="G179" s="3"/>
-      <c r="H179" s="4">
+      <c r="E179" s="3"/>
+      <c r="F179" s="2"/>
+      <c r="G179" s="2"/>
+      <c r="H179" s="3">
         <v>15935</v>
       </c>
-      <c r="I179" s="3"/>
-      <c r="J179" s="3"/>
-      <c r="L179" s="4">
+      <c r="I179" s="2"/>
+      <c r="J179" s="2"/>
+      <c r="L179" s="3">
         <v>15935</v>
       </c>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A180" s="3" t="s">
+      <c r="N179" s="3">
+        <v>3552</v>
+      </c>
+      <c r="O179" s="2">
+        <v>20</v>
+      </c>
+      <c r="P179" s="3">
+        <v>17300</v>
+      </c>
+      <c r="Q179" s="3">
+        <v>15935</v>
+      </c>
+      <c r="R179" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S179" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="T179" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="U179" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A180" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B180" t="s">
         <v>14</v>
       </c>
-      <c r="C180" s="3">
+      <c r="C180" s="2">
         <v>24</v>
       </c>
-      <c r="D180" s="3">
+      <c r="D180" s="2">
         <v>24</v>
       </c>
-      <c r="E180" s="4"/>
-      <c r="F180" s="3"/>
-      <c r="G180" s="3"/>
-      <c r="H180" s="4">
+      <c r="E180" s="3"/>
+      <c r="F180" s="2"/>
+      <c r="G180" s="2"/>
+      <c r="H180" s="3">
         <v>23230</v>
       </c>
-      <c r="I180" s="3"/>
-      <c r="J180" s="3"/>
-      <c r="L180" s="4">
+      <c r="I180" s="2"/>
+      <c r="J180" s="2"/>
+      <c r="L180" s="3">
         <v>23230</v>
       </c>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A181" s="3" t="s">
+      <c r="N180" s="3">
+        <v>3816</v>
+      </c>
+      <c r="O180" s="2">
+        <v>20</v>
+      </c>
+      <c r="P180" s="3">
+        <v>24600</v>
+      </c>
+      <c r="Q180" s="3">
+        <v>23230</v>
+      </c>
+      <c r="R180" s="2">
+        <v>2</v>
+      </c>
+      <c r="S180" s="2">
+        <v>17.7</v>
+      </c>
+      <c r="T180" s="2">
+        <v>11.8</v>
+      </c>
+      <c r="U180" s="2">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A181" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B181" t="s">
         <v>14</v>
       </c>
-      <c r="C181" s="3">
+      <c r="C181" s="2">
         <v>30</v>
       </c>
-      <c r="D181" s="3">
+      <c r="D181" s="2">
         <v>30</v>
       </c>
-      <c r="E181" s="4"/>
-      <c r="F181" s="3"/>
-      <c r="G181" s="3"/>
-      <c r="H181" s="4">
+      <c r="E181" s="3"/>
+      <c r="F181" s="2"/>
+      <c r="G181" s="2"/>
+      <c r="H181" s="3">
         <v>27295</v>
       </c>
-      <c r="I181" s="3"/>
-      <c r="J181" s="3"/>
-      <c r="L181" s="4">
+      <c r="I181" s="2"/>
+      <c r="J181" s="2"/>
+      <c r="L181" s="3">
         <v>27295</v>
       </c>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A182" s="3" t="s">
+      <c r="N181" s="3">
+        <v>4752</v>
+      </c>
+      <c r="O181" s="2">
         <v>25</v>
       </c>
+      <c r="P181" s="3">
+        <v>29400</v>
+      </c>
+      <c r="Q181" s="3">
+        <v>27295</v>
+      </c>
+      <c r="R181" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="S181" s="2">
+        <v>19</v>
+      </c>
+      <c r="T181" s="2">
+        <v>11.7</v>
+      </c>
+      <c r="U181" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A182" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="B182" t="s">
         <v>14</v>
       </c>
-      <c r="C182" s="3">
+      <c r="C182" s="2">
         <v>36</v>
       </c>
-      <c r="D182" s="3">
+      <c r="D182" s="2">
         <v>36</v>
       </c>
-      <c r="E182" s="4"/>
-      <c r="F182" s="3"/>
-      <c r="G182" s="3"/>
-      <c r="H182" s="4">
+      <c r="E182" s="3"/>
+      <c r="F182" s="2"/>
+      <c r="G182" s="2"/>
+      <c r="H182" s="3">
         <v>29925</v>
       </c>
-      <c r="I182" s="3"/>
-      <c r="J182" s="3"/>
-      <c r="L182" s="4">
+      <c r="I182" s="2"/>
+      <c r="J182" s="2"/>
+      <c r="L182" s="3">
         <v>29925</v>
       </c>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A183" s="3" t="s">
+      <c r="N182" s="3">
+        <v>4992</v>
+      </c>
+      <c r="O182" s="2">
+        <v>25</v>
+      </c>
+      <c r="P182" s="3">
+        <v>32000</v>
+      </c>
+      <c r="Q182" s="3">
+        <v>29925</v>
+      </c>
+      <c r="R182" s="2">
+        <v>3</v>
+      </c>
+      <c r="S182" s="2">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="T182" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="U182" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="183" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A183" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B183" t="s">
         <v>14</v>
       </c>
-      <c r="C183" s="3">
+      <c r="C183" s="2">
         <v>48</v>
       </c>
-      <c r="D183" s="3">
+      <c r="D183" s="2">
         <v>48</v>
       </c>
-      <c r="E183" s="4"/>
-      <c r="F183" s="3"/>
-      <c r="G183" s="3"/>
-      <c r="H183" s="4">
+      <c r="E183" s="3"/>
+      <c r="F183" s="2"/>
+      <c r="G183" s="2"/>
+      <c r="H183" s="3">
         <v>39480</v>
       </c>
-      <c r="I183" s="3"/>
-      <c r="J183" s="3"/>
-      <c r="L183" s="4">
+      <c r="I183" s="2"/>
+      <c r="J183" s="2"/>
+      <c r="L183" s="3">
         <v>39480</v>
+      </c>
+      <c r="N183" s="3">
+        <v>6000</v>
+      </c>
+      <c r="O183" s="2">
+        <v>30</v>
+      </c>
+      <c r="P183" s="3">
+        <v>41000</v>
+      </c>
+      <c r="Q183" s="3">
+        <v>39480</v>
+      </c>
+      <c r="R183" s="2">
+        <v>3.79</v>
+      </c>
+      <c r="S183" s="2">
+        <v>17</v>
+      </c>
+      <c r="T183" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="U183" s="2">
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>
@@ -6430,12 +6633,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">

--- a/backend/assets/data/fujitsu_capacities_calculated.xlsx
+++ b/backend/assets/data/fujitsu_capacities_calculated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pardigmpartners-my.sharepoint.com/personal/alex_paradigm-esco_com/Documents/data_operations/ashp_calculator/backend/assets/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{D420F103-AC1D-4B35-A441-D57FBF080E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C634B1E9-07E3-4BC0-A3B4-EFD420E9B3DF}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{D420F103-AC1D-4B35-A441-D57FBF080E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B6CDCDF-D5C2-4300-AB3A-19C2C6E6562C}"/>
   <bookViews>
-    <workbookView xWindow="5690" yWindow="2620" windowWidth="30890" windowHeight="17110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42270" yWindow="1540" windowWidth="33310" windowHeight="17110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="indoor_combinations" sheetId="2" r:id="rId1"/>
@@ -210,10 +210,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -586,6 +582,27 @@
       <c r="L2">
         <v>16335</v>
       </c>
+      <c r="N2" s="1">
+        <v>3720</v>
+      </c>
+      <c r="O2" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q2">
+        <v>16335</v>
+      </c>
+      <c r="R2" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S2" s="2">
+        <v>22</v>
+      </c>
+      <c r="T2" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U2" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -612,6 +629,27 @@
       <c r="L3">
         <v>17750</v>
       </c>
+      <c r="N3" s="1">
+        <v>3720</v>
+      </c>
+      <c r="O3" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q3">
+        <v>17750</v>
+      </c>
+      <c r="R3" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S3" s="2">
+        <v>22</v>
+      </c>
+      <c r="T3" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U3" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -638,6 +676,27 @@
       <c r="L4">
         <v>19725</v>
       </c>
+      <c r="N4" s="1">
+        <v>3720</v>
+      </c>
+      <c r="O4" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q4">
+        <v>19725</v>
+      </c>
+      <c r="R4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S4" s="2">
+        <v>22</v>
+      </c>
+      <c r="T4" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U4" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
@@ -664,6 +723,27 @@
       <c r="L5">
         <v>19725</v>
       </c>
+      <c r="N5" s="1">
+        <v>3720</v>
+      </c>
+      <c r="O5" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q5">
+        <v>19725</v>
+      </c>
+      <c r="R5" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S5" s="2">
+        <v>22</v>
+      </c>
+      <c r="T5" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U5" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
@@ -690,6 +770,27 @@
       <c r="L6">
         <v>19725</v>
       </c>
+      <c r="N6" s="1">
+        <v>3720</v>
+      </c>
+      <c r="O6" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q6">
+        <v>19725</v>
+      </c>
+      <c r="R6" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S6" s="2">
+        <v>22</v>
+      </c>
+      <c r="T6" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U6" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -716,6 +817,27 @@
       <c r="L7">
         <v>19725</v>
       </c>
+      <c r="N7" s="1">
+        <v>3720</v>
+      </c>
+      <c r="O7" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q7">
+        <v>19725</v>
+      </c>
+      <c r="R7" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S7" s="2">
+        <v>22</v>
+      </c>
+      <c r="T7" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U7" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -742,6 +864,27 @@
       <c r="L8">
         <v>19725</v>
       </c>
+      <c r="N8" s="1">
+        <v>3720</v>
+      </c>
+      <c r="O8" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q8">
+        <v>19725</v>
+      </c>
+      <c r="R8" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S8" s="2">
+        <v>22</v>
+      </c>
+      <c r="T8" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U8" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
@@ -768,6 +911,27 @@
       <c r="L9">
         <v>19725</v>
       </c>
+      <c r="N9" s="1">
+        <v>3720</v>
+      </c>
+      <c r="O9" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q9">
+        <v>19725</v>
+      </c>
+      <c r="R9" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S9" s="2">
+        <v>22</v>
+      </c>
+      <c r="T9" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U9" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
@@ -794,6 +958,27 @@
       <c r="L10">
         <v>16335</v>
       </c>
+      <c r="N10" s="1">
+        <v>3720</v>
+      </c>
+      <c r="O10" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q10">
+        <v>16335</v>
+      </c>
+      <c r="R10" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S10" s="2">
+        <v>22</v>
+      </c>
+      <c r="T10" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U10" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
@@ -820,6 +1005,27 @@
       <c r="L11">
         <v>17750</v>
       </c>
+      <c r="N11" s="1">
+        <v>3720</v>
+      </c>
+      <c r="O11" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q11">
+        <v>17750</v>
+      </c>
+      <c r="R11" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S11" s="2">
+        <v>22</v>
+      </c>
+      <c r="T11" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U11" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -846,6 +1052,27 @@
       <c r="L12">
         <v>19725</v>
       </c>
+      <c r="N12" s="1">
+        <v>3720</v>
+      </c>
+      <c r="O12" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q12">
+        <v>19725</v>
+      </c>
+      <c r="R12" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S12" s="2">
+        <v>22</v>
+      </c>
+      <c r="T12" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U12" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
@@ -872,6 +1099,27 @@
       <c r="L13">
         <v>19725</v>
       </c>
+      <c r="N13" s="1">
+        <v>3720</v>
+      </c>
+      <c r="O13" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q13">
+        <v>19725</v>
+      </c>
+      <c r="R13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S13" s="2">
+        <v>22</v>
+      </c>
+      <c r="T13" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U13" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
@@ -898,6 +1146,27 @@
       <c r="L14">
         <v>19725</v>
       </c>
+      <c r="N14" s="1">
+        <v>3720</v>
+      </c>
+      <c r="O14" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q14">
+        <v>19725</v>
+      </c>
+      <c r="R14" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S14" s="2">
+        <v>22</v>
+      </c>
+      <c r="T14" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U14" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
@@ -923,6 +1192,27 @@
       </c>
       <c r="L15">
         <v>19725</v>
+      </c>
+      <c r="N15" s="1">
+        <v>3720</v>
+      </c>
+      <c r="O15" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q15">
+        <v>19725</v>
+      </c>
+      <c r="R15" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="S15" s="2">
+        <v>22</v>
+      </c>
+      <c r="T15" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U15" s="2">
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
@@ -953,9 +1243,29 @@
         <v>16115</v>
       </c>
       <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N16" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O16" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>16115</v>
+      </c>
+      <c r="R16" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S16" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T16" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U16" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -983,9 +1293,29 @@
         <v>17785</v>
       </c>
       <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N17" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O17" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>17785</v>
+      </c>
+      <c r="R17" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S17" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T17" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U17" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -1013,9 +1343,29 @@
         <v>19165</v>
       </c>
       <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N18" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O18" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>19165</v>
+      </c>
+      <c r="R18" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S18" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T18" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U18" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -1043,9 +1393,29 @@
         <v>21630</v>
       </c>
       <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N19" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O19" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>21630</v>
+      </c>
+      <c r="R19" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S19" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T19" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U19" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -1073,9 +1443,29 @@
         <v>22505</v>
       </c>
       <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N20" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O20" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R20" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S20" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T20" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U20" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -1103,9 +1493,29 @@
         <v>18440</v>
       </c>
       <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N21" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O21" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>18440</v>
+      </c>
+      <c r="R21" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S21" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T21" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U21" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -1133,9 +1543,29 @@
         <v>20690</v>
       </c>
       <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N22" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O22" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>20690</v>
+      </c>
+      <c r="R22" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S22" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T22" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U22" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -1163,9 +1593,29 @@
         <v>22505</v>
       </c>
       <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N23" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O23" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R23" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S23" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T23" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U23" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1193,9 +1643,29 @@
         <v>22505</v>
       </c>
       <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N24" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O24" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R24" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S24" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T24" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U24" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -1223,9 +1693,29 @@
         <v>22505</v>
       </c>
       <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N25" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O25" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R25" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S25" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T25" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U25" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -1253,9 +1743,29 @@
         <v>22505</v>
       </c>
       <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N26" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O26" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R26" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S26" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T26" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U26" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -1283,9 +1793,29 @@
         <v>22505</v>
       </c>
       <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N27" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O27" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R27" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S27" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T27" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U27" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -1313,9 +1843,29 @@
         <v>22505</v>
       </c>
       <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N28" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O28" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R28" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S28" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T28" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U28" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -1348,9 +1898,29 @@
         <v>20690</v>
       </c>
       <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N29" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O29" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>20690</v>
+      </c>
+      <c r="R29" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S29" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T29" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U29" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>15</v>
       </c>
@@ -1383,9 +1953,29 @@
         <v>22505</v>
       </c>
       <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N30" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O30" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R30" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S30" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T30" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U30" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -1418,9 +2008,29 @@
         <v>22505</v>
       </c>
       <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N31" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O31" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R31" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S31" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T31" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U31" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -1453,9 +2063,29 @@
         <v>22505</v>
       </c>
       <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N32" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O32" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R32" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S32" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T32" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U32" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -1488,9 +2118,29 @@
         <v>22505</v>
       </c>
       <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N33" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O33" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R33" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S33" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T33" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U33" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -1523,9 +2173,29 @@
         <v>22505</v>
       </c>
       <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N34" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O34" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R34" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S34" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T34" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U34" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -1558,9 +2228,29 @@
         <v>22505</v>
       </c>
       <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N35" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O35" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R35" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S35" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T35" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U35" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -1593,9 +2283,29 @@
         <v>22505</v>
       </c>
       <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N36" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O36" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R36" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S36" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T36" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U36" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -1628,9 +2338,29 @@
         <v>22505</v>
       </c>
       <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N37" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O37" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R37" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S37" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T37" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U37" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -1663,9 +2393,29 @@
         <v>22505</v>
       </c>
       <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N38" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O38" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R38" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S38" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T38" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U38" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -1692,8 +2442,29 @@
       <c r="L39" s="1">
         <v>16115</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N39" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O39" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>16115</v>
+      </c>
+      <c r="R39" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S39" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T39" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U39" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -1720,8 +2491,29 @@
       <c r="L40" s="1">
         <v>17785</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N40" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O40" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>17785</v>
+      </c>
+      <c r="R40" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S40" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T40" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U40" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -1748,8 +2540,29 @@
       <c r="L41" s="1">
         <v>19165</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N41" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O41" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>19165</v>
+      </c>
+      <c r="R41" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S41" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T41" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U41" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>15</v>
       </c>
@@ -1776,8 +2589,29 @@
       <c r="L42" s="1">
         <v>22505</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N42" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O42" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R42" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S42" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T42" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U42" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>15</v>
       </c>
@@ -1804,8 +2638,29 @@
       <c r="L43" s="1">
         <v>18440</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N43" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O43" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>18440</v>
+      </c>
+      <c r="R43" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S43" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T43" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U43" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -1832,8 +2687,29 @@
       <c r="L44" s="1">
         <v>20690</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N44" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O44" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>20690</v>
+      </c>
+      <c r="R44" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S44" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T44" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U44" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -1860,8 +2736,29 @@
       <c r="L45" s="1">
         <v>22505</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N45" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O45" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R45" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S45" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T45" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U45" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -1888,8 +2785,29 @@
       <c r="L46" s="1">
         <v>22505</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N46" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O46" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R46" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S46" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T46" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U46" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -1916,8 +2834,29 @@
       <c r="L47" s="1">
         <v>22505</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N47" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O47" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R47" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S47" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T47" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U47" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -1950,8 +2889,29 @@
       <c r="L48" s="1">
         <v>20690</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N48" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O48" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>20690</v>
+      </c>
+      <c r="R48" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S48" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T48" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U48" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -1984,8 +2944,29 @@
       <c r="L49" s="1">
         <v>22505</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N49" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O49" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q49" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R49" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S49" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T49" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U49" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>15</v>
       </c>
@@ -2018,8 +2999,29 @@
       <c r="L50" s="1">
         <v>22505</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N50" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O50" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R50" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S50" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T50" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U50" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -2052,8 +3054,29 @@
       <c r="L51" s="1">
         <v>22505</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N51" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O51" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q51" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R51" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S51" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T51" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U51" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -2086,8 +3109,29 @@
       <c r="L52" s="1">
         <v>22505</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N52" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O52" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q52" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R52" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S52" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T52" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U52" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -2120,8 +3164,29 @@
       <c r="L53" s="1">
         <v>22505</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N53" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O53" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R53" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S53" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T53" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U53" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>15</v>
       </c>
@@ -2154,8 +3219,29 @@
       <c r="L54" s="1">
         <v>22505</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N54" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O54" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q54" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R54" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S54" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T54" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U54" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>15</v>
       </c>
@@ -2188,8 +3274,29 @@
       <c r="L55" s="1">
         <v>22505</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N55" s="1">
+        <v>4656</v>
+      </c>
+      <c r="O55" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>22505</v>
+      </c>
+      <c r="R55" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="S55" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T55" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="U55" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>16</v>
       </c>
@@ -2214,8 +3321,29 @@
       <c r="L56" s="1">
         <v>27260</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N56" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O56" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>27260</v>
+      </c>
+      <c r="R56" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S56" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T56" s="2">
+        <v>13</v>
+      </c>
+      <c r="U56" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>16</v>
       </c>
@@ -2240,8 +3368,29 @@
       <c r="L57" s="1">
         <v>28560</v>
       </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N57" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O57" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>28560</v>
+      </c>
+      <c r="R57" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S57" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T57" s="2">
+        <v>13</v>
+      </c>
+      <c r="U57" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>16</v>
       </c>
@@ -2266,8 +3415,29 @@
       <c r="L58" s="1">
         <v>26610</v>
       </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N58" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O58" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>26610</v>
+      </c>
+      <c r="R58" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S58" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T58" s="2">
+        <v>13</v>
+      </c>
+      <c r="U58" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>16</v>
       </c>
@@ -2292,8 +3462,29 @@
       <c r="L59" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N59" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O59" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q59" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R59" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S59" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T59" s="2">
+        <v>13</v>
+      </c>
+      <c r="U59" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>16</v>
       </c>
@@ -2318,8 +3509,29 @@
       <c r="L60" s="1">
         <v>28560</v>
       </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N60" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O60" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>28560</v>
+      </c>
+      <c r="R60" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S60" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T60" s="2">
+        <v>13</v>
+      </c>
+      <c r="U60" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>16</v>
       </c>
@@ -2344,8 +3556,29 @@
       <c r="L61" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N61" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O61" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R61" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S61" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T61" s="2">
+        <v>13</v>
+      </c>
+      <c r="U61" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>16</v>
       </c>
@@ -2370,8 +3603,29 @@
       <c r="L62" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N62" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O62" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R62" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S62" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T62" s="2">
+        <v>13</v>
+      </c>
+      <c r="U62" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>16</v>
       </c>
@@ -2396,8 +3650,29 @@
       <c r="L63" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N63" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O63" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R63" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S63" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T63" s="2">
+        <v>13</v>
+      </c>
+      <c r="U63" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>16</v>
       </c>
@@ -2428,8 +3703,29 @@
       <c r="L64" s="1">
         <v>24010</v>
       </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N64" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O64" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>24010</v>
+      </c>
+      <c r="R64" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S64" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T64" s="2">
+        <v>13</v>
+      </c>
+      <c r="U64" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>16</v>
       </c>
@@ -2460,8 +3756,29 @@
       <c r="L65" s="1">
         <v>25960</v>
       </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N65" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O65" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>25960</v>
+      </c>
+      <c r="R65" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S65" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T65" s="2">
+        <v>13</v>
+      </c>
+      <c r="U65" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>16</v>
       </c>
@@ -2492,8 +3809,29 @@
       <c r="L66" s="1">
         <v>27910</v>
       </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N66" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O66" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q66" s="1">
+        <v>27910</v>
+      </c>
+      <c r="R66" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S66" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T66" s="2">
+        <v>13</v>
+      </c>
+      <c r="U66" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>16</v>
       </c>
@@ -2524,8 +3862,29 @@
       <c r="L67" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N67" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O67" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q67" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R67" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S67" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T67" s="2">
+        <v>13</v>
+      </c>
+      <c r="U67" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>16</v>
       </c>
@@ -2556,8 +3915,29 @@
       <c r="L68" s="1">
         <v>23360</v>
       </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N68" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O68" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>23360</v>
+      </c>
+      <c r="R68" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S68" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T68" s="2">
+        <v>13</v>
+      </c>
+      <c r="U68" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>16</v>
       </c>
@@ -2588,8 +3968,29 @@
       <c r="L69" s="1">
         <v>25310</v>
       </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N69" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O69" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q69" s="1">
+        <v>25310</v>
+      </c>
+      <c r="R69" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S69" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T69" s="2">
+        <v>13</v>
+      </c>
+      <c r="U69" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>16</v>
       </c>
@@ -2620,8 +4021,29 @@
       <c r="L70" s="1">
         <v>27260</v>
       </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N70" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O70" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q70" s="1">
+        <v>27260</v>
+      </c>
+      <c r="R70" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S70" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T70" s="2">
+        <v>13</v>
+      </c>
+      <c r="U70" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>16</v>
       </c>
@@ -2652,8 +4074,29 @@
       <c r="L71" s="1">
         <v>29260</v>
       </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N71" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O71" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q71" s="1">
+        <v>29260</v>
+      </c>
+      <c r="R71" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S71" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T71" s="2">
+        <v>13</v>
+      </c>
+      <c r="U71" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>16</v>
       </c>
@@ -2684,8 +4127,29 @@
       <c r="L72" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N72" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O72" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q72" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R72" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S72" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T72" s="2">
+        <v>13</v>
+      </c>
+      <c r="U72" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>16</v>
       </c>
@@ -2716,8 +4180,29 @@
       <c r="L73" s="1">
         <v>27260</v>
       </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N73" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O73" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q73" s="1">
+        <v>27260</v>
+      </c>
+      <c r="R73" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S73" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T73" s="2">
+        <v>13</v>
+      </c>
+      <c r="U73" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>16</v>
       </c>
@@ -2748,8 +4233,29 @@
       <c r="L74" s="1">
         <v>29260</v>
       </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N74" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O74" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q74" s="1">
+        <v>29260</v>
+      </c>
+      <c r="R74" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S74" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T74" s="2">
+        <v>13</v>
+      </c>
+      <c r="U74" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>16</v>
       </c>
@@ -2780,8 +4286,29 @@
       <c r="L75" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N75" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O75" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q75" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R75" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S75" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T75" s="2">
+        <v>13</v>
+      </c>
+      <c r="U75" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>16</v>
       </c>
@@ -2812,8 +4339,29 @@
       <c r="L76" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N76" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O76" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q76" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R76" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S76" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T76" s="2">
+        <v>13</v>
+      </c>
+      <c r="U76" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>16</v>
       </c>
@@ -2844,8 +4392,29 @@
       <c r="L77" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N77" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O77" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q77" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R77" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S77" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T77" s="2">
+        <v>13</v>
+      </c>
+      <c r="U77" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>16</v>
       </c>
@@ -2876,8 +4445,29 @@
       <c r="L78" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N78" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O78" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q78" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R78" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S78" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T78" s="2">
+        <v>13</v>
+      </c>
+      <c r="U78" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>16</v>
       </c>
@@ -2908,8 +4498,29 @@
       <c r="L79" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N79" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O79" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q79" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R79" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S79" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T79" s="2">
+        <v>13</v>
+      </c>
+      <c r="U79" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>16</v>
       </c>
@@ -2940,8 +4551,29 @@
       <c r="L80" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N80" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O80" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q80" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R80" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S80" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T80" s="2">
+        <v>13</v>
+      </c>
+      <c r="U80" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>16</v>
       </c>
@@ -2972,8 +4604,29 @@
       <c r="L81" s="1">
         <v>24660</v>
       </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N81" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O81" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q81" s="1">
+        <v>24660</v>
+      </c>
+      <c r="R81" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S81" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T81" s="2">
+        <v>13</v>
+      </c>
+      <c r="U81" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>16</v>
       </c>
@@ -3004,8 +4657,29 @@
       <c r="L82" s="1">
         <v>26610</v>
       </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N82" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O82" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q82" s="1">
+        <v>26610</v>
+      </c>
+      <c r="R82" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S82" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T82" s="2">
+        <v>13</v>
+      </c>
+      <c r="U82" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>16</v>
       </c>
@@ -3036,8 +4710,29 @@
       <c r="L83" s="1">
         <v>28560</v>
       </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N83" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O83" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q83" s="1">
+        <v>28560</v>
+      </c>
+      <c r="R83" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S83" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T83" s="2">
+        <v>13</v>
+      </c>
+      <c r="U83" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>16</v>
       </c>
@@ -3068,8 +4763,29 @@
       <c r="L84" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N84" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O84" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q84" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R84" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S84" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T84" s="2">
+        <v>13</v>
+      </c>
+      <c r="U84" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>16</v>
       </c>
@@ -3100,8 +4816,29 @@
       <c r="L85" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N85" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O85" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q85" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R85" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S85" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T85" s="2">
+        <v>13</v>
+      </c>
+      <c r="U85" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>16</v>
       </c>
@@ -3132,8 +4869,29 @@
       <c r="L86" s="1">
         <v>28560</v>
       </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N86" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O86" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q86" s="1">
+        <v>28560</v>
+      </c>
+      <c r="R86" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S86" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T86" s="2">
+        <v>13</v>
+      </c>
+      <c r="U86" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>16</v>
       </c>
@@ -3164,8 +4922,29 @@
       <c r="L87" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N87" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O87" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q87" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R87" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S87" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T87" s="2">
+        <v>13</v>
+      </c>
+      <c r="U87" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>16</v>
       </c>
@@ -3196,8 +4975,29 @@
       <c r="L88" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N88" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O88" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q88" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R88" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S88" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T88" s="2">
+        <v>13</v>
+      </c>
+      <c r="U88" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>16</v>
       </c>
@@ -3228,8 +5028,29 @@
       <c r="L89" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N89" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O89" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q89" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R89" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S89" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T89" s="2">
+        <v>13</v>
+      </c>
+      <c r="U89" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>16</v>
       </c>
@@ -3260,8 +5081,29 @@
       <c r="L90" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N90" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O90" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q90" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R90" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S90" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T90" s="2">
+        <v>13</v>
+      </c>
+      <c r="U90" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>16</v>
       </c>
@@ -3292,8 +5134,29 @@
       <c r="L91" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N91" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O91" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q91" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R91" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S91" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T91" s="2">
+        <v>13</v>
+      </c>
+      <c r="U91" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>16</v>
       </c>
@@ -3324,8 +5187,29 @@
       <c r="L92" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N92" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O92" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q92" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R92" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S92" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T92" s="2">
+        <v>13</v>
+      </c>
+      <c r="U92" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>16</v>
       </c>
@@ -3356,8 +5240,29 @@
       <c r="L93" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N93" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O93" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q93" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R93" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S93" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T93" s="2">
+        <v>13</v>
+      </c>
+      <c r="U93" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>16</v>
       </c>
@@ -3388,8 +5293,29 @@
       <c r="L94" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N94" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O94" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q94" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R94" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S94" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T94" s="2">
+        <v>13</v>
+      </c>
+      <c r="U94" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>16</v>
       </c>
@@ -3420,8 +5346,29 @@
       <c r="L95" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N95" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O95" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q95" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R95" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S95" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T95" s="2">
+        <v>13</v>
+      </c>
+      <c r="U95" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>16</v>
       </c>
@@ -3452,8 +5399,29 @@
       <c r="L96" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N96" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O96" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q96" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R96" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S96" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T96" s="2">
+        <v>13</v>
+      </c>
+      <c r="U96" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>16</v>
       </c>
@@ -3484,8 +5452,29 @@
       <c r="L97" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N97" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O97" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q97" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R97" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S97" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T97" s="2">
+        <v>13</v>
+      </c>
+      <c r="U97" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>16</v>
       </c>
@@ -3516,8 +5505,29 @@
       <c r="L98" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N98" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O98" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q98" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R98" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S98" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T98" s="2">
+        <v>13</v>
+      </c>
+      <c r="U98" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>16</v>
       </c>
@@ -3554,8 +5564,29 @@
       <c r="L99" s="1">
         <v>25310</v>
       </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N99" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O99" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q99" s="1">
+        <v>25310</v>
+      </c>
+      <c r="R99" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S99" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T99" s="2">
+        <v>13</v>
+      </c>
+      <c r="U99" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>16</v>
       </c>
@@ -3592,8 +5623,29 @@
       <c r="L100" s="1">
         <v>26610</v>
       </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N100" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O100" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q100" s="1">
+        <v>26610</v>
+      </c>
+      <c r="R100" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S100" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T100" s="2">
+        <v>13</v>
+      </c>
+      <c r="U100" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>16</v>
       </c>
@@ -3630,8 +5682,29 @@
       <c r="L101" s="1">
         <v>28560</v>
       </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N101" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O101" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q101" s="1">
+        <v>28560</v>
+      </c>
+      <c r="R101" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S101" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T101" s="2">
+        <v>13</v>
+      </c>
+      <c r="U101" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -3668,8 +5741,29 @@
       <c r="L102" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N102" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O102" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q102" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R102" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S102" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T102" s="2">
+        <v>13</v>
+      </c>
+      <c r="U102" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -3706,8 +5800,29 @@
       <c r="L103" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N103" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O103" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q103" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R103" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S103" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T103" s="2">
+        <v>13</v>
+      </c>
+      <c r="U103" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -3744,8 +5859,29 @@
       <c r="L104" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N104" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O104" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q104" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R104" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S104" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T104" s="2">
+        <v>13</v>
+      </c>
+      <c r="U104" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>16</v>
       </c>
@@ -3782,8 +5918,29 @@
       <c r="L105" s="1">
         <v>27910</v>
       </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N105" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O105" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q105" s="1">
+        <v>27910</v>
+      </c>
+      <c r="R105" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S105" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T105" s="2">
+        <v>13</v>
+      </c>
+      <c r="U105" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>16</v>
       </c>
@@ -3820,8 +5977,29 @@
       <c r="L106" s="1">
         <v>29880</v>
       </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N106" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O106" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q106" s="1">
+        <v>29880</v>
+      </c>
+      <c r="R106" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S106" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T106" s="2">
+        <v>13</v>
+      </c>
+      <c r="U106" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>16</v>
       </c>
@@ -3858,8 +6036,29 @@
       <c r="L107" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N107" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O107" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q107" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R107" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S107" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T107" s="2">
+        <v>13</v>
+      </c>
+      <c r="U107" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>16</v>
       </c>
@@ -3896,8 +6095,29 @@
       <c r="L108" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N108" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O108" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q108" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R108" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S108" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T108" s="2">
+        <v>13</v>
+      </c>
+      <c r="U108" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>16</v>
       </c>
@@ -3934,8 +6154,29 @@
       <c r="L109" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N109" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O109" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q109" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R109" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S109" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T109" s="2">
+        <v>13</v>
+      </c>
+      <c r="U109" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>16</v>
       </c>
@@ -3972,8 +6213,29 @@
       <c r="L110" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N110" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O110" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q110" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R110" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S110" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T110" s="2">
+        <v>13</v>
+      </c>
+      <c r="U110" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>16</v>
       </c>
@@ -4010,8 +6272,29 @@
       <c r="L111" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N111" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O111" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q111" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R111" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S111" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T111" s="2">
+        <v>13</v>
+      </c>
+      <c r="U111" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>16</v>
       </c>
@@ -4048,8 +6331,29 @@
       <c r="L112" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N112" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O112" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q112" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R112" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S112" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T112" s="2">
+        <v>13</v>
+      </c>
+      <c r="U112" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>16</v>
       </c>
@@ -4086,8 +6390,29 @@
       <c r="L113" s="1">
         <v>29260</v>
       </c>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N113" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O113" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q113" s="1">
+        <v>29260</v>
+      </c>
+      <c r="R113" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S113" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T113" s="2">
+        <v>13</v>
+      </c>
+      <c r="U113" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>16</v>
       </c>
@@ -4124,8 +6449,29 @@
       <c r="L114" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N114" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O114" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q114" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R114" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S114" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T114" s="2">
+        <v>13</v>
+      </c>
+      <c r="U114" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>16</v>
       </c>
@@ -4162,8 +6508,29 @@
       <c r="L115" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N115" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O115" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q115" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R115" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S115" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T115" s="2">
+        <v>13</v>
+      </c>
+      <c r="U115" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>16</v>
       </c>
@@ -4200,8 +6567,29 @@
       <c r="L116" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N116" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O116" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q116" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R116" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S116" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T116" s="2">
+        <v>13</v>
+      </c>
+      <c r="U116" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>16</v>
       </c>
@@ -4238,8 +6626,29 @@
       <c r="L117" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N117" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O117" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q117" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R117" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S117" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T117" s="2">
+        <v>13</v>
+      </c>
+      <c r="U117" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>16</v>
       </c>
@@ -4276,8 +6685,29 @@
       <c r="L118" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N118" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O118" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q118" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R118" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S118" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T118" s="2">
+        <v>13</v>
+      </c>
+      <c r="U118" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>16</v>
       </c>
@@ -4314,8 +6744,29 @@
       <c r="L119" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N119" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O119" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q119" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R119" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S119" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T119" s="2">
+        <v>13</v>
+      </c>
+      <c r="U119" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>16</v>
       </c>
@@ -4352,8 +6803,29 @@
       <c r="L120" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N120" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O120" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q120" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R120" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S120" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T120" s="2">
+        <v>13</v>
+      </c>
+      <c r="U120" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>16</v>
       </c>
@@ -4390,8 +6862,29 @@
       <c r="L121" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N121" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O121" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q121" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R121" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S121" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T121" s="2">
+        <v>13</v>
+      </c>
+      <c r="U121" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>16</v>
       </c>
@@ -4428,8 +6921,29 @@
       <c r="L122" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N122" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O122" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q122" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R122" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S122" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T122" s="2">
+        <v>13</v>
+      </c>
+      <c r="U122" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>16</v>
       </c>
@@ -4466,8 +6980,29 @@
       <c r="L123" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N123" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O123" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q123" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R123" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S123" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T123" s="2">
+        <v>13</v>
+      </c>
+      <c r="U123" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>16</v>
       </c>
@@ -4504,8 +7039,29 @@
       <c r="L124" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N124" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O124" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q124" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R124" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S124" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T124" s="2">
+        <v>13</v>
+      </c>
+      <c r="U124" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>16</v>
       </c>
@@ -4542,8 +7098,29 @@
       <c r="L125" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N125" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O125" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q125" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R125" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S125" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T125" s="2">
+        <v>13</v>
+      </c>
+      <c r="U125" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>16</v>
       </c>
@@ -4580,8 +7157,29 @@
       <c r="L126" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N126" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O126" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q126" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R126" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S126" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T126" s="2">
+        <v>13</v>
+      </c>
+      <c r="U126" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>16</v>
       </c>
@@ -4618,8 +7216,29 @@
       <c r="L127" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N127" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O127" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q127" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R127" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S127" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T127" s="2">
+        <v>13</v>
+      </c>
+      <c r="U127" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>16</v>
       </c>
@@ -4656,8 +7275,29 @@
       <c r="L128" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N128" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O128" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q128" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R128" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S128" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T128" s="2">
+        <v>13</v>
+      </c>
+      <c r="U128" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>16</v>
       </c>
@@ -4694,8 +7334,29 @@
       <c r="L129" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N129" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O129" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q129" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R129" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S129" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T129" s="2">
+        <v>13</v>
+      </c>
+      <c r="U129" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>16</v>
       </c>
@@ -4720,8 +7381,29 @@
       <c r="L130" s="1">
         <v>27260</v>
       </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N130" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O130" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q130" s="1">
+        <v>27260</v>
+      </c>
+      <c r="R130" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S130" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T130" s="2">
+        <v>13</v>
+      </c>
+      <c r="U130" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>16</v>
       </c>
@@ -4746,8 +7428,29 @@
       <c r="L131" s="1">
         <v>28560</v>
       </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N131" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O131" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q131" s="1">
+        <v>28560</v>
+      </c>
+      <c r="R131" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S131" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T131" s="2">
+        <v>13</v>
+      </c>
+      <c r="U131" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>16</v>
       </c>
@@ -4772,8 +7475,29 @@
       <c r="L132" s="1">
         <v>26610</v>
       </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N132" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O132" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q132" s="1">
+        <v>26610</v>
+      </c>
+      <c r="R132" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S132" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T132" s="2">
+        <v>13</v>
+      </c>
+      <c r="U132" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>16</v>
       </c>
@@ -4798,8 +7522,29 @@
       <c r="L133" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N133" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O133" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q133" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R133" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S133" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T133" s="2">
+        <v>13</v>
+      </c>
+      <c r="U133" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>16</v>
       </c>
@@ -4824,8 +7569,29 @@
       <c r="L134" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N134" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O134" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q134" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R134" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S134" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T134" s="2">
+        <v>13</v>
+      </c>
+      <c r="U134" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>16</v>
       </c>
@@ -4850,8 +7616,29 @@
       <c r="L135" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N135" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O135" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q135" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R135" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S135" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T135" s="2">
+        <v>13</v>
+      </c>
+      <c r="U135" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>16</v>
       </c>
@@ -4882,8 +7669,29 @@
       <c r="L136" s="1">
         <v>24010</v>
       </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N136" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O136" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q136" s="1">
+        <v>24010</v>
+      </c>
+      <c r="R136" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S136" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T136" s="2">
+        <v>13</v>
+      </c>
+      <c r="U136" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>16</v>
       </c>
@@ -4914,8 +7722,29 @@
       <c r="L137" s="1">
         <v>27910</v>
       </c>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N137" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O137" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q137" s="1">
+        <v>27910</v>
+      </c>
+      <c r="R137" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S137" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T137" s="2">
+        <v>13</v>
+      </c>
+      <c r="U137" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>16</v>
       </c>
@@ -4946,8 +7775,29 @@
       <c r="L138" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N138" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O138" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q138" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R138" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S138" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T138" s="2">
+        <v>13</v>
+      </c>
+      <c r="U138" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>16</v>
       </c>
@@ -4978,8 +7828,29 @@
       <c r="L139" s="1">
         <v>23360</v>
       </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N139" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O139" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q139" s="1">
+        <v>23360</v>
+      </c>
+      <c r="R139" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S139" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T139" s="2">
+        <v>13</v>
+      </c>
+      <c r="U139" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>16</v>
       </c>
@@ -5010,8 +7881,29 @@
       <c r="L140" s="1">
         <v>25310</v>
       </c>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N140" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O140" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q140" s="1">
+        <v>25310</v>
+      </c>
+      <c r="R140" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S140" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T140" s="2">
+        <v>13</v>
+      </c>
+      <c r="U140" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>16</v>
       </c>
@@ -5042,8 +7934,29 @@
       <c r="L141" s="1">
         <v>29260</v>
       </c>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N141" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O141" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q141" s="1">
+        <v>29260</v>
+      </c>
+      <c r="R141" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S141" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T141" s="2">
+        <v>13</v>
+      </c>
+      <c r="U141" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>16</v>
       </c>
@@ -5074,8 +7987,29 @@
       <c r="L142" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N142" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O142" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q142" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R142" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S142" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T142" s="2">
+        <v>13</v>
+      </c>
+      <c r="U142" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>16</v>
       </c>
@@ -5106,8 +8040,29 @@
       <c r="L143" s="1">
         <v>27260</v>
       </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N143" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O143" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q143" s="1">
+        <v>27260</v>
+      </c>
+      <c r="R143" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S143" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T143" s="2">
+        <v>13</v>
+      </c>
+      <c r="U143" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>16</v>
       </c>
@@ -5138,8 +8093,29 @@
       <c r="L144" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N144" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O144" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q144" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R144" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S144" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T144" s="2">
+        <v>13</v>
+      </c>
+      <c r="U144" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>16</v>
       </c>
@@ -5170,8 +8146,29 @@
       <c r="L145" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N145" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O145" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q145" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R145" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S145" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T145" s="2">
+        <v>13</v>
+      </c>
+      <c r="U145" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>16</v>
       </c>
@@ -5202,8 +8199,29 @@
       <c r="L146" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N146" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O146" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q146" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R146" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S146" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T146" s="2">
+        <v>13</v>
+      </c>
+      <c r="U146" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>16</v>
       </c>
@@ -5234,8 +8252,29 @@
       <c r="L147" s="1">
         <v>24660</v>
       </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N147" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O147" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q147" s="1">
+        <v>24660</v>
+      </c>
+      <c r="R147" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S147" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T147" s="2">
+        <v>13</v>
+      </c>
+      <c r="U147" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>16</v>
       </c>
@@ -5266,8 +8305,29 @@
       <c r="L148" s="1">
         <v>26610</v>
       </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N148" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O148" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q148" s="1">
+        <v>26610</v>
+      </c>
+      <c r="R148" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S148" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T148" s="2">
+        <v>13</v>
+      </c>
+      <c r="U148" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>16</v>
       </c>
@@ -5298,8 +8358,29 @@
       <c r="L149" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N149" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O149" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q149" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R149" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S149" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T149" s="2">
+        <v>13</v>
+      </c>
+      <c r="U149" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>16</v>
       </c>
@@ -5330,8 +8411,29 @@
       <c r="L150" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N150" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O150" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q150" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R150" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S150" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T150" s="2">
+        <v>13</v>
+      </c>
+      <c r="U150" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>16</v>
       </c>
@@ -5362,8 +8464,29 @@
       <c r="L151" s="1">
         <v>28560</v>
       </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N151" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O151" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q151" s="1">
+        <v>28560</v>
+      </c>
+      <c r="R151" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S151" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T151" s="2">
+        <v>13</v>
+      </c>
+      <c r="U151" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>16</v>
       </c>
@@ -5394,8 +8517,29 @@
       <c r="L152" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N152" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O152" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q152" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R152" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S152" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T152" s="2">
+        <v>13</v>
+      </c>
+      <c r="U152" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>16</v>
       </c>
@@ -5426,8 +8570,29 @@
       <c r="L153" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N153" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O153" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q153" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R153" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S153" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T153" s="2">
+        <v>13</v>
+      </c>
+      <c r="U153" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>16</v>
       </c>
@@ -5458,8 +8623,29 @@
       <c r="L154" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N154" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O154" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q154" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R154" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S154" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T154" s="2">
+        <v>13</v>
+      </c>
+      <c r="U154" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>16</v>
       </c>
@@ -5490,8 +8676,29 @@
       <c r="L155" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N155" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O155" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q155" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R155" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S155" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T155" s="2">
+        <v>13</v>
+      </c>
+      <c r="U155" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>16</v>
       </c>
@@ -5522,8 +8729,29 @@
       <c r="L156" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N156" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O156" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q156" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R156" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S156" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T156" s="2">
+        <v>13</v>
+      </c>
+      <c r="U156" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>16</v>
       </c>
@@ -5560,8 +8788,29 @@
       <c r="L157" s="1">
         <v>25310</v>
       </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N157" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O157" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q157" s="1">
+        <v>25310</v>
+      </c>
+      <c r="R157" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S157" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T157" s="2">
+        <v>13</v>
+      </c>
+      <c r="U157" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>16</v>
       </c>
@@ -5598,8 +8847,29 @@
       <c r="L158" s="1">
         <v>26610</v>
       </c>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N158" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O158" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q158" s="1">
+        <v>26610</v>
+      </c>
+      <c r="R158" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S158" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T158" s="2">
+        <v>13</v>
+      </c>
+      <c r="U158" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>16</v>
       </c>
@@ -5636,8 +8906,29 @@
       <c r="L159" s="1">
         <v>28560</v>
       </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N159" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O159" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q159" s="1">
+        <v>28560</v>
+      </c>
+      <c r="R159" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S159" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T159" s="2">
+        <v>13</v>
+      </c>
+      <c r="U159" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>16</v>
       </c>
@@ -5674,8 +8965,29 @@
       <c r="L160" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N160" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O160" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q160" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R160" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S160" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T160" s="2">
+        <v>13</v>
+      </c>
+      <c r="U160" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>16</v>
       </c>
@@ -5712,8 +9024,29 @@
       <c r="L161" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N161" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O161" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q161" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R161" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S161" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T161" s="2">
+        <v>13</v>
+      </c>
+      <c r="U161" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>16</v>
       </c>
@@ -5750,8 +9083,29 @@
       <c r="L162" s="1">
         <v>27910</v>
       </c>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N162" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O162" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q162" s="1">
+        <v>27910</v>
+      </c>
+      <c r="R162" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S162" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T162" s="2">
+        <v>13</v>
+      </c>
+      <c r="U162" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>16</v>
       </c>
@@ -5788,8 +9142,29 @@
       <c r="L163" s="1">
         <v>29880</v>
       </c>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N163" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O163" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q163" s="1">
+        <v>29880</v>
+      </c>
+      <c r="R163" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S163" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T163" s="2">
+        <v>13</v>
+      </c>
+      <c r="U163" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>16</v>
       </c>
@@ -5826,8 +9201,29 @@
       <c r="L164" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N164" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O164" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q164" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R164" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S164" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T164" s="2">
+        <v>13</v>
+      </c>
+      <c r="U164" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>16</v>
       </c>
@@ -5864,8 +9260,29 @@
       <c r="L165" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N165" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O165" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q165" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R165" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S165" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T165" s="2">
+        <v>13</v>
+      </c>
+      <c r="U165" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>16</v>
       </c>
@@ -5902,8 +9319,29 @@
       <c r="L166" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N166" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O166" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q166" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R166" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S166" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T166" s="2">
+        <v>13</v>
+      </c>
+      <c r="U166" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>16</v>
       </c>
@@ -5940,8 +9378,29 @@
       <c r="L167" s="1">
         <v>29260</v>
       </c>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N167" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O167" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q167" s="1">
+        <v>29260</v>
+      </c>
+      <c r="R167" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S167" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T167" s="2">
+        <v>13</v>
+      </c>
+      <c r="U167" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>16</v>
       </c>
@@ -5978,8 +9437,29 @@
       <c r="L168" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N168" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O168" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q168" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R168" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S168" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T168" s="2">
+        <v>13</v>
+      </c>
+      <c r="U168" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>16</v>
       </c>
@@ -6016,8 +9496,29 @@
       <c r="L169" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N169" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O169" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q169" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R169" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S169" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T169" s="2">
+        <v>13</v>
+      </c>
+      <c r="U169" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>16</v>
       </c>
@@ -6054,8 +9555,29 @@
       <c r="L170" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N170" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O170" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q170" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R170" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S170" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T170" s="2">
+        <v>13</v>
+      </c>
+      <c r="U170" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>16</v>
       </c>
@@ -6092,8 +9614,29 @@
       <c r="L171" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N171" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O171" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q171" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R171" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S171" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T171" s="2">
+        <v>13</v>
+      </c>
+      <c r="U171" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>16</v>
       </c>
@@ -6130,8 +9673,29 @@
       <c r="L172" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N172" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O172" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q172" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R172" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S172" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T172" s="2">
+        <v>13</v>
+      </c>
+      <c r="U172" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>16</v>
       </c>
@@ -6168,8 +9732,29 @@
       <c r="L173" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N173" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O173" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q173" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R173" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S173" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T173" s="2">
+        <v>13</v>
+      </c>
+      <c r="U173" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>16</v>
       </c>
@@ -6206,8 +9791,29 @@
       <c r="L174" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N174" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O174" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q174" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R174" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S174" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T174" s="2">
+        <v>13</v>
+      </c>
+      <c r="U174" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>16</v>
       </c>
@@ -6244,8 +9850,29 @@
       <c r="L175" s="1">
         <v>30760</v>
       </c>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N175" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O175" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q175" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R175" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S175" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T175" s="2">
+        <v>13</v>
+      </c>
+      <c r="U175" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>16</v>
       </c>
@@ -6282,6 +9909,27 @@
       <c r="L176" s="1">
         <v>30760</v>
       </c>
+      <c r="N176" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O176" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q176" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R176" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S176" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T176" s="2">
+        <v>13</v>
+      </c>
+      <c r="U176" s="2">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
@@ -6319,6 +9967,27 @@
       </c>
       <c r="L177" s="1">
         <v>30760</v>
+      </c>
+      <c r="N177" s="1">
+        <v>6936</v>
+      </c>
+      <c r="O177" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q177" s="1">
+        <v>30760</v>
+      </c>
+      <c r="R177" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="S177" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T177" s="2">
+        <v>13</v>
+      </c>
+      <c r="U177" s="2">
+        <v>9.5</v>
       </c>
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.35">

--- a/backend/assets/data/fujitsu_capacities_calculated.xlsx
+++ b/backend/assets/data/fujitsu_capacities_calculated.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pardigmpartners-my.sharepoint.com/personal/alex_paradigm-esco_com/Documents/data_operations/ashp_calculator/backend/assets/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{D420F103-AC1D-4B35-A441-D57FBF080E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B6CDCDF-D5C2-4300-AB3A-19C2C6E6562C}"/>
+  <xr:revisionPtr revIDLastSave="277" documentId="13_ncr:1_{D420F103-AC1D-4B35-A441-D57FBF080E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F283166-8CE5-426D-945D-8A1DD982EAAE}"/>
   <bookViews>
     <workbookView xWindow="42270" yWindow="1540" windowWidth="33310" windowHeight="17110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,51 +75,6 @@
     <t>Total Capacity</t>
   </si>
   <si>
-    <t>AOUH18KWAH2</t>
-  </si>
-  <si>
-    <t>Non-ducted</t>
-  </si>
-  <si>
-    <t>Ducted</t>
-  </si>
-  <si>
-    <t>AOUH24KWAH3</t>
-  </si>
-  <si>
-    <t>AOUH36KWAH4</t>
-  </si>
-  <si>
-    <t>Capacity at 70°F Indoor / 0°F Outdoor</t>
-  </si>
-  <si>
-    <t>Indoor Capacity (kBtu/h)</t>
-  </si>
-  <si>
-    <t>Outdoor Temp (°F)</t>
-  </si>
-  <si>
-    <t>Capacity at 70F (Btu/h)</t>
-  </si>
-  <si>
-    <t>AOUH12KUAS1</t>
-  </si>
-  <si>
-    <t>AOUH18KUAS1</t>
-  </si>
-  <si>
-    <t>AOUH24KUAS1</t>
-  </si>
-  <si>
-    <t>AOUH30KUAS1</t>
-  </si>
-  <si>
-    <t>AOUH36KUAS1</t>
-  </si>
-  <si>
-    <t>AOUH48KUAS1</t>
-  </si>
-  <si>
     <t>Op. Watts/Htg</t>
   </si>
   <si>
@@ -143,12 +98,57 @@
   <si>
     <t>HSPF2</t>
   </si>
+  <si>
+    <t>AOUH18KWAH2</t>
+  </si>
+  <si>
+    <t>Non-ducted</t>
+  </si>
+  <si>
+    <t>Ducted</t>
+  </si>
+  <si>
+    <t>AOUH24KWAH3</t>
+  </si>
+  <si>
+    <t>AOUH36KWAH4</t>
+  </si>
+  <si>
+    <t>AOUH12KUAS1</t>
+  </si>
+  <si>
+    <t>AOUH18KUAS1</t>
+  </si>
+  <si>
+    <t>AOUH24KUAS1</t>
+  </si>
+  <si>
+    <t>AOUH30KUAS1</t>
+  </si>
+  <si>
+    <t>AOUH36KUAS1</t>
+  </si>
+  <si>
+    <t>AOUH48KUAS1</t>
+  </si>
+  <si>
+    <t>Capacity at 70°F Indoor / 0°F Outdoor</t>
+  </si>
+  <si>
+    <t>Indoor Capacity (kBtu/h)</t>
+  </si>
+  <si>
+    <t>Outdoor Temp (°F)</t>
+  </si>
+  <si>
+    <t>Capacity at 70F (Btu/h)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -476,26 +476,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4304B4-14C5-40DF-85A6-AED3FDED911B}">
   <dimension ref="A1:U183"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="5.7265625" customWidth="1"/>
-    <col min="8" max="9" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="17.453125" customWidth="1"/>
-    <col min="12" max="12" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.7109375" customWidth="1"/>
+    <col min="8" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="17.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -533,36 +534,36 @@
         <v>11</v>
       </c>
       <c r="N1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="O1" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="P1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="Q1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="R1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="S1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="T1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="U1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C2">
         <v>14</v>
@@ -588,6 +589,9 @@
       <c r="O2" s="1">
         <v>20</v>
       </c>
+      <c r="P2" s="1">
+        <v>18220</v>
+      </c>
       <c r="Q2">
         <v>16335</v>
       </c>
@@ -604,12 +608,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <v>16</v>
@@ -635,6 +639,9 @@
       <c r="O3" s="1">
         <v>20</v>
       </c>
+      <c r="P3" s="1">
+        <v>19800</v>
+      </c>
       <c r="Q3">
         <v>17750</v>
       </c>
@@ -651,12 +658,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C4">
         <v>19</v>
@@ -682,6 +689,9 @@
       <c r="O4" s="1">
         <v>20</v>
       </c>
+      <c r="P4" s="1">
+        <v>22000</v>
+      </c>
       <c r="Q4">
         <v>19725</v>
       </c>
@@ -698,12 +708,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>22</v>
@@ -729,6 +739,9 @@
       <c r="O5" s="1">
         <v>20</v>
       </c>
+      <c r="P5" s="1">
+        <v>22000</v>
+      </c>
       <c r="Q5">
         <v>19725</v>
       </c>
@@ -745,12 +758,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>18</v>
@@ -776,6 +789,9 @@
       <c r="O6" s="1">
         <v>20</v>
       </c>
+      <c r="P6" s="1">
+        <v>22000</v>
+      </c>
       <c r="Q6">
         <v>19725</v>
       </c>
@@ -792,12 +808,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C7">
         <v>21</v>
@@ -823,6 +839,9 @@
       <c r="O7" s="1">
         <v>20</v>
       </c>
+      <c r="P7" s="1">
+        <v>22000</v>
+      </c>
       <c r="Q7">
         <v>19725</v>
       </c>
@@ -839,12 +858,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C8">
         <v>24</v>
@@ -870,6 +889,9 @@
       <c r="O8" s="1">
         <v>20</v>
       </c>
+      <c r="P8" s="1">
+        <v>22000</v>
+      </c>
       <c r="Q8">
         <v>19725</v>
       </c>
@@ -886,12 +908,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C9">
         <v>24</v>
@@ -917,6 +939,9 @@
       <c r="O9" s="1">
         <v>20</v>
       </c>
+      <c r="P9" s="1">
+        <v>22000</v>
+      </c>
       <c r="Q9">
         <v>19725</v>
       </c>
@@ -933,12 +958,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C10">
         <v>14</v>
@@ -964,6 +989,9 @@
       <c r="O10" s="1">
         <v>20</v>
       </c>
+      <c r="P10" s="1">
+        <v>18220</v>
+      </c>
       <c r="Q10">
         <v>16335</v>
       </c>
@@ -980,12 +1008,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C11">
         <v>16</v>
@@ -1011,6 +1039,9 @@
       <c r="O11" s="1">
         <v>20</v>
       </c>
+      <c r="P11" s="1">
+        <v>19800</v>
+      </c>
       <c r="Q11">
         <v>17750</v>
       </c>
@@ -1027,12 +1058,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C12">
         <v>19</v>
@@ -1058,6 +1089,9 @@
       <c r="O12" s="1">
         <v>20</v>
       </c>
+      <c r="P12" s="1">
+        <v>22000</v>
+      </c>
       <c r="Q12">
         <v>19725</v>
       </c>
@@ -1074,12 +1108,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C13">
         <v>18</v>
@@ -1105,6 +1139,9 @@
       <c r="O13" s="1">
         <v>20</v>
       </c>
+      <c r="P13" s="1">
+        <v>22000</v>
+      </c>
       <c r="Q13">
         <v>19725</v>
       </c>
@@ -1121,12 +1158,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>21</v>
@@ -1152,6 +1189,9 @@
       <c r="O14" s="1">
         <v>20</v>
       </c>
+      <c r="P14" s="1">
+        <v>22000</v>
+      </c>
       <c r="Q14">
         <v>19725</v>
       </c>
@@ -1168,12 +1208,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C15">
         <v>24</v>
@@ -1199,6 +1239,9 @@
       <c r="O15" s="1">
         <v>20</v>
       </c>
+      <c r="P15" s="1">
+        <v>22000</v>
+      </c>
       <c r="Q15">
         <v>19725</v>
       </c>
@@ -1215,12 +1258,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C16">
         <v>14</v>
@@ -1249,6 +1292,9 @@
       <c r="O16" s="1">
         <v>25</v>
       </c>
+      <c r="P16" s="1">
+        <v>18050</v>
+      </c>
       <c r="Q16" s="1">
         <v>16115</v>
       </c>
@@ -1265,12 +1311,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:21">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1299,6 +1345,9 @@
       <c r="O17" s="1">
         <v>25</v>
       </c>
+      <c r="P17" s="1">
+        <v>19920</v>
+      </c>
       <c r="Q17" s="1">
         <v>17785</v>
       </c>
@@ -1315,12 +1364,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:21">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C18">
         <v>19</v>
@@ -1349,6 +1398,9 @@
       <c r="O18" s="1">
         <v>25</v>
       </c>
+      <c r="P18" s="1">
+        <v>21460</v>
+      </c>
       <c r="Q18" s="1">
         <v>19165</v>
       </c>
@@ -1365,12 +1417,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>22</v>
@@ -1399,6 +1451,9 @@
       <c r="O19" s="1">
         <v>25</v>
       </c>
+      <c r="P19" s="1">
+        <v>24220</v>
+      </c>
       <c r="Q19" s="1">
         <v>21630</v>
       </c>
@@ -1415,12 +1470,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:21">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C20">
         <v>25</v>
@@ -1449,6 +1504,9 @@
       <c r="O20" s="1">
         <v>25</v>
       </c>
+      <c r="P20" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q20" s="1">
         <v>22505</v>
       </c>
@@ -1465,12 +1523,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:21">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C21">
         <v>18</v>
@@ -1499,6 +1557,9 @@
       <c r="O21" s="1">
         <v>25</v>
       </c>
+      <c r="P21" s="1">
+        <v>20650</v>
+      </c>
       <c r="Q21" s="1">
         <v>18440</v>
       </c>
@@ -1515,12 +1576,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:21">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1549,6 +1610,9 @@
       <c r="O22" s="1">
         <v>25</v>
       </c>
+      <c r="P22" s="1">
+        <v>23170</v>
+      </c>
       <c r="Q22" s="1">
         <v>20690</v>
       </c>
@@ -1565,12 +1629,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C23">
         <v>24</v>
@@ -1599,6 +1663,9 @@
       <c r="O23" s="1">
         <v>25</v>
       </c>
+      <c r="P23" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q23" s="1">
         <v>22505</v>
       </c>
@@ -1615,12 +1682,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:21">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C24">
         <v>27</v>
@@ -1649,6 +1716,9 @@
       <c r="O24" s="1">
         <v>25</v>
       </c>
+      <c r="P24" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q24" s="1">
         <v>22505</v>
       </c>
@@ -1665,12 +1735,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:21">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1699,6 +1769,9 @@
       <c r="O25" s="1">
         <v>25</v>
       </c>
+      <c r="P25" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q25" s="1">
         <v>22505</v>
       </c>
@@ -1715,12 +1788,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:21">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C26">
         <v>27</v>
@@ -1749,6 +1822,9 @@
       <c r="O26" s="1">
         <v>25</v>
       </c>
+      <c r="P26" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q26" s="1">
         <v>22505</v>
       </c>
@@ -1765,12 +1841,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:21">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C27">
         <v>30</v>
@@ -1799,6 +1875,9 @@
       <c r="O27" s="1">
         <v>25</v>
       </c>
+      <c r="P27" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q27" s="1">
         <v>22505</v>
       </c>
@@ -1815,12 +1894,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:21">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C28">
         <v>30</v>
@@ -1849,6 +1928,9 @@
       <c r="O28" s="1">
         <v>25</v>
       </c>
+      <c r="P28" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q28" s="1">
         <v>22505</v>
       </c>
@@ -1865,12 +1947,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:21">
       <c r="A29" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C29">
         <v>21</v>
@@ -1904,6 +1986,9 @@
       <c r="O29" s="1">
         <v>25</v>
       </c>
+      <c r="P29" s="1">
+        <v>23170</v>
+      </c>
       <c r="Q29" s="1">
         <v>20690</v>
       </c>
@@ -1920,12 +2005,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:21">
       <c r="A30" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C30">
         <v>23</v>
@@ -1959,6 +2044,9 @@
       <c r="O30" s="1">
         <v>25</v>
       </c>
+      <c r="P30" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q30" s="1">
         <v>22505</v>
       </c>
@@ -1975,12 +2063,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:21">
       <c r="A31" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C31">
         <v>26</v>
@@ -2014,6 +2102,9 @@
       <c r="O31" s="1">
         <v>25</v>
       </c>
+      <c r="P31" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q31" s="1">
         <v>22505</v>
       </c>
@@ -2030,12 +2121,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:21">
       <c r="A32" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C32">
         <v>29</v>
@@ -2069,6 +2160,9 @@
       <c r="O32" s="1">
         <v>25</v>
       </c>
+      <c r="P32" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q32" s="1">
         <v>22505</v>
       </c>
@@ -2085,12 +2179,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:21">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C33">
         <v>25</v>
@@ -2124,6 +2218,9 @@
       <c r="O33" s="1">
         <v>25</v>
       </c>
+      <c r="P33" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q33" s="1">
         <v>22505</v>
       </c>
@@ -2140,12 +2237,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:21">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C34">
         <v>28</v>
@@ -2179,6 +2276,9 @@
       <c r="O34" s="1">
         <v>25</v>
       </c>
+      <c r="P34" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q34" s="1">
         <v>22505</v>
       </c>
@@ -2195,12 +2295,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:21">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C35">
         <v>31</v>
@@ -2234,6 +2334,9 @@
       <c r="O35" s="1">
         <v>25</v>
       </c>
+      <c r="P35" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q35" s="1">
         <v>22505</v>
       </c>
@@ -2250,12 +2353,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:21">
       <c r="A36" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C36">
         <v>31</v>
@@ -2289,6 +2392,9 @@
       <c r="O36" s="1">
         <v>25</v>
       </c>
+      <c r="P36" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q36" s="1">
         <v>22505</v>
       </c>
@@ -2305,12 +2411,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:21">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C37">
         <v>27</v>
@@ -2344,6 +2450,9 @@
       <c r="O37" s="1">
         <v>25</v>
       </c>
+      <c r="P37" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q37" s="1">
         <v>22505</v>
       </c>
@@ -2360,12 +2469,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:21">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C38">
         <v>30</v>
@@ -2399,6 +2508,9 @@
       <c r="O38" s="1">
         <v>25</v>
       </c>
+      <c r="P38" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q38" s="1">
         <v>22505</v>
       </c>
@@ -2415,12 +2527,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:21">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C39">
         <v>14</v>
@@ -2448,6 +2560,9 @@
       <c r="O39" s="1">
         <v>25</v>
       </c>
+      <c r="P39" s="1">
+        <v>18050</v>
+      </c>
       <c r="Q39" s="1">
         <v>16115</v>
       </c>
@@ -2464,12 +2579,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:21">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C40">
         <v>16</v>
@@ -2497,6 +2612,9 @@
       <c r="O40" s="1">
         <v>25</v>
       </c>
+      <c r="P40" s="1">
+        <v>19920</v>
+      </c>
       <c r="Q40" s="1">
         <v>17785</v>
       </c>
@@ -2513,12 +2631,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:21">
       <c r="A41" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C41">
         <v>19</v>
@@ -2546,6 +2664,9 @@
       <c r="O41" s="1">
         <v>25</v>
       </c>
+      <c r="P41" s="1">
+        <v>21460</v>
+      </c>
       <c r="Q41" s="1">
         <v>19165</v>
       </c>
@@ -2562,12 +2683,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:21">
       <c r="A42" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C42">
         <v>25</v>
@@ -2595,6 +2716,9 @@
       <c r="O42" s="1">
         <v>25</v>
       </c>
+      <c r="P42" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q42" s="1">
         <v>22505</v>
       </c>
@@ -2611,12 +2735,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:21">
       <c r="A43" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C43">
         <v>18</v>
@@ -2644,6 +2768,9 @@
       <c r="O43" s="1">
         <v>25</v>
       </c>
+      <c r="P43" s="1">
+        <v>20650</v>
+      </c>
       <c r="Q43" s="1">
         <v>18440</v>
       </c>
@@ -2660,12 +2787,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:21">
       <c r="A44" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C44">
         <v>21</v>
@@ -2693,6 +2820,9 @@
       <c r="O44" s="1">
         <v>25</v>
       </c>
+      <c r="P44" s="1">
+        <v>23170</v>
+      </c>
       <c r="Q44" s="1">
         <v>20690</v>
       </c>
@@ -2709,12 +2839,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:21">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C45">
         <v>27</v>
@@ -2742,6 +2872,9 @@
       <c r="O45" s="1">
         <v>25</v>
       </c>
+      <c r="P45" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q45" s="1">
         <v>22505</v>
       </c>
@@ -2758,12 +2891,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:21">
       <c r="A46" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C46">
         <v>24</v>
@@ -2791,6 +2924,9 @@
       <c r="O46" s="1">
         <v>25</v>
       </c>
+      <c r="P46" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q46" s="1">
         <v>22505</v>
       </c>
@@ -2807,12 +2943,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:21">
       <c r="A47" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B47" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C47">
         <v>30</v>
@@ -2840,6 +2976,9 @@
       <c r="O47" s="1">
         <v>25</v>
       </c>
+      <c r="P47" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q47" s="1">
         <v>22505</v>
       </c>
@@ -2856,12 +2995,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:21">
       <c r="A48" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C48">
         <v>21</v>
@@ -2895,6 +3034,9 @@
       <c r="O48" s="1">
         <v>25</v>
       </c>
+      <c r="P48" s="1">
+        <v>23170</v>
+      </c>
       <c r="Q48" s="1">
         <v>20690</v>
       </c>
@@ -2911,12 +3053,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:21">
       <c r="A49" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C49">
         <v>23</v>
@@ -2950,6 +3092,9 @@
       <c r="O49" s="1">
         <v>25</v>
       </c>
+      <c r="P49" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q49" s="1">
         <v>22505</v>
       </c>
@@ -2966,12 +3111,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:21">
       <c r="A50" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B50" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C50">
         <v>26</v>
@@ -3005,6 +3150,9 @@
       <c r="O50" s="1">
         <v>25</v>
       </c>
+      <c r="P50" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q50" s="1">
         <v>22505</v>
       </c>
@@ -3021,12 +3169,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:21">
       <c r="A51" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B51" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C51">
         <v>25</v>
@@ -3060,6 +3208,9 @@
       <c r="O51" s="1">
         <v>25</v>
       </c>
+      <c r="P51" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q51" s="1">
         <v>22505</v>
       </c>
@@ -3076,12 +3227,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:21">
       <c r="A52" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B52" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C52">
         <v>28</v>
@@ -3115,6 +3266,9 @@
       <c r="O52" s="1">
         <v>25</v>
       </c>
+      <c r="P52" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q52" s="1">
         <v>22505</v>
       </c>
@@ -3131,12 +3285,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:21">
       <c r="A53" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B53" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C53">
         <v>31</v>
@@ -3170,6 +3324,9 @@
       <c r="O53" s="1">
         <v>25</v>
       </c>
+      <c r="P53" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q53" s="1">
         <v>22505</v>
       </c>
@@ -3186,12 +3343,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:21">
       <c r="A54" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B54" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C54">
         <v>27</v>
@@ -3225,6 +3382,9 @@
       <c r="O54" s="1">
         <v>25</v>
       </c>
+      <c r="P54" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q54" s="1">
         <v>22505</v>
       </c>
@@ -3241,12 +3401,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:21">
       <c r="A55" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B55" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C55">
         <v>30</v>
@@ -3280,6 +3440,9 @@
       <c r="O55" s="1">
         <v>25</v>
       </c>
+      <c r="P55" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q55" s="1">
         <v>22505</v>
       </c>
@@ -3296,12 +3459,12 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:21">
       <c r="A56" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C56">
         <v>31</v>
@@ -3327,6 +3490,9 @@
       <c r="O56" s="1">
         <v>35</v>
       </c>
+      <c r="P56" s="1">
+        <v>31280</v>
+      </c>
       <c r="Q56" s="1">
         <v>27260</v>
       </c>
@@ -3343,12 +3509,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:21">
       <c r="A57" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C57">
         <v>33</v>
@@ -3374,6 +3540,9 @@
       <c r="O57" s="1">
         <v>35</v>
       </c>
+      <c r="P57" s="1">
+        <v>33270</v>
+      </c>
       <c r="Q57" s="1">
         <v>28560</v>
       </c>
@@ -3390,12 +3559,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:21">
       <c r="A58" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C58">
         <v>30</v>
@@ -3421,6 +3590,9 @@
       <c r="O58" s="1">
         <v>35</v>
       </c>
+      <c r="P58" s="1">
+        <v>30330</v>
+      </c>
       <c r="Q58" s="1">
         <v>26610</v>
       </c>
@@ -3437,12 +3609,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:21">
       <c r="A59" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B59" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C59">
         <v>36</v>
@@ -3468,6 +3640,9 @@
       <c r="O59" s="1">
         <v>35</v>
       </c>
+      <c r="P59" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q59" s="1">
         <v>30760</v>
       </c>
@@ -3484,12 +3659,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:21">
       <c r="A60" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C60">
         <v>33</v>
@@ -3515,6 +3690,9 @@
       <c r="O60" s="1">
         <v>35</v>
       </c>
+      <c r="P60" s="1">
+        <v>33270</v>
+      </c>
       <c r="Q60" s="1">
         <v>28560</v>
       </c>
@@ -3531,12 +3709,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:21">
       <c r="A61" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C61">
         <v>39</v>
@@ -3562,6 +3740,9 @@
       <c r="O61" s="1">
         <v>35</v>
       </c>
+      <c r="P61" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q61" s="1">
         <v>30760</v>
       </c>
@@ -3578,12 +3759,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:21">
       <c r="A62" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C62">
         <v>36</v>
@@ -3609,6 +3790,9 @@
       <c r="O62" s="1">
         <v>35</v>
       </c>
+      <c r="P62" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q62" s="1">
         <v>30760</v>
       </c>
@@ -3625,12 +3809,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:21">
       <c r="A63" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C63">
         <v>42</v>
@@ -3656,6 +3840,9 @@
       <c r="O63" s="1">
         <v>35</v>
       </c>
+      <c r="P63" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q63" s="1">
         <v>30760</v>
       </c>
@@ -3672,12 +3859,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:21">
       <c r="A64" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B64" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C64">
         <v>26</v>
@@ -3709,6 +3896,9 @@
       <c r="O64" s="1">
         <v>35</v>
       </c>
+      <c r="P64" s="1">
+        <v>26260</v>
+      </c>
       <c r="Q64" s="1">
         <v>24010</v>
       </c>
@@ -3725,12 +3915,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:21">
       <c r="A65" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C65">
         <v>29</v>
@@ -3762,6 +3952,9 @@
       <c r="O65" s="1">
         <v>35</v>
       </c>
+      <c r="P65" s="1">
+        <v>29290</v>
+      </c>
       <c r="Q65" s="1">
         <v>25960</v>
       </c>
@@ -3778,12 +3971,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:21">
       <c r="A66" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C66">
         <v>32</v>
@@ -3815,6 +4008,9 @@
       <c r="O66" s="1">
         <v>35</v>
       </c>
+      <c r="P66" s="1">
+        <v>32320</v>
+      </c>
       <c r="Q66" s="1">
         <v>27910</v>
       </c>
@@ -3831,12 +4027,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:21">
       <c r="A67" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B67" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C67">
         <v>38</v>
@@ -3868,6 +4064,9 @@
       <c r="O67" s="1">
         <v>35</v>
       </c>
+      <c r="P67" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q67" s="1">
         <v>30760</v>
       </c>
@@ -3884,12 +4083,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:21">
       <c r="A68" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B68" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C68">
         <v>25</v>
@@ -3921,6 +4120,9 @@
       <c r="O68" s="1">
         <v>35</v>
       </c>
+      <c r="P68" s="1">
+        <v>25220</v>
+      </c>
       <c r="Q68" s="1">
         <v>23360</v>
       </c>
@@ -3937,12 +4139,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:21">
       <c r="A69" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B69" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C69">
         <v>28</v>
@@ -3974,6 +4176,9 @@
       <c r="O69" s="1">
         <v>35</v>
       </c>
+      <c r="P69" s="1">
+        <v>28250</v>
+      </c>
       <c r="Q69" s="1">
         <v>25310</v>
       </c>
@@ -3990,12 +4195,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:21">
       <c r="A70" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C70">
         <v>31</v>
@@ -4027,6 +4232,9 @@
       <c r="O70" s="1">
         <v>35</v>
       </c>
+      <c r="P70" s="1">
+        <v>31280</v>
+      </c>
       <c r="Q70" s="1">
         <v>27260</v>
       </c>
@@ -4043,12 +4251,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:21">
       <c r="A71" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B71" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C71">
         <v>34</v>
@@ -4080,6 +4288,9 @@
       <c r="O71" s="1">
         <v>35</v>
       </c>
+      <c r="P71" s="1">
+        <v>34310</v>
+      </c>
       <c r="Q71" s="1">
         <v>29260</v>
       </c>
@@ -4096,12 +4307,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:21">
       <c r="A72" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C72">
         <v>40</v>
@@ -4133,6 +4344,9 @@
       <c r="O72" s="1">
         <v>35</v>
       </c>
+      <c r="P72" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q72" s="1">
         <v>30760</v>
       </c>
@@ -4149,12 +4363,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:21">
       <c r="A73" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B73" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C73">
         <v>31</v>
@@ -4186,6 +4400,9 @@
       <c r="O73" s="1">
         <v>35</v>
       </c>
+      <c r="P73" s="1">
+        <v>31280</v>
+      </c>
       <c r="Q73" s="1">
         <v>27260</v>
       </c>
@@ -4202,12 +4419,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:21">
       <c r="A74" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C74">
         <v>34</v>
@@ -4239,6 +4456,9 @@
       <c r="O74" s="1">
         <v>35</v>
       </c>
+      <c r="P74" s="1">
+        <v>34310</v>
+      </c>
       <c r="Q74" s="1">
         <v>29260</v>
       </c>
@@ -4255,12 +4475,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:21">
       <c r="A75" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C75">
         <v>37</v>
@@ -4292,6 +4512,9 @@
       <c r="O75" s="1">
         <v>35</v>
       </c>
+      <c r="P75" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q75" s="1">
         <v>30760</v>
       </c>
@@ -4308,12 +4531,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:21">
       <c r="A76" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C76">
         <v>43</v>
@@ -4345,6 +4568,9 @@
       <c r="O76" s="1">
         <v>35</v>
       </c>
+      <c r="P76" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q76" s="1">
         <v>30760</v>
       </c>
@@ -4361,12 +4587,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:21">
       <c r="A77" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B77" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C77">
         <v>37</v>
@@ -4398,6 +4624,9 @@
       <c r="O77" s="1">
         <v>35</v>
       </c>
+      <c r="P77" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q77" s="1">
         <v>30760</v>
       </c>
@@ -4414,12 +4643,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:21">
       <c r="A78" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B78" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C78">
         <v>40</v>
@@ -4451,6 +4680,9 @@
       <c r="O78" s="1">
         <v>35</v>
       </c>
+      <c r="P78" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q78" s="1">
         <v>30760</v>
       </c>
@@ -4467,12 +4699,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:21">
       <c r="A79" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B79" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C79">
         <v>46</v>
@@ -4504,6 +4736,9 @@
       <c r="O79" s="1">
         <v>35</v>
       </c>
+      <c r="P79" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q79" s="1">
         <v>30760</v>
       </c>
@@ -4520,12 +4755,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:21">
       <c r="A80" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B80" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C80">
         <v>43</v>
@@ -4557,6 +4792,9 @@
       <c r="O80" s="1">
         <v>35</v>
       </c>
+      <c r="P80" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q80" s="1">
         <v>30760</v>
       </c>
@@ -4573,12 +4811,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:21">
       <c r="A81" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B81" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C81">
         <v>27</v>
@@ -4610,6 +4848,9 @@
       <c r="O81" s="1">
         <v>35</v>
       </c>
+      <c r="P81" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q81" s="1">
         <v>24660</v>
       </c>
@@ -4626,12 +4867,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:21">
       <c r="A82" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C82">
         <v>30</v>
@@ -4663,6 +4904,9 @@
       <c r="O82" s="1">
         <v>35</v>
       </c>
+      <c r="P82" s="1">
+        <v>25200</v>
+      </c>
       <c r="Q82" s="1">
         <v>26610</v>
       </c>
@@ -4679,12 +4923,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:21">
       <c r="A83" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B83" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C83">
         <v>33</v>
@@ -4716,6 +4960,9 @@
       <c r="O83" s="1">
         <v>35</v>
       </c>
+      <c r="P83" s="1">
+        <v>33270</v>
+      </c>
       <c r="Q83" s="1">
         <v>28560</v>
       </c>
@@ -4732,12 +4979,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:21">
       <c r="A84" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B84" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C84">
         <v>36</v>
@@ -4769,6 +5016,9 @@
       <c r="O84" s="1">
         <v>35</v>
       </c>
+      <c r="P84" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q84" s="1">
         <v>30760</v>
       </c>
@@ -4785,12 +5035,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:21">
       <c r="A85" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B85" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C85">
         <v>42</v>
@@ -4822,6 +5072,9 @@
       <c r="O85" s="1">
         <v>35</v>
       </c>
+      <c r="P85" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q85" s="1">
         <v>30760</v>
       </c>
@@ -4838,12 +5091,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:21">
       <c r="A86" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B86" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C86">
         <v>33</v>
@@ -4875,6 +5128,9 @@
       <c r="O86" s="1">
         <v>35</v>
       </c>
+      <c r="P86" s="1">
+        <v>33270</v>
+      </c>
       <c r="Q86" s="1">
         <v>28560</v>
       </c>
@@ -4891,12 +5147,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:21">
       <c r="A87" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B87" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C87">
         <v>36</v>
@@ -4928,6 +5184,9 @@
       <c r="O87" s="1">
         <v>35</v>
       </c>
+      <c r="P87" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q87" s="1">
         <v>30760</v>
       </c>
@@ -4944,12 +5203,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:21">
       <c r="A88" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B88" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C88">
         <v>39</v>
@@ -4981,6 +5240,9 @@
       <c r="O88" s="1">
         <v>35</v>
       </c>
+      <c r="P88" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q88" s="1">
         <v>30760</v>
       </c>
@@ -4997,12 +5259,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:21">
       <c r="A89" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B89" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C89">
         <v>45</v>
@@ -5034,6 +5296,9 @@
       <c r="O89" s="1">
         <v>35</v>
       </c>
+      <c r="P89" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q89" s="1">
         <v>30760</v>
       </c>
@@ -5050,12 +5315,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:21">
       <c r="A90" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B90" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C90">
         <v>39</v>
@@ -5087,6 +5352,9 @@
       <c r="O90" s="1">
         <v>35</v>
       </c>
+      <c r="P90" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q90" s="1">
         <v>30760</v>
       </c>
@@ -5103,12 +5371,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:21">
       <c r="A91" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B91" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C91">
         <v>42</v>
@@ -5140,6 +5408,9 @@
       <c r="O91" s="1">
         <v>35</v>
       </c>
+      <c r="P91" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q91" s="1">
         <v>30760</v>
       </c>
@@ -5156,12 +5427,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:21">
       <c r="A92" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B92" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C92">
         <v>45</v>
@@ -5193,6 +5464,9 @@
       <c r="O92" s="1">
         <v>35</v>
       </c>
+      <c r="P92" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q92" s="1">
         <v>30760</v>
       </c>
@@ -5209,12 +5483,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:21">
       <c r="A93" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B93" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C93">
         <v>36</v>
@@ -5246,6 +5520,9 @@
       <c r="O93" s="1">
         <v>35</v>
       </c>
+      <c r="P93" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q93" s="1">
         <v>30760</v>
       </c>
@@ -5262,12 +5539,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:21">
       <c r="A94" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B94" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C94">
         <v>39</v>
@@ -5299,6 +5576,9 @@
       <c r="O94" s="1">
         <v>35</v>
       </c>
+      <c r="P94" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q94" s="1">
         <v>30760</v>
       </c>
@@ -5315,12 +5595,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:21">
       <c r="A95" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B95" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C95">
         <v>42</v>
@@ -5352,6 +5632,9 @@
       <c r="O95" s="1">
         <v>35</v>
       </c>
+      <c r="P95" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q95" s="1">
         <v>30760</v>
       </c>
@@ -5368,12 +5651,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:21">
       <c r="A96" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C96">
         <v>42</v>
@@ -5405,6 +5688,9 @@
       <c r="O96" s="1">
         <v>35</v>
       </c>
+      <c r="P96" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q96" s="1">
         <v>30760</v>
       </c>
@@ -5421,12 +5707,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:21">
       <c r="A97" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C97">
         <v>45</v>
@@ -5458,6 +5744,9 @@
       <c r="O97" s="1">
         <v>35</v>
       </c>
+      <c r="P97" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q97" s="1">
         <v>30760</v>
       </c>
@@ -5474,12 +5763,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:21">
       <c r="A98" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C98">
         <v>45</v>
@@ -5511,6 +5800,9 @@
       <c r="O98" s="1">
         <v>35</v>
       </c>
+      <c r="P98" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q98" s="1">
         <v>30760</v>
       </c>
@@ -5527,12 +5819,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:21">
       <c r="A99" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C99">
         <v>28</v>
@@ -5570,6 +5862,9 @@
       <c r="O99" s="1">
         <v>35</v>
       </c>
+      <c r="P99" s="1">
+        <v>28250</v>
+      </c>
       <c r="Q99" s="1">
         <v>25310</v>
       </c>
@@ -5586,12 +5881,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:21">
       <c r="A100" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B100" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C100">
         <v>30</v>
@@ -5629,6 +5924,9 @@
       <c r="O100" s="1">
         <v>35</v>
       </c>
+      <c r="P100" s="1">
+        <v>30330</v>
+      </c>
       <c r="Q100" s="1">
         <v>26610</v>
       </c>
@@ -5645,12 +5943,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:21">
       <c r="A101" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C101">
         <v>33</v>
@@ -5688,6 +5986,9 @@
       <c r="O101" s="1">
         <v>35</v>
       </c>
+      <c r="P101" s="1">
+        <v>33270</v>
+      </c>
       <c r="Q101" s="1">
         <v>28560</v>
       </c>
@@ -5704,12 +6005,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:21">
       <c r="A102" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B102" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C102">
         <v>36</v>
@@ -5747,6 +6048,9 @@
       <c r="O102" s="1">
         <v>35</v>
       </c>
+      <c r="P102" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q102" s="1">
         <v>30760</v>
       </c>
@@ -5763,12 +6067,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:21">
       <c r="A103" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B103" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C103">
         <v>39</v>
@@ -5806,6 +6110,9 @@
       <c r="O103" s="1">
         <v>35</v>
       </c>
+      <c r="P103" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q103" s="1">
         <v>30760</v>
       </c>
@@ -5822,12 +6129,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:21">
       <c r="A104" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B104" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C104">
         <v>45</v>
@@ -5865,6 +6172,9 @@
       <c r="O104" s="1">
         <v>35</v>
       </c>
+      <c r="P104" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q104" s="1">
         <v>30760</v>
       </c>
@@ -5881,12 +6191,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:21">
       <c r="A105" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B105" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C105">
         <v>32</v>
@@ -5924,6 +6234,9 @@
       <c r="O105" s="1">
         <v>35</v>
       </c>
+      <c r="P105" s="1">
+        <v>32320</v>
+      </c>
       <c r="Q105" s="1">
         <v>27910</v>
       </c>
@@ -5940,12 +6253,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:21">
       <c r="A106" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B106" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C106">
         <v>35</v>
@@ -5983,6 +6296,9 @@
       <c r="O106" s="1">
         <v>35</v>
       </c>
+      <c r="P106" s="1">
+        <v>35360</v>
+      </c>
       <c r="Q106" s="1">
         <v>29880</v>
       </c>
@@ -5999,12 +6315,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:21">
       <c r="A107" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B107" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C107">
         <v>38</v>
@@ -6042,6 +6358,9 @@
       <c r="O107" s="1">
         <v>35</v>
       </c>
+      <c r="P107" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q107" s="1">
         <v>30760</v>
       </c>
@@ -6058,12 +6377,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:21">
       <c r="A108" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B108" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C108">
         <v>41</v>
@@ -6101,6 +6420,9 @@
       <c r="O108" s="1">
         <v>35</v>
       </c>
+      <c r="P108" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q108" s="1">
         <v>30760</v>
       </c>
@@ -6117,12 +6439,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:21">
       <c r="A109" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C109">
         <v>38</v>
@@ -6160,6 +6482,9 @@
       <c r="O109" s="1">
         <v>35</v>
       </c>
+      <c r="P109" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q109" s="1">
         <v>30760</v>
       </c>
@@ -6176,12 +6501,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:21">
       <c r="A110" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B110" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C110">
         <v>41</v>
@@ -6219,6 +6544,9 @@
       <c r="O110" s="1">
         <v>35</v>
       </c>
+      <c r="P110" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q110" s="1">
         <v>30760</v>
       </c>
@@ -6235,12 +6563,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:21">
       <c r="A111" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C111">
         <v>44</v>
@@ -6278,6 +6606,9 @@
       <c r="O111" s="1">
         <v>35</v>
       </c>
+      <c r="P111" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q111" s="1">
         <v>30760</v>
       </c>
@@ -6294,12 +6625,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:21">
       <c r="A112" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B112" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C112">
         <v>44</v>
@@ -6337,6 +6668,9 @@
       <c r="O112" s="1">
         <v>35</v>
       </c>
+      <c r="P112" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q112" s="1">
         <v>30760</v>
       </c>
@@ -6353,12 +6687,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:21">
       <c r="A113" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B113" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C113">
         <v>34</v>
@@ -6396,6 +6730,9 @@
       <c r="O113" s="1">
         <v>35</v>
       </c>
+      <c r="P113" s="1">
+        <v>34310</v>
+      </c>
       <c r="Q113" s="1">
         <v>29260</v>
       </c>
@@ -6412,12 +6749,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:21">
       <c r="A114" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B114" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C114">
         <v>37</v>
@@ -6455,6 +6792,9 @@
       <c r="O114" s="1">
         <v>35</v>
       </c>
+      <c r="P114" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q114" s="1">
         <v>30760</v>
       </c>
@@ -6471,12 +6811,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:21">
       <c r="A115" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B115" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C115">
         <v>40</v>
@@ -6514,6 +6854,9 @@
       <c r="O115" s="1">
         <v>35</v>
       </c>
+      <c r="P115" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q115" s="1">
         <v>30760</v>
       </c>
@@ -6530,12 +6873,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:21">
       <c r="A116" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B116" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C116">
         <v>43</v>
@@ -6573,6 +6916,9 @@
       <c r="O116" s="1">
         <v>35</v>
       </c>
+      <c r="P116" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q116" s="1">
         <v>30760</v>
       </c>
@@ -6589,12 +6935,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:21">
       <c r="A117" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B117" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C117">
         <v>40</v>
@@ -6632,6 +6978,9 @@
       <c r="O117" s="1">
         <v>35</v>
       </c>
+      <c r="P117" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q117" s="1">
         <v>30760</v>
       </c>
@@ -6648,12 +6997,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:21">
       <c r="A118" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B118" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C118">
         <v>43</v>
@@ -6691,6 +7040,9 @@
       <c r="O118" s="1">
         <v>35</v>
       </c>
+      <c r="P118" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q118" s="1">
         <v>30760</v>
       </c>
@@ -6707,12 +7059,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:21">
       <c r="A119" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B119" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C119">
         <v>46</v>
@@ -6750,6 +7102,9 @@
       <c r="O119" s="1">
         <v>35</v>
       </c>
+      <c r="P119" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q119" s="1">
         <v>30760</v>
       </c>
@@ -6766,12 +7121,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:21">
       <c r="A120" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B120" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C120">
         <v>46</v>
@@ -6809,6 +7164,9 @@
       <c r="O120" s="1">
         <v>35</v>
       </c>
+      <c r="P120" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q120" s="1">
         <v>30760</v>
       </c>
@@ -6825,12 +7183,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:21">
       <c r="A121" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B121" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C121">
         <v>43</v>
@@ -6868,6 +7226,9 @@
       <c r="O121" s="1">
         <v>35</v>
       </c>
+      <c r="P121" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q121" s="1">
         <v>30760</v>
       </c>
@@ -6884,12 +7245,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:21">
       <c r="A122" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B122" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C122">
         <v>46</v>
@@ -6927,6 +7288,9 @@
       <c r="O122" s="1">
         <v>35</v>
       </c>
+      <c r="P122" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q122" s="1">
         <v>30760</v>
       </c>
@@ -6943,12 +7307,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:21">
       <c r="A123" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B123" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C123">
         <v>36</v>
@@ -6986,6 +7350,9 @@
       <c r="O123" s="1">
         <v>35</v>
       </c>
+      <c r="P123" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q123" s="1">
         <v>30760</v>
       </c>
@@ -7002,12 +7369,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:21">
       <c r="A124" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B124" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C124">
         <v>39</v>
@@ -7045,6 +7412,9 @@
       <c r="O124" s="1">
         <v>35</v>
       </c>
+      <c r="P124" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q124" s="1">
         <v>30760</v>
       </c>
@@ -7061,12 +7431,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:21">
       <c r="A125" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B125" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C125">
         <v>42</v>
@@ -7104,6 +7474,9 @@
       <c r="O125" s="1">
         <v>35</v>
       </c>
+      <c r="P125" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q125" s="1">
         <v>30760</v>
       </c>
@@ -7120,12 +7493,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:21">
       <c r="A126" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B126" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C126">
         <v>45</v>
@@ -7163,6 +7536,9 @@
       <c r="O126" s="1">
         <v>35</v>
       </c>
+      <c r="P126" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q126" s="1">
         <v>30760</v>
       </c>
@@ -7179,12 +7555,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:21">
       <c r="A127" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B127" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C127">
         <v>42</v>
@@ -7222,6 +7598,9 @@
       <c r="O127" s="1">
         <v>35</v>
       </c>
+      <c r="P127" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q127" s="1">
         <v>30760</v>
       </c>
@@ -7238,12 +7617,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:21">
       <c r="A128" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B128" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C128">
         <v>45</v>
@@ -7281,6 +7660,9 @@
       <c r="O128" s="1">
         <v>35</v>
       </c>
+      <c r="P128" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q128" s="1">
         <v>30760</v>
       </c>
@@ -7297,12 +7679,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:21">
       <c r="A129" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B129" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C129">
         <v>45</v>
@@ -7340,6 +7722,9 @@
       <c r="O129" s="1">
         <v>35</v>
       </c>
+      <c r="P129" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q129" s="1">
         <v>30760</v>
       </c>
@@ -7356,12 +7741,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:21">
       <c r="A130" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B130" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C130">
         <v>31</v>
@@ -7387,6 +7772,9 @@
       <c r="O130" s="1">
         <v>35</v>
       </c>
+      <c r="P130" s="1">
+        <v>31280</v>
+      </c>
       <c r="Q130" s="1">
         <v>27260</v>
       </c>
@@ -7403,12 +7791,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:21">
       <c r="A131" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B131" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C131">
         <v>33</v>
@@ -7434,6 +7822,9 @@
       <c r="O131" s="1">
         <v>35</v>
       </c>
+      <c r="P131" s="1">
+        <v>33270</v>
+      </c>
       <c r="Q131" s="1">
         <v>28560</v>
       </c>
@@ -7450,12 +7841,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:21">
       <c r="A132" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B132" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C132">
         <v>30</v>
@@ -7481,6 +7872,9 @@
       <c r="O132" s="1">
         <v>35</v>
       </c>
+      <c r="P132" s="1">
+        <v>30330</v>
+      </c>
       <c r="Q132" s="1">
         <v>26610</v>
       </c>
@@ -7497,12 +7891,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:21">
       <c r="A133" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B133" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -7528,6 +7922,9 @@
       <c r="O133" s="1">
         <v>35</v>
       </c>
+      <c r="P133" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q133" s="1">
         <v>30760</v>
       </c>
@@ -7544,12 +7941,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:21">
       <c r="A134" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B134" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C134">
         <v>36</v>
@@ -7575,6 +7972,9 @@
       <c r="O134" s="1">
         <v>35</v>
       </c>
+      <c r="P134" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q134" s="1">
         <v>30760</v>
       </c>
@@ -7591,12 +7991,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:21">
       <c r="A135" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B135" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C135">
         <v>42</v>
@@ -7622,6 +8022,9 @@
       <c r="O135" s="1">
         <v>35</v>
       </c>
+      <c r="P135" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q135" s="1">
         <v>30760</v>
       </c>
@@ -7638,12 +8041,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:21">
       <c r="A136" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B136" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C136">
         <v>26</v>
@@ -7675,6 +8078,9 @@
       <c r="O136" s="1">
         <v>35</v>
       </c>
+      <c r="P136" s="1">
+        <v>26260</v>
+      </c>
       <c r="Q136" s="1">
         <v>24010</v>
       </c>
@@ -7691,12 +8097,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:21">
       <c r="A137" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B137" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C137">
         <v>32</v>
@@ -7728,6 +8134,9 @@
       <c r="O137" s="1">
         <v>35</v>
       </c>
+      <c r="P137" s="1">
+        <v>32320</v>
+      </c>
       <c r="Q137" s="1">
         <v>27910</v>
       </c>
@@ -7744,12 +8153,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:21">
       <c r="A138" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B138" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C138">
         <v>38</v>
@@ -7781,6 +8190,9 @@
       <c r="O138" s="1">
         <v>35</v>
       </c>
+      <c r="P138" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q138" s="1">
         <v>30760</v>
       </c>
@@ -7797,12 +8209,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:21">
       <c r="A139" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B139" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C139">
         <v>25</v>
@@ -7834,6 +8246,9 @@
       <c r="O139" s="1">
         <v>35</v>
       </c>
+      <c r="P139" s="1">
+        <v>25220</v>
+      </c>
       <c r="Q139" s="1">
         <v>23360</v>
       </c>
@@ -7850,12 +8265,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:21">
       <c r="A140" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B140" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C140">
         <v>28</v>
@@ -7887,6 +8302,9 @@
       <c r="O140" s="1">
         <v>35</v>
       </c>
+      <c r="P140" s="1">
+        <v>28250</v>
+      </c>
       <c r="Q140" s="1">
         <v>25310</v>
       </c>
@@ -7903,12 +8321,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:21">
       <c r="A141" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B141" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C141">
         <v>34</v>
@@ -7940,6 +8358,9 @@
       <c r="O141" s="1">
         <v>35</v>
       </c>
+      <c r="P141" s="1">
+        <v>34310</v>
+      </c>
       <c r="Q141" s="1">
         <v>29260</v>
       </c>
@@ -7956,12 +8377,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:21">
       <c r="A142" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B142" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C142">
         <v>40</v>
@@ -7993,6 +8414,9 @@
       <c r="O142" s="1">
         <v>35</v>
       </c>
+      <c r="P142" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q142" s="1">
         <v>30760</v>
       </c>
@@ -8009,12 +8433,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:21">
       <c r="A143" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B143" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C143">
         <v>31</v>
@@ -8046,6 +8470,9 @@
       <c r="O143" s="1">
         <v>35</v>
       </c>
+      <c r="P143" s="1">
+        <v>31280</v>
+      </c>
       <c r="Q143" s="1">
         <v>27260</v>
       </c>
@@ -8062,12 +8489,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:21">
       <c r="A144" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B144" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C144">
         <v>37</v>
@@ -8099,6 +8526,9 @@
       <c r="O144" s="1">
         <v>35</v>
       </c>
+      <c r="P144" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q144" s="1">
         <v>30760</v>
       </c>
@@ -8115,12 +8545,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:21">
       <c r="A145" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B145" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C145">
         <v>43</v>
@@ -8152,6 +8582,9 @@
       <c r="O145" s="1">
         <v>35</v>
       </c>
+      <c r="P145" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q145" s="1">
         <v>30760</v>
       </c>
@@ -8168,12 +8601,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:21">
       <c r="A146" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B146" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C146">
         <v>43</v>
@@ -8205,6 +8638,9 @@
       <c r="O146" s="1">
         <v>35</v>
       </c>
+      <c r="P146" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q146" s="1">
         <v>30760</v>
       </c>
@@ -8221,12 +8657,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:21">
       <c r="A147" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B147" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C147">
         <v>27</v>
@@ -8258,6 +8694,9 @@
       <c r="O147" s="1">
         <v>35</v>
       </c>
+      <c r="P147" s="1">
+        <v>27300</v>
+      </c>
       <c r="Q147" s="1">
         <v>24660</v>
       </c>
@@ -8274,12 +8713,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:21">
       <c r="A148" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B148" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C148">
         <v>30</v>
@@ -8311,6 +8750,9 @@
       <c r="O148" s="1">
         <v>35</v>
       </c>
+      <c r="P148" s="1">
+        <v>30330</v>
+      </c>
       <c r="Q148" s="1">
         <v>26610</v>
       </c>
@@ -8327,12 +8769,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:21">
       <c r="A149" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B149" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C149">
         <v>36</v>
@@ -8364,6 +8806,9 @@
       <c r="O149" s="1">
         <v>35</v>
       </c>
+      <c r="P149" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q149" s="1">
         <v>30760</v>
       </c>
@@ -8380,12 +8825,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:21">
       <c r="A150" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B150" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C150">
         <v>42</v>
@@ -8417,6 +8862,9 @@
       <c r="O150" s="1">
         <v>35</v>
       </c>
+      <c r="P150" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q150" s="1">
         <v>30760</v>
       </c>
@@ -8433,12 +8881,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:21">
       <c r="A151" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B151" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C151">
         <v>33</v>
@@ -8470,6 +8918,9 @@
       <c r="O151" s="1">
         <v>35</v>
       </c>
+      <c r="P151" s="1">
+        <v>33270</v>
+      </c>
       <c r="Q151" s="1">
         <v>28560</v>
       </c>
@@ -8486,12 +8937,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:21">
       <c r="A152" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B152" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C152">
         <v>39</v>
@@ -8523,6 +8974,9 @@
       <c r="O152" s="1">
         <v>35</v>
       </c>
+      <c r="P152" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q152" s="1">
         <v>30760</v>
       </c>
@@ -8539,12 +8993,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:21">
       <c r="A153" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B153" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C153">
         <v>45</v>
@@ -8576,6 +9030,9 @@
       <c r="O153" s="1">
         <v>35</v>
       </c>
+      <c r="P153" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q153" s="1">
         <v>30760</v>
       </c>
@@ -8592,12 +9049,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:21">
       <c r="A154" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B154" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C154">
         <v>45</v>
@@ -8629,6 +9086,9 @@
       <c r="O154" s="1">
         <v>35</v>
       </c>
+      <c r="P154" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q154" s="1">
         <v>30760</v>
       </c>
@@ -8645,12 +9105,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:21">
       <c r="A155" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B155" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C155">
         <v>36</v>
@@ -8682,6 +9142,9 @@
       <c r="O155" s="1">
         <v>35</v>
       </c>
+      <c r="P155" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q155" s="1">
         <v>30760</v>
       </c>
@@ -8698,12 +9161,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:21">
       <c r="A156" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B156" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C156">
         <v>42</v>
@@ -8735,6 +9198,9 @@
       <c r="O156" s="1">
         <v>35</v>
       </c>
+      <c r="P156" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q156" s="1">
         <v>30760</v>
       </c>
@@ -8751,12 +9217,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:21">
       <c r="A157" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B157" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C157">
         <v>28</v>
@@ -8794,6 +9260,9 @@
       <c r="O157" s="1">
         <v>35</v>
       </c>
+      <c r="P157" s="1">
+        <v>28250</v>
+      </c>
       <c r="Q157" s="1">
         <v>25310</v>
       </c>
@@ -8810,12 +9279,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="158" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:21">
       <c r="A158" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B158" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C158">
         <v>30</v>
@@ -8853,6 +9322,9 @@
       <c r="O158" s="1">
         <v>35</v>
       </c>
+      <c r="P158" s="1">
+        <v>30330</v>
+      </c>
       <c r="Q158" s="1">
         <v>26610</v>
       </c>
@@ -8869,12 +9341,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="159" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:21">
       <c r="A159" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B159" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C159">
         <v>33</v>
@@ -8912,6 +9384,9 @@
       <c r="O159" s="1">
         <v>35</v>
       </c>
+      <c r="P159" s="1">
+        <v>33270</v>
+      </c>
       <c r="Q159" s="1">
         <v>28560</v>
       </c>
@@ -8928,12 +9403,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="160" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:21">
       <c r="A160" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B160" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C160">
         <v>39</v>
@@ -8971,6 +9446,9 @@
       <c r="O160" s="1">
         <v>35</v>
       </c>
+      <c r="P160" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q160" s="1">
         <v>30760</v>
       </c>
@@ -8987,12 +9465,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:21">
       <c r="A161" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B161" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C161">
         <v>45</v>
@@ -9030,6 +9508,9 @@
       <c r="O161" s="1">
         <v>35</v>
       </c>
+      <c r="P161" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q161" s="1">
         <v>30760</v>
       </c>
@@ -9046,12 +9527,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:21">
       <c r="A162" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B162" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C162">
         <v>32</v>
@@ -9089,6 +9570,9 @@
       <c r="O162" s="1">
         <v>35</v>
       </c>
+      <c r="P162" s="1">
+        <v>32320</v>
+      </c>
       <c r="Q162" s="1">
         <v>27910</v>
       </c>
@@ -9105,12 +9589,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:21">
       <c r="A163" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B163" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C163">
         <v>35</v>
@@ -9148,6 +9632,9 @@
       <c r="O163" s="1">
         <v>35</v>
       </c>
+      <c r="P163" s="1">
+        <v>35360</v>
+      </c>
       <c r="Q163" s="1">
         <v>29880</v>
       </c>
@@ -9164,12 +9651,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:21">
       <c r="A164" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B164" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C164">
         <v>41</v>
@@ -9207,6 +9694,9 @@
       <c r="O164" s="1">
         <v>35</v>
       </c>
+      <c r="P164" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q164" s="1">
         <v>30760</v>
       </c>
@@ -9223,12 +9713,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:21">
       <c r="A165" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B165" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C165">
         <v>38</v>
@@ -9266,6 +9756,9 @@
       <c r="O165" s="1">
         <v>35</v>
       </c>
+      <c r="P165" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q165" s="1">
         <v>30760</v>
       </c>
@@ -9282,12 +9775,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:21">
       <c r="A166" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B166" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C166">
         <v>44</v>
@@ -9325,6 +9818,9 @@
       <c r="O166" s="1">
         <v>35</v>
       </c>
+      <c r="P166" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q166" s="1">
         <v>30760</v>
       </c>
@@ -9341,12 +9837,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:21">
       <c r="A167" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B167" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C167">
         <v>34</v>
@@ -9384,6 +9880,9 @@
       <c r="O167" s="1">
         <v>35</v>
       </c>
+      <c r="P167" s="1">
+        <v>34310</v>
+      </c>
       <c r="Q167" s="1">
         <v>29260</v>
       </c>
@@ -9400,12 +9899,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:21">
       <c r="A168" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B168" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C168">
         <v>37</v>
@@ -9443,6 +9942,9 @@
       <c r="O168" s="1">
         <v>35</v>
       </c>
+      <c r="P168" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q168" s="1">
         <v>30760</v>
       </c>
@@ -9459,12 +9961,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:21">
       <c r="A169" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B169" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C169">
         <v>43</v>
@@ -9502,6 +10004,9 @@
       <c r="O169" s="1">
         <v>35</v>
       </c>
+      <c r="P169" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q169" s="1">
         <v>30760</v>
       </c>
@@ -9518,12 +10023,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:21">
       <c r="A170" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B170" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C170">
         <v>40</v>
@@ -9561,6 +10066,9 @@
       <c r="O170" s="1">
         <v>35</v>
       </c>
+      <c r="P170" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q170" s="1">
         <v>30760</v>
       </c>
@@ -9577,12 +10085,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:21">
       <c r="A171" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B171" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C171">
         <v>46</v>
@@ -9620,6 +10128,9 @@
       <c r="O171" s="1">
         <v>35</v>
       </c>
+      <c r="P171" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q171" s="1">
         <v>30760</v>
       </c>
@@ -9636,12 +10147,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:21">
       <c r="A172" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B172" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C172">
         <v>43</v>
@@ -9679,6 +10190,9 @@
       <c r="O172" s="1">
         <v>35</v>
       </c>
+      <c r="P172" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q172" s="1">
         <v>30760</v>
       </c>
@@ -9695,12 +10209,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="173" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:21">
       <c r="A173" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B173" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C173">
         <v>36</v>
@@ -9738,6 +10252,9 @@
       <c r="O173" s="1">
         <v>35</v>
       </c>
+      <c r="P173" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q173" s="1">
         <v>30760</v>
       </c>
@@ -9754,12 +10271,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="174" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:21">
       <c r="A174" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B174" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C174">
         <v>39</v>
@@ -9797,6 +10314,9 @@
       <c r="O174" s="1">
         <v>35</v>
       </c>
+      <c r="P174" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q174" s="1">
         <v>30760</v>
       </c>
@@ -9813,12 +10333,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="175" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:21">
       <c r="A175" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B175" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C175">
         <v>45</v>
@@ -9856,6 +10376,9 @@
       <c r="O175" s="1">
         <v>35</v>
       </c>
+      <c r="P175" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q175" s="1">
         <v>30760</v>
       </c>
@@ -9872,12 +10395,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="176" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:21">
       <c r="A176" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B176" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C176">
         <v>42</v>
@@ -9915,6 +10438,9 @@
       <c r="O176" s="1">
         <v>35</v>
       </c>
+      <c r="P176" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q176" s="1">
         <v>30760</v>
       </c>
@@ -9931,12 +10457,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="177" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:21">
       <c r="A177" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B177" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C177">
         <v>45</v>
@@ -9974,6 +10500,9 @@
       <c r="O177" s="1">
         <v>35</v>
       </c>
+      <c r="P177" s="1">
+        <v>36400</v>
+      </c>
       <c r="Q177" s="1">
         <v>30760</v>
       </c>
@@ -9990,12 +10519,12 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="178" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:21">
       <c r="A178" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B178" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C178" s="2">
         <v>12</v>
@@ -10039,12 +10568,12 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="179" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:21">
       <c r="A179" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B179" t="s">
         <v>22</v>
-      </c>
-      <c r="B179" t="s">
-        <v>14</v>
       </c>
       <c r="C179" s="2">
         <v>18</v>
@@ -10088,12 +10617,12 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="180" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:21">
       <c r="A180" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B180" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C180" s="2">
         <v>24</v>
@@ -10137,12 +10666,12 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="181" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:21">
       <c r="A181" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B181" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C181" s="2">
         <v>30</v>
@@ -10186,12 +10715,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:21">
       <c r="A182" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B182" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C182" s="2">
         <v>36</v>
@@ -10235,12 +10764,12 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="183" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:21">
       <c r="A183" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B183" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C183" s="2">
         <v>48</v>
@@ -10293,39 +10822,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D46"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>46</v>
@@ -10337,9 +10866,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>45</v>
@@ -10351,9 +10880,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>44</v>
@@ -10365,9 +10894,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B6">
         <v>43</v>
@@ -10379,9 +10908,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>42</v>
@@ -10393,9 +10922,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>41</v>
@@ -10407,9 +10936,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>40</v>
@@ -10421,9 +10950,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>39</v>
@@ -10435,9 +10964,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>38</v>
@@ -10449,9 +10978,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>37</v>
@@ -10463,9 +10992,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>36</v>
@@ -10477,9 +11006,9 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>35</v>
@@ -10491,9 +11020,9 @@
         <v>29880</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>34</v>
@@ -10505,9 +11034,9 @@
         <v>29260</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>33</v>
@@ -10519,9 +11048,9 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B17">
         <v>32</v>
@@ -10533,9 +11062,9 @@
         <v>27910</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B18">
         <v>31</v>
@@ -10547,9 +11076,9 @@
         <v>27260</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B19">
         <v>30</v>
@@ -10561,9 +11090,9 @@
         <v>26610</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B20">
         <v>29</v>
@@ -10575,9 +11104,9 @@
         <v>25960</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B21">
         <v>28</v>
@@ -10589,9 +11118,9 @@
         <v>25310</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B22">
         <v>27</v>
@@ -10603,9 +11132,9 @@
         <v>24660</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B23">
         <v>26</v>
@@ -10617,9 +11146,9 @@
         <v>24010</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B24">
         <v>25</v>
@@ -10631,9 +11160,9 @@
         <v>23360</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B25">
         <v>31</v>
@@ -10645,9 +11174,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B26">
         <v>30</v>
@@ -10659,9 +11188,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B27">
         <v>29</v>
@@ -10673,9 +11202,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B28">
         <v>28</v>
@@ -10687,9 +11216,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B29">
         <v>27</v>
@@ -10701,9 +11230,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B30">
         <v>26</v>
@@ -10715,9 +11244,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B31">
         <v>25</v>
@@ -10729,9 +11258,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B32">
         <v>24</v>
@@ -10743,9 +11272,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B33">
         <v>23</v>
@@ -10757,9 +11286,9 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B34">
         <v>22</v>
@@ -10771,9 +11300,9 @@
         <v>21630</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B35">
         <v>21</v>
@@ -10785,9 +11314,9 @@
         <v>20690</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B36">
         <v>19</v>
@@ -10799,9 +11328,9 @@
         <v>19165</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B37">
         <v>18</v>
@@ -10813,9 +11342,9 @@
         <v>18440</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B38">
         <v>16</v>
@@ -10827,9 +11356,9 @@
         <v>17785</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B39">
         <v>14</v>
@@ -10841,9 +11370,9 @@
         <v>16115</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B40">
         <v>24</v>
@@ -10855,9 +11384,9 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B41">
         <v>22</v>
@@ -10869,9 +11398,9 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B42">
         <v>21</v>
@@ -10883,9 +11412,9 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B43">
         <v>19</v>
@@ -10897,9 +11426,9 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B44">
         <v>18</v>
@@ -10911,9 +11440,9 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B45">
         <v>16</v>
@@ -10925,9 +11454,9 @@
         <v>17750</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B46">
         <v>14</v>

--- a/backend/assets/data/fujitsu_capacities_calculated.xlsx
+++ b/backend/assets/data/fujitsu_capacities_calculated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pardigmpartners-my.sharepoint.com/personal/alex_paradigm-esco_com/Documents/data_operations/ashp_calculator/backend/assets/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="277" documentId="13_ncr:1_{D420F103-AC1D-4B35-A441-D57FBF080E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F283166-8CE5-426D-945D-8A1DD982EAAE}"/>
+  <xr:revisionPtr revIDLastSave="296" documentId="13_ncr:1_{D420F103-AC1D-4B35-A441-D57FBF080E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{153E2128-3854-43EC-A3FF-472A9CE7E92E}"/>
   <bookViews>
-    <workbookView xWindow="42270" yWindow="1540" windowWidth="33310" windowHeight="17110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="1130" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="indoor_combinations" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="38">
   <si>
     <t>Model</t>
   </si>
@@ -143,12 +143,21 @@
   <si>
     <t>Capacity at 70F (Btu/h)</t>
   </si>
+  <si>
+    <t>AOUH30KUAH1</t>
+  </si>
+  <si>
+    <t>AOUH36KUAH1</t>
+  </si>
+  <si>
+    <t>AOUH48KUAH1</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -475,28 +484,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4304B4-14C5-40DF-85A6-AED3FDED911B}">
-  <dimension ref="A1:U183"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:U186"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="5.7109375" customWidth="1"/>
-    <col min="8" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="17.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.7265625" customWidth="1"/>
+    <col min="8" max="9" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="17.453125" customWidth="1"/>
+    <col min="12" max="12" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +567,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -608,7 +617,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -658,7 +667,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -708,7 +717,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -758,7 +767,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -808,7 +817,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -858,7 +867,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -908,7 +917,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -958,7 +967,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -1008,7 +1017,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1058,7 +1067,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1108,7 +1117,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1158,7 +1167,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1208,7 +1217,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -1258,7 +1267,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1311,7 +1320,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -1364,7 +1373,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="18" spans="1:21">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1417,7 +1426,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1470,7 +1479,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1523,7 +1532,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1576,7 +1585,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1629,7 +1638,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1682,7 +1691,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -1735,7 +1744,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -1788,7 +1797,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -1841,7 +1850,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="27" spans="1:21">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -1894,7 +1903,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="28" spans="1:21">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -1947,7 +1956,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="29" spans="1:21">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>23</v>
       </c>
@@ -2005,7 +2014,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="30" spans="1:21">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -2063,7 +2072,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>23</v>
       </c>
@@ -2121,7 +2130,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>23</v>
       </c>
@@ -2179,7 +2188,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>23</v>
       </c>
@@ -2237,7 +2246,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="34" spans="1:21">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>23</v>
       </c>
@@ -2295,7 +2304,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="35" spans="1:21">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>23</v>
       </c>
@@ -2353,7 +2362,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>23</v>
       </c>
@@ -2411,7 +2420,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>23</v>
       </c>
@@ -2469,7 +2478,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="38" spans="1:21">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>23</v>
       </c>
@@ -2527,7 +2536,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>23</v>
       </c>
@@ -2579,7 +2588,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -2631,7 +2640,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="41" spans="1:21">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>23</v>
       </c>
@@ -2683,7 +2692,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="42" spans="1:21">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>23</v>
       </c>
@@ -2735,7 +2744,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="43" spans="1:21">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>23</v>
       </c>
@@ -2787,7 +2796,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="44" spans="1:21">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>23</v>
       </c>
@@ -2839,7 +2848,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="45" spans="1:21">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>23</v>
       </c>
@@ -2891,7 +2900,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>23</v>
       </c>
@@ -2943,7 +2952,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="47" spans="1:21">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>23</v>
       </c>
@@ -2995,7 +3004,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="48" spans="1:21">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>23</v>
       </c>
@@ -3053,7 +3062,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="49" spans="1:21">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>23</v>
       </c>
@@ -3111,7 +3120,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="50" spans="1:21">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>23</v>
       </c>
@@ -3169,7 +3178,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="51" spans="1:21">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>23</v>
       </c>
@@ -3227,7 +3236,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="52" spans="1:21">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -3285,7 +3294,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="53" spans="1:21">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>23</v>
       </c>
@@ -3343,7 +3352,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="54" spans="1:21">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>23</v>
       </c>
@@ -3401,7 +3410,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="55" spans="1:21">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>23</v>
       </c>
@@ -3459,7 +3468,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="56" spans="1:21">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>24</v>
       </c>
@@ -3509,7 +3518,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="57" spans="1:21">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>24</v>
       </c>
@@ -3559,7 +3568,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="58" spans="1:21">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>24</v>
       </c>
@@ -3609,7 +3618,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="59" spans="1:21">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>24</v>
       </c>
@@ -3659,7 +3668,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="60" spans="1:21">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>24</v>
       </c>
@@ -3709,7 +3718,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="61" spans="1:21">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>24</v>
       </c>
@@ -3759,7 +3768,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="62" spans="1:21">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>24</v>
       </c>
@@ -3809,7 +3818,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="63" spans="1:21">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>24</v>
       </c>
@@ -3859,7 +3868,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="64" spans="1:21">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>24</v>
       </c>
@@ -3915,7 +3924,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="65" spans="1:21">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>24</v>
       </c>
@@ -3971,7 +3980,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="66" spans="1:21">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>24</v>
       </c>
@@ -4027,7 +4036,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="67" spans="1:21">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>24</v>
       </c>
@@ -4083,7 +4092,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="68" spans="1:21">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>24</v>
       </c>
@@ -4139,7 +4148,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="69" spans="1:21">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>24</v>
       </c>
@@ -4195,7 +4204,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="70" spans="1:21">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>24</v>
       </c>
@@ -4251,7 +4260,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="71" spans="1:21">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>24</v>
       </c>
@@ -4307,7 +4316,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="72" spans="1:21">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>24</v>
       </c>
@@ -4363,7 +4372,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="73" spans="1:21">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>24</v>
       </c>
@@ -4419,7 +4428,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="74" spans="1:21">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>24</v>
       </c>
@@ -4475,7 +4484,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="75" spans="1:21">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>24</v>
       </c>
@@ -4531,7 +4540,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="76" spans="1:21">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>24</v>
       </c>
@@ -4587,7 +4596,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="77" spans="1:21">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>24</v>
       </c>
@@ -4643,7 +4652,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="78" spans="1:21">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>24</v>
       </c>
@@ -4699,7 +4708,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="79" spans="1:21">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>24</v>
       </c>
@@ -4755,7 +4764,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="80" spans="1:21">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>24</v>
       </c>
@@ -4811,7 +4820,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="81" spans="1:21">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>24</v>
       </c>
@@ -4867,7 +4876,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="82" spans="1:21">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>24</v>
       </c>
@@ -4923,7 +4932,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="83" spans="1:21">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>24</v>
       </c>
@@ -4979,7 +4988,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="84" spans="1:21">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>24</v>
       </c>
@@ -5035,7 +5044,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="85" spans="1:21">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>24</v>
       </c>
@@ -5091,7 +5100,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="86" spans="1:21">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>24</v>
       </c>
@@ -5147,7 +5156,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="87" spans="1:21">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>24</v>
       </c>
@@ -5203,7 +5212,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="88" spans="1:21">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>24</v>
       </c>
@@ -5259,7 +5268,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="89" spans="1:21">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>24</v>
       </c>
@@ -5315,7 +5324,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="90" spans="1:21">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>24</v>
       </c>
@@ -5371,7 +5380,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="91" spans="1:21">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>24</v>
       </c>
@@ -5427,7 +5436,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="92" spans="1:21">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>24</v>
       </c>
@@ -5483,7 +5492,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="93" spans="1:21">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>24</v>
       </c>
@@ -5539,7 +5548,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="94" spans="1:21">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>24</v>
       </c>
@@ -5595,7 +5604,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="95" spans="1:21">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>24</v>
       </c>
@@ -5651,7 +5660,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="96" spans="1:21">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>24</v>
       </c>
@@ -5707,7 +5716,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="97" spans="1:21">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>24</v>
       </c>
@@ -5763,7 +5772,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="98" spans="1:21">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>24</v>
       </c>
@@ -5819,7 +5828,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="99" spans="1:21">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>24</v>
       </c>
@@ -5881,7 +5890,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="100" spans="1:21">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>24</v>
       </c>
@@ -5943,7 +5952,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="101" spans="1:21">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>24</v>
       </c>
@@ -6005,7 +6014,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="102" spans="1:21">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>24</v>
       </c>
@@ -6067,7 +6076,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="103" spans="1:21">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>24</v>
       </c>
@@ -6129,7 +6138,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="104" spans="1:21">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>24</v>
       </c>
@@ -6191,7 +6200,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="105" spans="1:21">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>24</v>
       </c>
@@ -6253,7 +6262,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="106" spans="1:21">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>24</v>
       </c>
@@ -6315,7 +6324,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="107" spans="1:21">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>24</v>
       </c>
@@ -6377,7 +6386,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="108" spans="1:21">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>24</v>
       </c>
@@ -6439,7 +6448,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="109" spans="1:21">
+    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>24</v>
       </c>
@@ -6501,7 +6510,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="110" spans="1:21">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>24</v>
       </c>
@@ -6563,7 +6572,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="111" spans="1:21">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>24</v>
       </c>
@@ -6625,7 +6634,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="112" spans="1:21">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>24</v>
       </c>
@@ -6687,7 +6696,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="113" spans="1:21">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>24</v>
       </c>
@@ -6749,7 +6758,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="114" spans="1:21">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>24</v>
       </c>
@@ -6811,7 +6820,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="115" spans="1:21">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>24</v>
       </c>
@@ -6873,7 +6882,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="116" spans="1:21">
+    <row r="116" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>24</v>
       </c>
@@ -6935,7 +6944,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="117" spans="1:21">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>24</v>
       </c>
@@ -6997,7 +7006,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="118" spans="1:21">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>24</v>
       </c>
@@ -7059,7 +7068,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="119" spans="1:21">
+    <row r="119" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>24</v>
       </c>
@@ -7121,7 +7130,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="120" spans="1:21">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>24</v>
       </c>
@@ -7183,7 +7192,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="121" spans="1:21">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>24</v>
       </c>
@@ -7245,7 +7254,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="122" spans="1:21">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>24</v>
       </c>
@@ -7307,7 +7316,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="123" spans="1:21">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>24</v>
       </c>
@@ -7369,7 +7378,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="124" spans="1:21">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>24</v>
       </c>
@@ -7431,7 +7440,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="125" spans="1:21">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>24</v>
       </c>
@@ -7493,7 +7502,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="126" spans="1:21">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>24</v>
       </c>
@@ -7555,7 +7564,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="127" spans="1:21">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>24</v>
       </c>
@@ -7617,7 +7626,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="128" spans="1:21">
+    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>24</v>
       </c>
@@ -7679,7 +7688,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="129" spans="1:21">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>24</v>
       </c>
@@ -7741,7 +7750,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="130" spans="1:21">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>24</v>
       </c>
@@ -7791,7 +7800,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="131" spans="1:21">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>24</v>
       </c>
@@ -7841,7 +7850,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="132" spans="1:21">
+    <row r="132" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>24</v>
       </c>
@@ -7891,7 +7900,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="133" spans="1:21">
+    <row r="133" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>24</v>
       </c>
@@ -7941,7 +7950,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="134" spans="1:21">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>24</v>
       </c>
@@ -7991,7 +8000,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="135" spans="1:21">
+    <row r="135" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>24</v>
       </c>
@@ -8041,7 +8050,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="136" spans="1:21">
+    <row r="136" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>24</v>
       </c>
@@ -8097,7 +8106,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="137" spans="1:21">
+    <row r="137" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>24</v>
       </c>
@@ -8153,7 +8162,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="138" spans="1:21">
+    <row r="138" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>24</v>
       </c>
@@ -8209,7 +8218,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="139" spans="1:21">
+    <row r="139" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>24</v>
       </c>
@@ -8265,7 +8274,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="140" spans="1:21">
+    <row r="140" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>24</v>
       </c>
@@ -8321,7 +8330,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="141" spans="1:21">
+    <row r="141" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>24</v>
       </c>
@@ -8377,7 +8386,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="142" spans="1:21">
+    <row r="142" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>24</v>
       </c>
@@ -8433,7 +8442,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="143" spans="1:21">
+    <row r="143" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>24</v>
       </c>
@@ -8489,7 +8498,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="144" spans="1:21">
+    <row r="144" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>24</v>
       </c>
@@ -8545,7 +8554,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="145" spans="1:21">
+    <row r="145" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>24</v>
       </c>
@@ -8601,7 +8610,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="146" spans="1:21">
+    <row r="146" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>24</v>
       </c>
@@ -8657,7 +8666,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="147" spans="1:21">
+    <row r="147" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>24</v>
       </c>
@@ -8713,7 +8722,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="148" spans="1:21">
+    <row r="148" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>24</v>
       </c>
@@ -8769,7 +8778,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="149" spans="1:21">
+    <row r="149" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>24</v>
       </c>
@@ -8825,7 +8834,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="150" spans="1:21">
+    <row r="150" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>24</v>
       </c>
@@ -8881,7 +8890,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="151" spans="1:21">
+    <row r="151" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>24</v>
       </c>
@@ -8937,7 +8946,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="152" spans="1:21">
+    <row r="152" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>24</v>
       </c>
@@ -8993,7 +9002,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="153" spans="1:21">
+    <row r="153" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>24</v>
       </c>
@@ -9049,7 +9058,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="154" spans="1:21">
+    <row r="154" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>24</v>
       </c>
@@ -9105,7 +9114,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="155" spans="1:21">
+    <row r="155" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>24</v>
       </c>
@@ -9161,7 +9170,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="156" spans="1:21">
+    <row r="156" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>24</v>
       </c>
@@ -9217,7 +9226,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="157" spans="1:21">
+    <row r="157" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>24</v>
       </c>
@@ -9279,7 +9288,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="158" spans="1:21">
+    <row r="158" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>24</v>
       </c>
@@ -9341,7 +9350,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="159" spans="1:21">
+    <row r="159" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>24</v>
       </c>
@@ -9403,7 +9412,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="160" spans="1:21">
+    <row r="160" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>24</v>
       </c>
@@ -9465,7 +9474,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="161" spans="1:21">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>24</v>
       </c>
@@ -9527,7 +9536,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="162" spans="1:21">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>24</v>
       </c>
@@ -9589,7 +9598,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="163" spans="1:21">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>24</v>
       </c>
@@ -9651,7 +9660,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="164" spans="1:21">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>24</v>
       </c>
@@ -9713,7 +9722,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="165" spans="1:21">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>24</v>
       </c>
@@ -9775,7 +9784,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="166" spans="1:21">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>24</v>
       </c>
@@ -9837,7 +9846,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="167" spans="1:21">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>24</v>
       </c>
@@ -9899,7 +9908,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="168" spans="1:21">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>24</v>
       </c>
@@ -9961,7 +9970,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="169" spans="1:21">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>24</v>
       </c>
@@ -10023,7 +10032,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="170" spans="1:21">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>24</v>
       </c>
@@ -10085,7 +10094,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="171" spans="1:21">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>24</v>
       </c>
@@ -10147,7 +10156,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="172" spans="1:21">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>24</v>
       </c>
@@ -10209,7 +10218,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="173" spans="1:21">
+    <row r="173" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>24</v>
       </c>
@@ -10271,7 +10280,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="174" spans="1:21">
+    <row r="174" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>24</v>
       </c>
@@ -10333,7 +10342,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="175" spans="1:21">
+    <row r="175" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>24</v>
       </c>
@@ -10395,7 +10404,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="176" spans="1:21">
+    <row r="176" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>24</v>
       </c>
@@ -10457,7 +10466,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="177" spans="1:21">
+    <row r="177" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>24</v>
       </c>
@@ -10519,7 +10528,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="178" spans="1:21">
+    <row r="178" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>25</v>
       </c>
@@ -10568,7 +10577,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="179" spans="1:21">
+    <row r="179" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>26</v>
       </c>
@@ -10617,7 +10626,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="180" spans="1:21">
+    <row r="180" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>27</v>
       </c>
@@ -10666,7 +10675,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="181" spans="1:21">
+    <row r="181" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>28</v>
       </c>
@@ -10715,7 +10724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:21">
+    <row r="182" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>29</v>
       </c>
@@ -10764,7 +10773,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="183" spans="1:21">
+    <row r="183" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>30</v>
       </c>
@@ -10811,6 +10820,138 @@
       </c>
       <c r="U183" s="2">
         <v>9.6</v>
+      </c>
+    </row>
+    <row r="184" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>35</v>
+      </c>
+      <c r="B184" t="s">
+        <v>22</v>
+      </c>
+      <c r="C184" s="2">
+        <v>30</v>
+      </c>
+      <c r="D184" s="2">
+        <v>30</v>
+      </c>
+      <c r="H184" s="3">
+        <v>31940</v>
+      </c>
+      <c r="L184" s="3">
+        <v>31940</v>
+      </c>
+      <c r="N184" s="3">
+        <v>6432</v>
+      </c>
+      <c r="O184" s="2">
+        <v>30</v>
+      </c>
+      <c r="P184" s="3">
+        <v>34000</v>
+      </c>
+      <c r="Q184" s="3">
+        <v>31940</v>
+      </c>
+      <c r="R184" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="S184" s="2">
+        <v>18.8</v>
+      </c>
+      <c r="T184" s="2">
+        <v>12.2</v>
+      </c>
+      <c r="U184" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="185" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>36</v>
+      </c>
+      <c r="B185" t="s">
+        <v>22</v>
+      </c>
+      <c r="C185" s="2">
+        <v>36</v>
+      </c>
+      <c r="D185" s="2">
+        <v>36</v>
+      </c>
+      <c r="H185" s="3">
+        <v>38750</v>
+      </c>
+      <c r="L185" s="3">
+        <v>38750</v>
+      </c>
+      <c r="N185" s="3">
+        <v>6720</v>
+      </c>
+      <c r="O185" s="2">
+        <v>35</v>
+      </c>
+      <c r="P185" s="3">
+        <v>41000</v>
+      </c>
+      <c r="Q185" s="3">
+        <v>38750</v>
+      </c>
+      <c r="R185" s="2">
+        <v>3</v>
+      </c>
+      <c r="S185" s="2">
+        <v>18.3</v>
+      </c>
+      <c r="T185" s="2">
+        <v>11.4</v>
+      </c>
+      <c r="U185" s="2">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="186" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>37</v>
+      </c>
+      <c r="B186" t="s">
+        <v>22</v>
+      </c>
+      <c r="C186" s="2">
+        <v>48</v>
+      </c>
+      <c r="D186" s="2">
+        <v>48</v>
+      </c>
+      <c r="H186" s="3">
+        <v>48000</v>
+      </c>
+      <c r="L186" s="3">
+        <v>48000</v>
+      </c>
+      <c r="N186" s="3">
+        <v>8904</v>
+      </c>
+      <c r="O186" s="2">
+        <v>45</v>
+      </c>
+      <c r="P186" s="3">
+        <v>51000</v>
+      </c>
+      <c r="Q186" s="3">
+        <v>48000</v>
+      </c>
+      <c r="R186" s="2">
+        <v>3.79</v>
+      </c>
+      <c r="S186" s="2">
+        <v>19</v>
+      </c>
+      <c r="T186" s="2">
+        <v>11.2</v>
+      </c>
+      <c r="U186" s="2">
+        <v>10.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -10822,15 +10963,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D46"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>31</v>
       </c>
@@ -10838,7 +10979,7 @@
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -10852,7 +10993,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -10866,7 +11007,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -10880,7 +11021,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -10894,7 +11035,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -10908,7 +11049,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -10922,7 +11063,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -10936,7 +11077,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -10950,7 +11091,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -10964,7 +11105,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -10978,7 +11119,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -10992,7 +11133,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -11006,7 +11147,7 @@
         <v>30760</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -11020,7 +11161,7 @@
         <v>29880</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -11034,7 +11175,7 @@
         <v>29260</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -11048,7 +11189,7 @@
         <v>28560</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -11062,7 +11203,7 @@
         <v>27910</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -11076,7 +11217,7 @@
         <v>27260</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -11090,7 +11231,7 @@
         <v>26610</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -11104,7 +11245,7 @@
         <v>25960</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -11118,7 +11259,7 @@
         <v>25310</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -11132,7 +11273,7 @@
         <v>24660</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -11146,7 +11287,7 @@
         <v>24010</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -11160,7 +11301,7 @@
         <v>23360</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -11174,7 +11315,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -11188,7 +11329,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -11202,7 +11343,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -11216,7 +11357,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>23</v>
       </c>
@@ -11230,7 +11371,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -11244,7 +11385,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>23</v>
       </c>
@@ -11258,7 +11399,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>23</v>
       </c>
@@ -11272,7 +11413,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>23</v>
       </c>
@@ -11286,7 +11427,7 @@
         <v>22505</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>23</v>
       </c>
@@ -11300,7 +11441,7 @@
         <v>21630</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>23</v>
       </c>
@@ -11314,7 +11455,7 @@
         <v>20690</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>23</v>
       </c>
@@ -11328,7 +11469,7 @@
         <v>19165</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>23</v>
       </c>
@@ -11342,7 +11483,7 @@
         <v>18440</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>23</v>
       </c>
@@ -11356,7 +11497,7 @@
         <v>17785</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>23</v>
       </c>
@@ -11370,7 +11511,7 @@
         <v>16115</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -11384,7 +11525,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -11398,7 +11539,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>20</v>
       </c>
@@ -11412,7 +11553,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>20</v>
       </c>
@@ -11426,7 +11567,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -11440,7 +11581,7 @@
         <v>19725</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>20</v>
       </c>
@@ -11454,7 +11595,7 @@
         <v>17750</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>20</v>
       </c>

--- a/backend/assets/data/fujitsu_capacities_calculated.xlsx
+++ b/backend/assets/data/fujitsu_capacities_calculated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pardigmpartners-my.sharepoint.com/personal/alex_paradigm-esco_com/Documents/data_operations/ashp_calculator/backend/assets/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="296" documentId="13_ncr:1_{D420F103-AC1D-4B35-A441-D57FBF080E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{153E2128-3854-43EC-A3FF-472A9CE7E92E}"/>
+  <xr:revisionPtr revIDLastSave="302" documentId="13_ncr:1_{D420F103-AC1D-4B35-A441-D57FBF080E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E29A19E0-3F0A-499A-8CA7-95FE708198C1}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="1130" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41780" yWindow="320" windowWidth="30890" windowHeight="17110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="indoor_combinations" sheetId="2" r:id="rId1"/>

--- a/backend/assets/data/fujitsu_capacities_calculated.xlsx
+++ b/backend/assets/data/fujitsu_capacities_calculated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pardigmpartners-my.sharepoint.com/personal/alex_paradigm-esco_com/Documents/data_operations/ashp_calculator/backend/assets/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="315" documentId="13_ncr:1_{D420F103-AC1D-4B35-A441-D57FBF080E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E289441D-E452-43B6-9BDE-7DAA0DA81D85}"/>
+  <xr:revisionPtr revIDLastSave="323" documentId="13_ncr:1_{D420F103-AC1D-4B35-A441-D57FBF080E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2ADA4DA6-6CDF-4987-9DFE-B82EF0220CBB}"/>
   <bookViews>
     <workbookView xWindow="48710" yWindow="260" windowWidth="27700" windowHeight="17110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="42">
   <si>
     <t>Model</t>
   </si>
@@ -102,9 +102,6 @@
     <t>AOUH18KWAH2</t>
   </si>
   <si>
-    <t>Non-ducted</t>
-  </si>
-  <si>
     <t>Ducted</t>
   </si>
   <si>
@@ -153,6 +150,9 @@
     <t>AOUH48KUAH1</t>
   </si>
   <si>
+    <t>AOUH45KWAS5</t>
+  </si>
+  <si>
     <t>Unit 5</t>
   </si>
   <si>
@@ -160,6 +160,9 @@
   </si>
   <si>
     <t>Not Tested</t>
+  </si>
+  <si>
+    <t>Ductless</t>
   </si>
 </sst>
 </file>
@@ -587,7 +590,7 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C2">
         <v>14</v>
@@ -637,7 +640,7 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C3">
         <v>16</v>
@@ -687,7 +690,7 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C4">
         <v>19</v>
@@ -737,7 +740,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C5">
         <v>22</v>
@@ -787,7 +790,7 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C6">
         <v>18</v>
@@ -837,7 +840,7 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C7">
         <v>21</v>
@@ -887,7 +890,7 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C8">
         <v>24</v>
@@ -937,7 +940,7 @@
         <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C9">
         <v>24</v>
@@ -987,7 +990,7 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10">
         <v>14</v>
@@ -1037,7 +1040,7 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11">
         <v>16</v>
@@ -1087,7 +1090,7 @@
         <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12">
         <v>19</v>
@@ -1137,7 +1140,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>18</v>
@@ -1187,7 +1190,7 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14">
         <v>21</v>
@@ -1237,7 +1240,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15">
         <v>24</v>
@@ -1284,10 +1287,10 @@
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>14</v>
@@ -1338,10 +1341,10 @@
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -1392,10 +1395,10 @@
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C18">
         <v>19</v>
@@ -1446,10 +1449,10 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>22</v>
@@ -1500,10 +1503,10 @@
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C20">
         <v>25</v>
@@ -1554,10 +1557,10 @@
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C21">
         <v>18</v>
@@ -1608,10 +1611,10 @@
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C22">
         <v>21</v>
@@ -1662,10 +1665,10 @@
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C23">
         <v>24</v>
@@ -1716,10 +1719,10 @@
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C24">
         <v>27</v>
@@ -1770,10 +1773,10 @@
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C25">
         <v>24</v>
@@ -1824,10 +1827,10 @@
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C26">
         <v>27</v>
@@ -1878,10 +1881,10 @@
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C27">
         <v>30</v>
@@ -1932,10 +1935,10 @@
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C28">
         <v>30</v>
@@ -1986,10 +1989,10 @@
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C29">
         <v>21</v>
@@ -2045,10 +2048,10 @@
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C30">
         <v>23</v>
@@ -2104,10 +2107,10 @@
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C31">
         <v>26</v>
@@ -2163,10 +2166,10 @@
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C32">
         <v>29</v>
@@ -2222,10 +2225,10 @@
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>25</v>
@@ -2281,10 +2284,10 @@
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C34">
         <v>28</v>
@@ -2340,10 +2343,10 @@
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C35">
         <v>31</v>
@@ -2399,10 +2402,10 @@
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C36">
         <v>31</v>
@@ -2458,10 +2461,10 @@
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C37">
         <v>27</v>
@@ -2517,10 +2520,10 @@
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C38">
         <v>30</v>
@@ -2576,10 +2579,10 @@
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C39">
         <v>14</v>
@@ -2630,10 +2633,10 @@
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40">
         <v>16</v>
@@ -2684,10 +2687,10 @@
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C41">
         <v>19</v>
@@ -2738,10 +2741,10 @@
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C42">
         <v>25</v>
@@ -2792,10 +2795,10 @@
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B43" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C43">
         <v>18</v>
@@ -2846,10 +2849,10 @@
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C44">
         <v>21</v>
@@ -2900,10 +2903,10 @@
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C45">
         <v>27</v>
@@ -2954,10 +2957,10 @@
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C46">
         <v>24</v>
@@ -3008,10 +3011,10 @@
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C47">
         <v>30</v>
@@ -3062,10 +3065,10 @@
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C48">
         <v>21</v>
@@ -3122,10 +3125,10 @@
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C49">
         <v>23</v>
@@ -3182,10 +3185,10 @@
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C50">
         <v>26</v>
@@ -3242,10 +3245,10 @@
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C51">
         <v>25</v>
@@ -3302,10 +3305,10 @@
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B52" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C52">
         <v>28</v>
@@ -3362,10 +3365,10 @@
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C53">
         <v>31</v>
@@ -3422,10 +3425,10 @@
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C54">
         <v>27</v>
@@ -3482,10 +3485,10 @@
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C55">
         <v>30</v>
@@ -3542,10 +3545,10 @@
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B56" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C56">
         <v>31</v>
@@ -3592,10 +3595,10 @@
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B57" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C57">
         <v>33</v>
@@ -3642,10 +3645,10 @@
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B58" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C58">
         <v>30</v>
@@ -3692,10 +3695,10 @@
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B59" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C59">
         <v>36</v>
@@ -3742,10 +3745,10 @@
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B60" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C60">
         <v>33</v>
@@ -3792,10 +3795,10 @@
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B61" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C61">
         <v>39</v>
@@ -3842,10 +3845,10 @@
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B62" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C62">
         <v>36</v>
@@ -3892,10 +3895,10 @@
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B63" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C63">
         <v>42</v>
@@ -3942,10 +3945,10 @@
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B64" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C64">
         <v>26</v>
@@ -3998,10 +4001,10 @@
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B65" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C65">
         <v>29</v>
@@ -4054,10 +4057,10 @@
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B66" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C66">
         <v>32</v>
@@ -4110,10 +4113,10 @@
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B67" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C67">
         <v>38</v>
@@ -4166,10 +4169,10 @@
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B68" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C68">
         <v>25</v>
@@ -4222,10 +4225,10 @@
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B69" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C69">
         <v>28</v>
@@ -4278,10 +4281,10 @@
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B70" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C70">
         <v>31</v>
@@ -4334,10 +4337,10 @@
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B71" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C71">
         <v>34</v>
@@ -4390,10 +4393,10 @@
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B72" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C72">
         <v>40</v>
@@ -4446,10 +4449,10 @@
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B73" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C73">
         <v>31</v>
@@ -4502,10 +4505,10 @@
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B74" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C74">
         <v>34</v>
@@ -4558,10 +4561,10 @@
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B75" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C75">
         <v>37</v>
@@ -4614,10 +4617,10 @@
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B76" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C76">
         <v>43</v>
@@ -4670,10 +4673,10 @@
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B77" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C77">
         <v>37</v>
@@ -4726,10 +4729,10 @@
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B78" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C78">
         <v>40</v>
@@ -4782,10 +4785,10 @@
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B79" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C79">
         <v>46</v>
@@ -4838,10 +4841,10 @@
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B80" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C80">
         <v>43</v>
@@ -4894,10 +4897,10 @@
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B81" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C81">
         <v>27</v>
@@ -4950,10 +4953,10 @@
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B82" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C82">
         <v>30</v>
@@ -5006,10 +5009,10 @@
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B83" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C83">
         <v>33</v>
@@ -5062,10 +5065,10 @@
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B84" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C84">
         <v>36</v>
@@ -5118,10 +5121,10 @@
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B85" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C85">
         <v>42</v>
@@ -5174,10 +5177,10 @@
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B86" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C86">
         <v>33</v>
@@ -5230,10 +5233,10 @@
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B87" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C87">
         <v>36</v>
@@ -5286,10 +5289,10 @@
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B88" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C88">
         <v>39</v>
@@ -5342,10 +5345,10 @@
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B89" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C89">
         <v>45</v>
@@ -5398,10 +5401,10 @@
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B90" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C90">
         <v>39</v>
@@ -5454,10 +5457,10 @@
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B91" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C91">
         <v>42</v>
@@ -5510,10 +5513,10 @@
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B92" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C92">
         <v>45</v>
@@ -5566,10 +5569,10 @@
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B93" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C93">
         <v>36</v>
@@ -5622,10 +5625,10 @@
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B94" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C94">
         <v>39</v>
@@ -5678,10 +5681,10 @@
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B95" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C95">
         <v>42</v>
@@ -5734,10 +5737,10 @@
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B96" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C96">
         <v>42</v>
@@ -5790,10 +5793,10 @@
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B97" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C97">
         <v>45</v>
@@ -5846,10 +5849,10 @@
     </row>
     <row r="98" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B98" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C98">
         <v>45</v>
@@ -5902,10 +5905,10 @@
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B99" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C99">
         <v>28</v>
@@ -5965,10 +5968,10 @@
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B100" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C100">
         <v>30</v>
@@ -6028,10 +6031,10 @@
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B101" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C101">
         <v>33</v>
@@ -6091,10 +6094,10 @@
     </row>
     <row r="102" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B102" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C102">
         <v>36</v>
@@ -6154,10 +6157,10 @@
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B103" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C103">
         <v>39</v>
@@ -6217,10 +6220,10 @@
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B104" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C104">
         <v>45</v>
@@ -6280,10 +6283,10 @@
     </row>
     <row r="105" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B105" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C105">
         <v>32</v>
@@ -6343,10 +6346,10 @@
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B106" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C106">
         <v>35</v>
@@ -6406,10 +6409,10 @@
     </row>
     <row r="107" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B107" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C107">
         <v>38</v>
@@ -6469,10 +6472,10 @@
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B108" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C108">
         <v>41</v>
@@ -6532,10 +6535,10 @@
     </row>
     <row r="109" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B109" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C109">
         <v>38</v>
@@ -6595,10 +6598,10 @@
     </row>
     <row r="110" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B110" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C110">
         <v>41</v>
@@ -6658,10 +6661,10 @@
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B111" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C111">
         <v>44</v>
@@ -6721,10 +6724,10 @@
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B112" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C112">
         <v>44</v>
@@ -6784,10 +6787,10 @@
     </row>
     <row r="113" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B113" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C113">
         <v>34</v>
@@ -6847,10 +6850,10 @@
     </row>
     <row r="114" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B114" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C114">
         <v>37</v>
@@ -6910,10 +6913,10 @@
     </row>
     <row r="115" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B115" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C115">
         <v>40</v>
@@ -6973,10 +6976,10 @@
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B116" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C116">
         <v>43</v>
@@ -7036,10 +7039,10 @@
     </row>
     <row r="117" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B117" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C117">
         <v>40</v>
@@ -7099,10 +7102,10 @@
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B118" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C118">
         <v>43</v>
@@ -7162,10 +7165,10 @@
     </row>
     <row r="119" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B119" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C119">
         <v>46</v>
@@ -7225,10 +7228,10 @@
     </row>
     <row r="120" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B120" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C120">
         <v>46</v>
@@ -7288,10 +7291,10 @@
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B121" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C121">
         <v>43</v>
@@ -7351,10 +7354,10 @@
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B122" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C122">
         <v>46</v>
@@ -7414,10 +7417,10 @@
     </row>
     <row r="123" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B123" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C123">
         <v>36</v>
@@ -7477,10 +7480,10 @@
     </row>
     <row r="124" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B124" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C124">
         <v>39</v>
@@ -7540,10 +7543,10 @@
     </row>
     <row r="125" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B125" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C125">
         <v>42</v>
@@ -7603,10 +7606,10 @@
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B126" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C126">
         <v>45</v>
@@ -7666,10 +7669,10 @@
     </row>
     <row r="127" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B127" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C127">
         <v>42</v>
@@ -7729,10 +7732,10 @@
     </row>
     <row r="128" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B128" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C128">
         <v>45</v>
@@ -7792,10 +7795,10 @@
     </row>
     <row r="129" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B129" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C129">
         <v>45</v>
@@ -7855,10 +7858,10 @@
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B130" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C130">
         <v>31</v>
@@ -7905,10 +7908,10 @@
     </row>
     <row r="131" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B131" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C131">
         <v>33</v>
@@ -7955,10 +7958,10 @@
     </row>
     <row r="132" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B132" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C132">
         <v>30</v>
@@ -8005,10 +8008,10 @@
     </row>
     <row r="133" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B133" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C133">
         <v>36</v>
@@ -8055,10 +8058,10 @@
     </row>
     <row r="134" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B134" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C134">
         <v>36</v>
@@ -8105,10 +8108,10 @@
     </row>
     <row r="135" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B135" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C135">
         <v>42</v>
@@ -8155,10 +8158,10 @@
     </row>
     <row r="136" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B136" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C136">
         <v>26</v>
@@ -8211,10 +8214,10 @@
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B137" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C137">
         <v>32</v>
@@ -8267,10 +8270,10 @@
     </row>
     <row r="138" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B138" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C138">
         <v>38</v>
@@ -8323,10 +8326,10 @@
     </row>
     <row r="139" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B139" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C139">
         <v>25</v>
@@ -8379,10 +8382,10 @@
     </row>
     <row r="140" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B140" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C140">
         <v>28</v>
@@ -8435,10 +8438,10 @@
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B141" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C141">
         <v>34</v>
@@ -8491,10 +8494,10 @@
     </row>
     <row r="142" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B142" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C142">
         <v>40</v>
@@ -8547,10 +8550,10 @@
     </row>
     <row r="143" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B143" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C143">
         <v>31</v>
@@ -8603,10 +8606,10 @@
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B144" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C144">
         <v>37</v>
@@ -8659,10 +8662,10 @@
     </row>
     <row r="145" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B145" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C145">
         <v>43</v>
@@ -8715,10 +8718,10 @@
     </row>
     <row r="146" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B146" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C146">
         <v>43</v>
@@ -8771,10 +8774,10 @@
     </row>
     <row r="147" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B147" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C147">
         <v>27</v>
@@ -8827,10 +8830,10 @@
     </row>
     <row r="148" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B148" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C148">
         <v>30</v>
@@ -8883,10 +8886,10 @@
     </row>
     <row r="149" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B149" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C149">
         <v>36</v>
@@ -8939,10 +8942,10 @@
     </row>
     <row r="150" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B150" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C150">
         <v>42</v>
@@ -8995,10 +8998,10 @@
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B151" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C151">
         <v>33</v>
@@ -9051,10 +9054,10 @@
     </row>
     <row r="152" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B152" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C152">
         <v>39</v>
@@ -9107,10 +9110,10 @@
     </row>
     <row r="153" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B153" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C153">
         <v>45</v>
@@ -9163,10 +9166,10 @@
     </row>
     <row r="154" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B154" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C154">
         <v>45</v>
@@ -9219,10 +9222,10 @@
     </row>
     <row r="155" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B155" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C155">
         <v>36</v>
@@ -9275,10 +9278,10 @@
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B156" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C156">
         <v>42</v>
@@ -9331,10 +9334,10 @@
     </row>
     <row r="157" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B157" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C157">
         <v>28</v>
@@ -9394,10 +9397,10 @@
     </row>
     <row r="158" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B158" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C158">
         <v>30</v>
@@ -9457,10 +9460,10 @@
     </row>
     <row r="159" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B159" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C159">
         <v>33</v>
@@ -9520,10 +9523,10 @@
     </row>
     <row r="160" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B160" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C160">
         <v>39</v>
@@ -9583,10 +9586,10 @@
     </row>
     <row r="161" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B161" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C161">
         <v>45</v>
@@ -9646,10 +9649,10 @@
     </row>
     <row r="162" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B162" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C162">
         <v>32</v>
@@ -9709,10 +9712,10 @@
     </row>
     <row r="163" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B163" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C163">
         <v>35</v>
@@ -9772,10 +9775,10 @@
     </row>
     <row r="164" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B164" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C164">
         <v>41</v>
@@ -9835,10 +9838,10 @@
     </row>
     <row r="165" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B165" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C165">
         <v>38</v>
@@ -9898,10 +9901,10 @@
     </row>
     <row r="166" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B166" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C166">
         <v>44</v>
@@ -9961,10 +9964,10 @@
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B167" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C167">
         <v>34</v>
@@ -10024,10 +10027,10 @@
     </row>
     <row r="168" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B168" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C168">
         <v>37</v>
@@ -10087,10 +10090,10 @@
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B169" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C169">
         <v>43</v>
@@ -10150,10 +10153,10 @@
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B170" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C170">
         <v>40</v>
@@ -10213,10 +10216,10 @@
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B171" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C171">
         <v>46</v>
@@ -10276,10 +10279,10 @@
     </row>
     <row r="172" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B172" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C172">
         <v>43</v>
@@ -10339,10 +10342,10 @@
     </row>
     <row r="173" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B173" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C173">
         <v>36</v>
@@ -10402,10 +10405,10 @@
     </row>
     <row r="174" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B174" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C174">
         <v>39</v>
@@ -10465,10 +10468,10 @@
     </row>
     <row r="175" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B175" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C175">
         <v>45</v>
@@ -10528,10 +10531,10 @@
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B176" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C176">
         <v>42</v>
@@ -10591,10 +10594,10 @@
     </row>
     <row r="177" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B177" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C177">
         <v>45</v>
@@ -10654,10 +10657,10 @@
     </row>
     <row r="178" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B178" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C178" s="2">
         <v>12</v>
@@ -10704,10 +10707,10 @@
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B179" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C179" s="2">
         <v>18</v>
@@ -10754,10 +10757,10 @@
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B180" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C180" s="2">
         <v>24</v>
@@ -10804,10 +10807,10 @@
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B181" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C181" s="2">
         <v>30</v>
@@ -10854,10 +10857,10 @@
     </row>
     <row r="182" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B182" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C182" s="2">
         <v>36</v>
@@ -10904,10 +10907,10 @@
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B183" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C183" s="2">
         <v>48</v>
@@ -10954,10 +10957,10 @@
     </row>
     <row r="184" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B184" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C184" s="2">
         <v>30</v>
@@ -10998,10 +11001,10 @@
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B185" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C185" s="2">
         <v>36</v>
@@ -11042,10 +11045,10 @@
     </row>
     <row r="186" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B186" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C186" s="2">
         <v>48</v>
@@ -11085,6 +11088,12 @@
       </c>
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>37</v>
+      </c>
+      <c r="B187" t="s">
+        <v>41</v>
+      </c>
       <c r="C187">
         <v>34</v>
       </c>
@@ -11129,6 +11138,12 @@
       </c>
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>37</v>
+      </c>
+      <c r="B188" t="s">
+        <v>41</v>
+      </c>
       <c r="C188">
         <v>34</v>
       </c>
@@ -11173,6 +11188,12 @@
       </c>
     </row>
     <row r="189" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>37</v>
+      </c>
+      <c r="B189" t="s">
+        <v>41</v>
+      </c>
       <c r="C189">
         <v>34</v>
       </c>
@@ -11217,6 +11238,12 @@
       </c>
     </row>
     <row r="190" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>37</v>
+      </c>
+      <c r="B190" t="s">
+        <v>41</v>
+      </c>
       <c r="C190">
         <v>35</v>
       </c>
@@ -11261,6 +11288,12 @@
       </c>
     </row>
     <row r="191" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>37</v>
+      </c>
+      <c r="B191" t="s">
+        <v>41</v>
+      </c>
       <c r="C191">
         <v>35</v>
       </c>
@@ -11305,6 +11338,12 @@
       </c>
     </row>
     <row r="192" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>37</v>
+      </c>
+      <c r="B192" t="s">
+        <v>41</v>
+      </c>
       <c r="C192">
         <v>36</v>
       </c>
@@ -11348,7 +11387,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="193" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>37</v>
+      </c>
+      <c r="B193" t="s">
+        <v>41</v>
+      </c>
       <c r="C193">
         <v>36</v>
       </c>
@@ -11392,7 +11437,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="194" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>37</v>
+      </c>
+      <c r="B194" t="s">
+        <v>41</v>
+      </c>
       <c r="C194">
         <v>36</v>
       </c>
@@ -11436,7 +11487,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="195" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>37</v>
+      </c>
+      <c r="B195" t="s">
+        <v>41</v>
+      </c>
       <c r="C195">
         <v>36</v>
       </c>
@@ -11480,7 +11537,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="196" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>37</v>
+      </c>
+      <c r="B196" t="s">
+        <v>41</v>
+      </c>
       <c r="C196">
         <v>36</v>
       </c>
@@ -11524,7 +11587,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="197" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>37</v>
+      </c>
+      <c r="B197" t="s">
+        <v>41</v>
+      </c>
       <c r="C197">
         <v>36</v>
       </c>
@@ -11568,7 +11637,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="198" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>37</v>
+      </c>
+      <c r="B198" t="s">
+        <v>41</v>
+      </c>
       <c r="C198">
         <v>36</v>
       </c>
@@ -11612,7 +11687,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="199" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>37</v>
+      </c>
+      <c r="B199" t="s">
+        <v>41</v>
+      </c>
       <c r="C199">
         <v>37</v>
       </c>
@@ -11656,7 +11737,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="200" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>37</v>
+      </c>
+      <c r="B200" t="s">
+        <v>41</v>
+      </c>
       <c r="C200">
         <v>37</v>
       </c>
@@ -11700,7 +11787,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="201" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>37</v>
+      </c>
+      <c r="B201" t="s">
+        <v>41</v>
+      </c>
       <c r="C201">
         <v>37</v>
       </c>
@@ -11744,7 +11837,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="202" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>37</v>
+      </c>
+      <c r="B202" t="s">
+        <v>41</v>
+      </c>
       <c r="C202">
         <v>37</v>
       </c>
@@ -11788,7 +11887,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="203" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>37</v>
+      </c>
+      <c r="B203" t="s">
+        <v>41</v>
+      </c>
       <c r="C203">
         <v>38</v>
       </c>
@@ -11832,7 +11937,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="204" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>37</v>
+      </c>
+      <c r="B204" t="s">
+        <v>41</v>
+      </c>
       <c r="C204">
         <v>38</v>
       </c>
@@ -11876,7 +11987,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="205" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>37</v>
+      </c>
+      <c r="B205" t="s">
+        <v>41</v>
+      </c>
       <c r="C205">
         <v>38</v>
       </c>
@@ -11920,7 +12037,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="206" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>37</v>
+      </c>
+      <c r="B206" t="s">
+        <v>41</v>
+      </c>
       <c r="C206">
         <v>39</v>
       </c>
@@ -11964,7 +12087,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="207" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>37</v>
+      </c>
+      <c r="B207" t="s">
+        <v>41</v>
+      </c>
       <c r="C207">
         <v>39</v>
       </c>
@@ -12008,7 +12137,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="208" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>37</v>
+      </c>
+      <c r="B208" t="s">
+        <v>41</v>
+      </c>
       <c r="C208">
         <v>39</v>
       </c>
@@ -12052,7 +12187,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="209" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>37</v>
+      </c>
+      <c r="B209" t="s">
+        <v>41</v>
+      </c>
       <c r="C209">
         <v>39</v>
       </c>
@@ -12096,7 +12237,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="210" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>37</v>
+      </c>
+      <c r="B210" t="s">
+        <v>41</v>
+      </c>
       <c r="C210">
         <v>39</v>
       </c>
@@ -12140,7 +12287,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="211" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>37</v>
+      </c>
+      <c r="B211" t="s">
+        <v>41</v>
+      </c>
       <c r="C211">
         <v>39</v>
       </c>
@@ -12184,7 +12337,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="212" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>37</v>
+      </c>
+      <c r="B212" t="s">
+        <v>41</v>
+      </c>
       <c r="C212">
         <v>39</v>
       </c>
@@ -12228,7 +12387,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="213" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>37</v>
+      </c>
+      <c r="B213" t="s">
+        <v>41</v>
+      </c>
       <c r="C213">
         <v>40</v>
       </c>
@@ -12272,7 +12437,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="214" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>37</v>
+      </c>
+      <c r="B214" t="s">
+        <v>41</v>
+      </c>
       <c r="C214">
         <v>40</v>
       </c>
@@ -12316,7 +12487,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="215" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>37</v>
+      </c>
+      <c r="B215" t="s">
+        <v>41</v>
+      </c>
       <c r="C215">
         <v>40</v>
       </c>
@@ -12360,7 +12537,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="216" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>37</v>
+      </c>
+      <c r="B216" t="s">
+        <v>41</v>
+      </c>
       <c r="C216">
         <v>40</v>
       </c>
@@ -12404,7 +12587,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="217" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>37</v>
+      </c>
+      <c r="B217" t="s">
+        <v>41</v>
+      </c>
       <c r="C217">
         <v>40</v>
       </c>
@@ -12448,7 +12637,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="218" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>37</v>
+      </c>
+      <c r="B218" t="s">
+        <v>41</v>
+      </c>
       <c r="C218">
         <v>41</v>
       </c>
@@ -12492,7 +12687,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="219" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>37</v>
+      </c>
+      <c r="B219" t="s">
+        <v>41</v>
+      </c>
       <c r="C219">
         <v>41</v>
       </c>
@@ -12536,7 +12737,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="220" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>37</v>
+      </c>
+      <c r="B220" t="s">
+        <v>41</v>
+      </c>
       <c r="C220">
         <v>41</v>
       </c>
@@ -12580,7 +12787,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="221" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>37</v>
+      </c>
+      <c r="B221" t="s">
+        <v>41</v>
+      </c>
       <c r="C221">
         <v>42</v>
       </c>
@@ -12624,7 +12837,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="222" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>37</v>
+      </c>
+      <c r="B222" t="s">
+        <v>41</v>
+      </c>
       <c r="C222">
         <v>42</v>
       </c>
@@ -12668,7 +12887,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="223" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>37</v>
+      </c>
+      <c r="B223" t="s">
+        <v>41</v>
+      </c>
       <c r="C223">
         <v>42</v>
       </c>
@@ -12712,7 +12937,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="224" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>37</v>
+      </c>
+      <c r="B224" t="s">
+        <v>41</v>
+      </c>
       <c r="C224">
         <v>42</v>
       </c>
@@ -12756,7 +12987,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="225" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>37</v>
+      </c>
+      <c r="B225" t="s">
+        <v>41</v>
+      </c>
       <c r="C225">
         <v>42</v>
       </c>
@@ -12800,7 +13037,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>37</v>
+      </c>
+      <c r="B226" t="s">
+        <v>41</v>
+      </c>
       <c r="C226">
         <v>42</v>
       </c>
@@ -12844,7 +13087,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="227" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>37</v>
+      </c>
+      <c r="B227" t="s">
+        <v>41</v>
+      </c>
       <c r="C227">
         <v>42</v>
       </c>
@@ -12888,7 +13137,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="228" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>37</v>
+      </c>
+      <c r="B228" t="s">
+        <v>41</v>
+      </c>
       <c r="C228">
         <v>42</v>
       </c>
@@ -12932,7 +13187,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="229" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>37</v>
+      </c>
+      <c r="B229" t="s">
+        <v>41</v>
+      </c>
       <c r="C229">
         <v>43</v>
       </c>
@@ -12976,7 +13237,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="230" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>37</v>
+      </c>
+      <c r="B230" t="s">
+        <v>41</v>
+      </c>
       <c r="C230">
         <v>43</v>
       </c>
@@ -13020,7 +13287,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="231" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>37</v>
+      </c>
+      <c r="B231" t="s">
+        <v>41</v>
+      </c>
       <c r="C231">
         <v>43</v>
       </c>
@@ -13064,7 +13337,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="232" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>37</v>
+      </c>
+      <c r="B232" t="s">
+        <v>41</v>
+      </c>
       <c r="C232">
         <v>43</v>
       </c>
@@ -13108,7 +13387,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="233" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>37</v>
+      </c>
+      <c r="B233" t="s">
+        <v>41</v>
+      </c>
       <c r="C233">
         <v>43</v>
       </c>
@@ -13152,7 +13437,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="234" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>37</v>
+      </c>
+      <c r="B234" t="s">
+        <v>41</v>
+      </c>
       <c r="C234">
         <v>43</v>
       </c>
@@ -13196,7 +13487,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="235" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>37</v>
+      </c>
+      <c r="B235" t="s">
+        <v>41</v>
+      </c>
       <c r="C235">
         <v>43</v>
       </c>
@@ -13240,7 +13537,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="236" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>37</v>
+      </c>
+      <c r="B236" t="s">
+        <v>41</v>
+      </c>
       <c r="C236">
         <v>44</v>
       </c>
@@ -13284,7 +13587,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="237" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>37</v>
+      </c>
+      <c r="B237" t="s">
+        <v>41</v>
+      </c>
       <c r="C237">
         <v>44</v>
       </c>
@@ -13328,7 +13637,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="238" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>37</v>
+      </c>
+      <c r="B238" t="s">
+        <v>41</v>
+      </c>
       <c r="C238">
         <v>44</v>
       </c>
@@ -13372,7 +13687,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="239" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>37</v>
+      </c>
+      <c r="B239" t="s">
+        <v>41</v>
+      </c>
       <c r="C239">
         <v>45</v>
       </c>
@@ -13416,7 +13737,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="240" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>37</v>
+      </c>
+      <c r="B240" t="s">
+        <v>41</v>
+      </c>
       <c r="C240">
         <v>45</v>
       </c>
@@ -13460,7 +13787,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="241" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>37</v>
+      </c>
+      <c r="B241" t="s">
+        <v>41</v>
+      </c>
       <c r="C241">
         <v>45</v>
       </c>
@@ -13504,7 +13837,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="242" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>37</v>
+      </c>
+      <c r="B242" t="s">
+        <v>41</v>
+      </c>
       <c r="C242">
         <v>45</v>
       </c>
@@ -13548,7 +13887,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="243" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>37</v>
+      </c>
+      <c r="B243" t="s">
+        <v>41</v>
+      </c>
       <c r="C243">
         <v>45</v>
       </c>
@@ -13592,7 +13937,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="244" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>37</v>
+      </c>
+      <c r="B244" t="s">
+        <v>41</v>
+      </c>
       <c r="C244">
         <v>45</v>
       </c>
@@ -13636,7 +13987,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="245" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>37</v>
+      </c>
+      <c r="B245" t="s">
+        <v>41</v>
+      </c>
       <c r="C245">
         <v>45</v>
       </c>
@@ -13680,7 +14037,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="246" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>37</v>
+      </c>
+      <c r="B246" t="s">
+        <v>41</v>
+      </c>
       <c r="C246">
         <v>45</v>
       </c>
@@ -13724,7 +14087,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="247" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>37</v>
+      </c>
+      <c r="B247" t="s">
+        <v>41</v>
+      </c>
       <c r="C247">
         <v>45</v>
       </c>
@@ -13768,7 +14137,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="248" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>37</v>
+      </c>
+      <c r="B248" t="s">
+        <v>41</v>
+      </c>
       <c r="C248">
         <v>45</v>
       </c>
@@ -13812,7 +14187,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="249" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>37</v>
+      </c>
+      <c r="B249" t="s">
+        <v>41</v>
+      </c>
       <c r="C249">
         <v>45</v>
       </c>
@@ -13856,7 +14237,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="250" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>37</v>
+      </c>
+      <c r="B250" t="s">
+        <v>41</v>
+      </c>
       <c r="C250">
         <v>46</v>
       </c>
@@ -13900,7 +14287,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="251" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>37</v>
+      </c>
+      <c r="B251" t="s">
+        <v>41</v>
+      </c>
       <c r="C251">
         <v>46</v>
       </c>
@@ -13944,7 +14337,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="252" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>37</v>
+      </c>
+      <c r="B252" t="s">
+        <v>41</v>
+      </c>
       <c r="C252">
         <v>46</v>
       </c>
@@ -13988,7 +14387,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="253" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>37</v>
+      </c>
+      <c r="B253" t="s">
+        <v>41</v>
+      </c>
       <c r="C253">
         <v>46</v>
       </c>
@@ -14032,7 +14437,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="254" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>37</v>
+      </c>
+      <c r="B254" t="s">
+        <v>41</v>
+      </c>
       <c r="C254">
         <v>46</v>
       </c>
@@ -14076,7 +14487,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="255" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>37</v>
+      </c>
+      <c r="B255" t="s">
+        <v>41</v>
+      </c>
       <c r="C255">
         <v>46</v>
       </c>
@@ -14120,7 +14537,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="256" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>37</v>
+      </c>
+      <c r="B256" t="s">
+        <v>41</v>
+      </c>
       <c r="C256">
         <v>47</v>
       </c>
@@ -14164,7 +14587,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="257" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>37</v>
+      </c>
+      <c r="B257" t="s">
+        <v>41</v>
+      </c>
       <c r="C257">
         <v>47</v>
       </c>
@@ -14208,7 +14637,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="258" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>37</v>
+      </c>
+      <c r="B258" t="s">
+        <v>41</v>
+      </c>
       <c r="C258">
         <v>47</v>
       </c>
@@ -14252,7 +14687,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="259" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>37</v>
+      </c>
+      <c r="B259" t="s">
+        <v>41</v>
+      </c>
       <c r="C259">
         <v>47</v>
       </c>
@@ -14296,7 +14737,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="260" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>37</v>
+      </c>
+      <c r="B260" t="s">
+        <v>41</v>
+      </c>
       <c r="C260">
         <v>48</v>
       </c>
@@ -14340,7 +14787,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="261" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>37</v>
+      </c>
+      <c r="B261" t="s">
+        <v>41</v>
+      </c>
       <c r="C261">
         <v>48</v>
       </c>
@@ -14384,7 +14837,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="262" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>37</v>
+      </c>
+      <c r="B262" t="s">
+        <v>41</v>
+      </c>
       <c r="C262">
         <v>48</v>
       </c>
@@ -14428,7 +14887,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="263" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>37</v>
+      </c>
+      <c r="B263" t="s">
+        <v>41</v>
+      </c>
       <c r="C263">
         <v>48</v>
       </c>
@@ -14472,7 +14937,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="264" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>37</v>
+      </c>
+      <c r="B264" t="s">
+        <v>41</v>
+      </c>
       <c r="C264">
         <v>48</v>
       </c>
@@ -14516,7 +14987,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="265" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>37</v>
+      </c>
+      <c r="B265" t="s">
+        <v>41</v>
+      </c>
       <c r="C265">
         <v>48</v>
       </c>
@@ -14560,7 +15037,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="266" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>37</v>
+      </c>
+      <c r="B266" t="s">
+        <v>41</v>
+      </c>
       <c r="C266">
         <v>48</v>
       </c>
@@ -14604,7 +15087,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="267" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
+        <v>37</v>
+      </c>
+      <c r="B267" t="s">
+        <v>41</v>
+      </c>
       <c r="C267">
         <v>48</v>
       </c>
@@ -14648,7 +15137,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="268" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
+        <v>37</v>
+      </c>
+      <c r="B268" t="s">
+        <v>41</v>
+      </c>
       <c r="C268">
         <v>48</v>
       </c>
@@ -14692,7 +15187,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="269" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
+        <v>37</v>
+      </c>
+      <c r="B269" t="s">
+        <v>41</v>
+      </c>
       <c r="C269">
         <v>48</v>
       </c>
@@ -14736,7 +15237,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="270" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
+        <v>37</v>
+      </c>
+      <c r="B270" t="s">
+        <v>41</v>
+      </c>
       <c r="C270">
         <v>48</v>
       </c>
@@ -14780,7 +15287,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="271" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
+        <v>37</v>
+      </c>
+      <c r="B271" t="s">
+        <v>41</v>
+      </c>
       <c r="C271">
         <v>48</v>
       </c>
@@ -14824,7 +15337,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="272" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
+        <v>37</v>
+      </c>
+      <c r="B272" t="s">
+        <v>41</v>
+      </c>
       <c r="C272">
         <v>49</v>
       </c>
@@ -14868,7 +15387,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="273" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>37</v>
+      </c>
+      <c r="B273" t="s">
+        <v>41</v>
+      </c>
       <c r="C273">
         <v>49</v>
       </c>
@@ -14912,7 +15437,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="274" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>37</v>
+      </c>
+      <c r="B274" t="s">
+        <v>41</v>
+      </c>
       <c r="C274">
         <v>49</v>
       </c>
@@ -14956,7 +15487,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="275" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>37</v>
+      </c>
+      <c r="B275" t="s">
+        <v>41</v>
+      </c>
       <c r="C275">
         <v>49</v>
       </c>
@@ -15000,7 +15537,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="276" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>37</v>
+      </c>
+      <c r="B276" t="s">
+        <v>41</v>
+      </c>
       <c r="C276">
         <v>49</v>
       </c>
@@ -15044,7 +15587,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="277" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>37</v>
+      </c>
+      <c r="B277" t="s">
+        <v>41</v>
+      </c>
       <c r="C277">
         <v>49</v>
       </c>
@@ -15088,7 +15637,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="278" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>37</v>
+      </c>
+      <c r="B278" t="s">
+        <v>41</v>
+      </c>
       <c r="C278">
         <v>49</v>
       </c>
@@ -15132,7 +15687,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="279" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>37</v>
+      </c>
+      <c r="B279" t="s">
+        <v>41</v>
+      </c>
       <c r="C279">
         <v>50</v>
       </c>
@@ -15176,7 +15737,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="280" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>37</v>
+      </c>
+      <c r="B280" t="s">
+        <v>41</v>
+      </c>
       <c r="C280">
         <v>50</v>
       </c>
@@ -15220,7 +15787,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="281" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>37</v>
+      </c>
+      <c r="B281" t="s">
+        <v>41</v>
+      </c>
       <c r="C281">
         <v>50</v>
       </c>
@@ -15264,7 +15837,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="282" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>37</v>
+      </c>
+      <c r="B282" t="s">
+        <v>41</v>
+      </c>
       <c r="C282">
         <v>50</v>
       </c>
@@ -15308,7 +15887,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="283" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>37</v>
+      </c>
+      <c r="B283" t="s">
+        <v>41</v>
+      </c>
       <c r="C283">
         <v>50</v>
       </c>
@@ -15352,7 +15937,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="284" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>37</v>
+      </c>
+      <c r="B284" t="s">
+        <v>41</v>
+      </c>
       <c r="C284">
         <v>51</v>
       </c>
@@ -15396,7 +15987,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="285" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>37</v>
+      </c>
+      <c r="B285" t="s">
+        <v>41</v>
+      </c>
       <c r="C285">
         <v>51</v>
       </c>
@@ -15440,7 +16037,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="286" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>37</v>
+      </c>
+      <c r="B286" t="s">
+        <v>41</v>
+      </c>
       <c r="C286">
         <v>51</v>
       </c>
@@ -15484,7 +16087,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="287" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>37</v>
+      </c>
+      <c r="B287" t="s">
+        <v>41</v>
+      </c>
       <c r="C287">
         <v>51</v>
       </c>
@@ -15528,7 +16137,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="288" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>37</v>
+      </c>
+      <c r="B288" t="s">
+        <v>41</v>
+      </c>
       <c r="C288">
         <v>51</v>
       </c>
@@ -15572,7 +16187,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="289" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>37</v>
+      </c>
+      <c r="B289" t="s">
+        <v>41</v>
+      </c>
       <c r="C289">
         <v>51</v>
       </c>
@@ -15616,7 +16237,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="290" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>37</v>
+      </c>
+      <c r="B290" t="s">
+        <v>41</v>
+      </c>
       <c r="C290">
         <v>51</v>
       </c>
@@ -15660,7 +16287,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="291" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>37</v>
+      </c>
+      <c r="B291" t="s">
+        <v>41</v>
+      </c>
       <c r="C291">
         <v>51</v>
       </c>
@@ -15704,7 +16337,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="292" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>37</v>
+      </c>
+      <c r="B292" t="s">
+        <v>41</v>
+      </c>
       <c r="C292">
         <v>51</v>
       </c>
@@ -15748,7 +16387,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="293" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>37</v>
+      </c>
+      <c r="B293" t="s">
+        <v>41</v>
+      </c>
       <c r="C293">
         <v>51</v>
       </c>
@@ -15792,7 +16437,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="294" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>37</v>
+      </c>
+      <c r="B294" t="s">
+        <v>41</v>
+      </c>
       <c r="C294">
         <v>51</v>
       </c>
@@ -15836,7 +16487,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="295" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>37</v>
+      </c>
+      <c r="B295" t="s">
+        <v>41</v>
+      </c>
       <c r="C295">
         <v>51</v>
       </c>
@@ -15880,7 +16537,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="296" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>37</v>
+      </c>
+      <c r="B296" t="s">
+        <v>41</v>
+      </c>
       <c r="C296">
         <v>52</v>
       </c>
@@ -15924,7 +16587,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="297" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>37</v>
+      </c>
+      <c r="B297" t="s">
+        <v>41</v>
+      </c>
       <c r="C297">
         <v>52</v>
       </c>
@@ -15968,7 +16637,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="298" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>37</v>
+      </c>
+      <c r="B298" t="s">
+        <v>41</v>
+      </c>
       <c r="C298">
         <v>52</v>
       </c>
@@ -16012,7 +16687,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="299" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>37</v>
+      </c>
+      <c r="B299" t="s">
+        <v>41</v>
+      </c>
       <c r="C299">
         <v>52</v>
       </c>
@@ -16056,7 +16737,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="300" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>37</v>
+      </c>
+      <c r="B300" t="s">
+        <v>41</v>
+      </c>
       <c r="C300">
         <v>52</v>
       </c>
@@ -16100,7 +16787,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="301" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>37</v>
+      </c>
+      <c r="B301" t="s">
+        <v>41</v>
+      </c>
       <c r="C301">
         <v>52</v>
       </c>
@@ -16144,7 +16837,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="302" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>37</v>
+      </c>
+      <c r="B302" t="s">
+        <v>41</v>
+      </c>
       <c r="C302">
         <v>52</v>
       </c>
@@ -16188,7 +16887,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="303" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>37</v>
+      </c>
+      <c r="B303" t="s">
+        <v>41</v>
+      </c>
       <c r="C303">
         <v>52</v>
       </c>
@@ -16232,7 +16937,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="304" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>37</v>
+      </c>
+      <c r="B304" t="s">
+        <v>41</v>
+      </c>
       <c r="C304">
         <v>53</v>
       </c>
@@ -16276,7 +16987,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="305" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>37</v>
+      </c>
+      <c r="B305" t="s">
+        <v>41</v>
+      </c>
       <c r="C305">
         <v>53</v>
       </c>
@@ -16320,7 +17037,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="306" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>37</v>
+      </c>
+      <c r="B306" t="s">
+        <v>41</v>
+      </c>
       <c r="C306">
         <v>53</v>
       </c>
@@ -16364,7 +17087,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="307" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>37</v>
+      </c>
+      <c r="B307" t="s">
+        <v>41</v>
+      </c>
       <c r="C307">
         <v>53</v>
       </c>
@@ -16408,7 +17137,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="308" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>37</v>
+      </c>
+      <c r="B308" t="s">
+        <v>41</v>
+      </c>
       <c r="C308">
         <v>54</v>
       </c>
@@ -16452,7 +17187,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="309" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>37</v>
+      </c>
+      <c r="B309" t="s">
+        <v>41</v>
+      </c>
       <c r="C309">
         <v>54</v>
       </c>
@@ -16496,7 +17237,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="310" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>37</v>
+      </c>
+      <c r="B310" t="s">
+        <v>41</v>
+      </c>
       <c r="C310">
         <v>54</v>
       </c>
@@ -16540,7 +17287,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="311" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>37</v>
+      </c>
+      <c r="B311" t="s">
+        <v>41</v>
+      </c>
       <c r="C311">
         <v>54</v>
       </c>
@@ -16584,7 +17337,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="312" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>37</v>
+      </c>
+      <c r="B312" t="s">
+        <v>41</v>
+      </c>
       <c r="C312">
         <v>54</v>
       </c>
@@ -16628,7 +17387,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="313" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>37</v>
+      </c>
+      <c r="B313" t="s">
+        <v>41</v>
+      </c>
       <c r="C313">
         <v>54</v>
       </c>
@@ -16672,7 +17437,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="314" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>37</v>
+      </c>
+      <c r="B314" t="s">
+        <v>41</v>
+      </c>
       <c r="C314">
         <v>54</v>
       </c>
@@ -16716,7 +17487,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="315" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>37</v>
+      </c>
+      <c r="B315" t="s">
+        <v>41</v>
+      </c>
       <c r="C315">
         <v>54</v>
       </c>
@@ -16760,7 +17537,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="316" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>37</v>
+      </c>
+      <c r="B316" t="s">
+        <v>41</v>
+      </c>
       <c r="C316">
         <v>54</v>
       </c>
@@ -16804,7 +17587,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="317" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>37</v>
+      </c>
+      <c r="B317" t="s">
+        <v>41</v>
+      </c>
       <c r="C317">
         <v>54</v>
       </c>
@@ -16848,7 +17637,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="318" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>37</v>
+      </c>
+      <c r="B318" t="s">
+        <v>41</v>
+      </c>
       <c r="C318">
         <v>54</v>
       </c>
@@ -16892,7 +17687,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="319" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>37</v>
+      </c>
+      <c r="B319" t="s">
+        <v>41</v>
+      </c>
       <c r="C319">
         <v>54</v>
       </c>
@@ -16936,7 +17737,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="320" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>37</v>
+      </c>
+      <c r="B320" t="s">
+        <v>41</v>
+      </c>
       <c r="C320">
         <v>54</v>
       </c>
@@ -16980,7 +17787,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="321" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>37</v>
+      </c>
+      <c r="B321" t="s">
+        <v>41</v>
+      </c>
       <c r="C321">
         <v>54</v>
       </c>
@@ -17024,7 +17837,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="322" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>37</v>
+      </c>
+      <c r="B322" t="s">
+        <v>41</v>
+      </c>
       <c r="C322">
         <v>55</v>
       </c>
@@ -17068,7 +17887,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="323" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>37</v>
+      </c>
+      <c r="B323" t="s">
+        <v>41</v>
+      </c>
       <c r="C323">
         <v>55</v>
       </c>
@@ -17112,7 +17937,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="324" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>37</v>
+      </c>
+      <c r="B324" t="s">
+        <v>41</v>
+      </c>
       <c r="C324">
         <v>55</v>
       </c>
@@ -17156,7 +17987,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="325" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>37</v>
+      </c>
+      <c r="B325" t="s">
+        <v>41</v>
+      </c>
       <c r="C325">
         <v>55</v>
       </c>
@@ -17200,7 +18037,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="326" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>37</v>
+      </c>
+      <c r="B326" t="s">
+        <v>41</v>
+      </c>
       <c r="C326">
         <v>55</v>
       </c>
@@ -17244,7 +18087,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="327" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>37</v>
+      </c>
+      <c r="B327" t="s">
+        <v>41</v>
+      </c>
       <c r="C327">
         <v>55</v>
       </c>
@@ -17288,7 +18137,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="328" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>37</v>
+      </c>
+      <c r="B328" t="s">
+        <v>41</v>
+      </c>
       <c r="C328">
         <v>55</v>
       </c>
@@ -17332,7 +18187,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="329" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>37</v>
+      </c>
+      <c r="B329" t="s">
+        <v>41</v>
+      </c>
       <c r="C329">
         <v>55</v>
       </c>
@@ -17376,7 +18237,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="330" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>37</v>
+      </c>
+      <c r="B330" t="s">
+        <v>41</v>
+      </c>
       <c r="C330">
         <v>55</v>
       </c>
@@ -17420,7 +18287,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="331" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>37</v>
+      </c>
+      <c r="B331" t="s">
+        <v>41</v>
+      </c>
       <c r="C331">
         <v>56</v>
       </c>
@@ -17464,7 +18337,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="332" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>37</v>
+      </c>
+      <c r="B332" t="s">
+        <v>41</v>
+      </c>
       <c r="C332">
         <v>56</v>
       </c>
@@ -17508,7 +18387,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="333" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>37</v>
+      </c>
+      <c r="B333" t="s">
+        <v>41</v>
+      </c>
       <c r="C333">
         <v>56</v>
       </c>
@@ -17552,7 +18437,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="334" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>37</v>
+      </c>
+      <c r="B334" t="s">
+        <v>41</v>
+      </c>
       <c r="C334">
         <v>56</v>
       </c>
@@ -17596,7 +18487,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="335" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>37</v>
+      </c>
+      <c r="B335" t="s">
+        <v>41</v>
+      </c>
       <c r="C335">
         <v>56</v>
       </c>
@@ -17640,7 +18537,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="336" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>37</v>
+      </c>
+      <c r="B336" t="s">
+        <v>41</v>
+      </c>
       <c r="C336">
         <v>57</v>
       </c>
@@ -17684,7 +18587,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="337" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>37</v>
+      </c>
+      <c r="B337" t="s">
+        <v>41</v>
+      </c>
       <c r="C337">
         <v>57</v>
       </c>
@@ -17728,7 +18637,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="338" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>37</v>
+      </c>
+      <c r="B338" t="s">
+        <v>41</v>
+      </c>
       <c r="C338">
         <v>57</v>
       </c>
@@ -17772,7 +18687,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="339" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>37</v>
+      </c>
+      <c r="B339" t="s">
+        <v>41</v>
+      </c>
       <c r="C339">
         <v>57</v>
       </c>
@@ -17816,7 +18737,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="340" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>37</v>
+      </c>
+      <c r="B340" t="s">
+        <v>41</v>
+      </c>
       <c r="C340">
         <v>57</v>
       </c>
@@ -17860,7 +18787,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="341" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>37</v>
+      </c>
+      <c r="B341" t="s">
+        <v>41</v>
+      </c>
       <c r="C341">
         <v>57</v>
       </c>
@@ -17904,7 +18837,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="342" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>37</v>
+      </c>
+      <c r="B342" t="s">
+        <v>41</v>
+      </c>
       <c r="C342">
         <v>57</v>
       </c>
@@ -17948,7 +18887,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="343" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>37</v>
+      </c>
+      <c r="B343" t="s">
+        <v>41</v>
+      </c>
       <c r="C343">
         <v>57</v>
       </c>
@@ -17992,7 +18937,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="344" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>37</v>
+      </c>
+      <c r="B344" t="s">
+        <v>41</v>
+      </c>
       <c r="C344">
         <v>57</v>
       </c>
@@ -18036,7 +18987,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="345" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>37</v>
+      </c>
+      <c r="B345" t="s">
+        <v>41</v>
+      </c>
       <c r="C345">
         <v>57</v>
       </c>
@@ -18080,7 +19037,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="346" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A346" t="s">
+        <v>37</v>
+      </c>
+      <c r="B346" t="s">
+        <v>41</v>
+      </c>
       <c r="C346">
         <v>57</v>
       </c>
@@ -18124,7 +19087,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="347" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>37</v>
+      </c>
+      <c r="B347" t="s">
+        <v>41</v>
+      </c>
       <c r="C347">
         <v>57</v>
       </c>
@@ -18168,7 +19137,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="348" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>37</v>
+      </c>
+      <c r="B348" t="s">
+        <v>41</v>
+      </c>
       <c r="C348">
         <v>57</v>
       </c>
@@ -18212,7 +19187,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="349" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>37</v>
+      </c>
+      <c r="B349" t="s">
+        <v>41</v>
+      </c>
       <c r="C349">
         <v>57</v>
       </c>
@@ -18256,7 +19237,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="350" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>37</v>
+      </c>
+      <c r="B350" t="s">
+        <v>41</v>
+      </c>
       <c r="C350">
         <v>58</v>
       </c>
@@ -18300,7 +19287,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="351" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>37</v>
+      </c>
+      <c r="B351" t="s">
+        <v>41</v>
+      </c>
       <c r="C351">
         <v>58</v>
       </c>
@@ -18344,7 +19337,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="352" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>37</v>
+      </c>
+      <c r="B352" t="s">
+        <v>41</v>
+      </c>
       <c r="C352">
         <v>58</v>
       </c>
@@ -18388,7 +19387,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="353" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A353" t="s">
+        <v>37</v>
+      </c>
+      <c r="B353" t="s">
+        <v>41</v>
+      </c>
       <c r="C353">
         <v>58</v>
       </c>
@@ -18432,7 +19437,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="354" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A354" t="s">
+        <v>37</v>
+      </c>
+      <c r="B354" t="s">
+        <v>41</v>
+      </c>
       <c r="C354">
         <v>58</v>
       </c>
@@ -18476,7 +19487,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="355" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A355" t="s">
+        <v>37</v>
+      </c>
+      <c r="B355" t="s">
+        <v>41</v>
+      </c>
       <c r="C355">
         <v>58</v>
       </c>
@@ -18520,7 +19537,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="356" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A356" t="s">
+        <v>37</v>
+      </c>
+      <c r="B356" t="s">
+        <v>41</v>
+      </c>
       <c r="C356">
         <v>58</v>
       </c>
@@ -18564,7 +19587,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="357" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A357" t="s">
+        <v>37</v>
+      </c>
+      <c r="B357" t="s">
+        <v>41</v>
+      </c>
       <c r="C357">
         <v>58</v>
       </c>
@@ -18627,7 +19656,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -18638,18 +19667,18 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>33</v>
-      </c>
-      <c r="D2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>46</v>
@@ -18663,7 +19692,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>45</v>
@@ -18677,7 +19706,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>44</v>
@@ -18691,7 +19720,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>43</v>
@@ -18705,7 +19734,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>42</v>
@@ -18719,7 +19748,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>41</v>
@@ -18733,7 +19762,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>40</v>
@@ -18747,7 +19776,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>39</v>
@@ -18761,7 +19790,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>38</v>
@@ -18775,7 +19804,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>37</v>
@@ -18789,7 +19818,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>36</v>
@@ -18803,7 +19832,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14">
         <v>35</v>
@@ -18817,7 +19846,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <v>34</v>
@@ -18831,7 +19860,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>33</v>
@@ -18845,7 +19874,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17">
         <v>32</v>
@@ -18859,7 +19888,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18">
         <v>31</v>
@@ -18873,7 +19902,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19">
         <v>30</v>
@@ -18887,7 +19916,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20">
         <v>29</v>
@@ -18901,7 +19930,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>28</v>
@@ -18915,7 +19944,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22">
         <v>27</v>
@@ -18929,7 +19958,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23">
         <v>26</v>
@@ -18943,7 +19972,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24">
         <v>25</v>
@@ -18957,7 +19986,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25">
         <v>31</v>
@@ -18971,7 +20000,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26">
         <v>30</v>
@@ -18985,7 +20014,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27">
         <v>29</v>
@@ -18999,7 +20028,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28">
         <v>28</v>
@@ -19013,7 +20042,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B29">
         <v>27</v>
@@ -19027,7 +20056,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B30">
         <v>26</v>
@@ -19041,7 +20070,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B31">
         <v>25</v>
@@ -19055,7 +20084,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B32">
         <v>24</v>
@@ -19069,7 +20098,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B33">
         <v>23</v>
@@ -19083,7 +20112,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B34">
         <v>22</v>
@@ -19097,7 +20126,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B35">
         <v>21</v>
@@ -19111,7 +20140,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B36">
         <v>19</v>
@@ -19125,7 +20154,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B37">
         <v>18</v>
@@ -19139,7 +20168,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B38">
         <v>16</v>
@@ -19153,7 +20182,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B39">
         <v>14</v>
